--- a/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
+++ b/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Target Fields'!$A$1:$S$151</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Template Fields'!$A$1:$H$180</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Evidence'!$A$1:$D$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$J$234</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$J$232</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Output Objects'!$A$1:$E$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Missing Important Fields'!$A$1:$E$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'SAP Investigation Log'!$A$1:$E$10</definedName>
@@ -244,8 +244,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:J234" headerRowCount="1">
-  <autoFilter ref="A1:J234"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:J232" headerRowCount="1">
+  <autoFilter ref="A1:J232"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Field"/>
     <tableColumn id="2" name="Object"/>
@@ -17045,36 +17045,32 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>WarehouseStockOnHand</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>inventoryType</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>Enum&lt;String&gt;</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr"/>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>Not available in checked source</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr"/>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>Left blank. SAP OITW live stock metrics do not identify Planning V2 good/bad inventory type; do not infer from warehouse names.</t>
+      <c r="D63" s="5" t="inlineStr"/>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr"/>
+      <c r="G63" s="5" t="inlineStr"/>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Not needed for CoCre8 MVP; no confirmed good/bad inventory type source in SAP stock metrics.</t>
         </is>
       </c>
     </row>
@@ -17193,70 +17189,70 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>WarehouseStockOnHand</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>quantityOutbound</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr"/>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>Not available in checked source</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr"/>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>Left blank. SAP OITW has IsCommited, which is already mapped to quantityAllocated; no separate outbound quantity was found in the live stock metrics.</t>
+      <c r="D67" s="5" t="inlineStr"/>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr"/>
+      <c r="G67" s="5" t="inlineStr"/>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Not needed for CoCre8 MVP; CoCre8 issues stock directly and no separate outbound stock source was found.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>WarehouseStockOnHand</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>uniqueId</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr"/>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>Investigate source</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr"/>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>Left blank. Template expects an integer technical id, but no confirmed source/key rule has been provided.</t>
+      <c r="D68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Derived stable integer from MinStock-style RowKey part|SPLMaster|warehouse</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -20327,40 +20323,36 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+      <c r="A158" s="3" t="inlineStr">
         <is>
           <t>PurchaseOrders</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B158" s="3" t="inlineStr">
         <is>
           <t>demandStatus</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
+      <c r="C158" s="3" t="inlineStr">
         <is>
           <t>Enum&lt;String&gt;</t>
         </is>
       </c>
-      <c r="D158" s="2" t="inlineStr"/>
-      <c r="E158" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t>CoCre8 HelpDesk issue tracker:ReplenishStatus when exact PO plus exact part/SPL Master evidence exists</t>
-        </is>
-      </c>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
+      <c r="D158" s="3" t="inlineStr"/>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="inlineStr"/>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.DocNum and part/SPL Master evidence also matches; current export needs reconciliation.</t>
         </is>
       </c>
     </row>
@@ -21447,7 +21439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J234"/>
+  <dimension ref="A1:J232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -28625,12 +28617,12 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>inventoryType</t>
+          <t>personId</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>WarehouseStockOnHand</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
@@ -28641,12 +28633,12 @@
       <c r="D150" s="4" t="inlineStr"/>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>Not available in checked source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseStockOnHand.inventoryType?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.personId?</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr">
@@ -28658,19 +28650,19 @@
       <c r="I150" s="4" t="inlineStr"/>
       <c r="J150" s="4" t="inlineStr">
         <is>
-          <t>Left blank. SAP OITW live stock metrics do not identify Planning V2 good/bad inventory type; do not infer from warehouse names.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>quantityOutbound</t>
+          <t>role</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>WarehouseStockOnHand</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -28681,12 +28673,12 @@
       <c r="D151" s="4" t="inlineStr"/>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>Not available in checked source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseStockOnHand.quantityOutbound?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.role?</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
@@ -28698,19 +28690,19 @@
       <c r="I151" s="4" t="inlineStr"/>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>Left blank. SAP OITW has IsCommited, which is already mapped to quantityAllocated; no separate outbound quantity was found in the live stock metrics.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>uniqueId</t>
+          <t>addressId</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>WarehouseStockOnHand</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
@@ -28721,12 +28713,12 @@
       <c r="D152" s="4" t="inlineStr"/>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>Investigate source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseStockOnHand.uniqueId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.addressId?</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
@@ -28738,14 +28730,14 @@
       <c r="I152" s="4" t="inlineStr"/>
       <c r="J152" s="4" t="inlineStr">
         <is>
-          <t>Left blank. Template expects an integer technical id, but no confirmed source/key rule has been provided.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>personId</t>
+          <t>nodeId</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
@@ -28766,7 +28758,7 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.personId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.nodeId?</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
@@ -28785,7 +28777,7 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>firstName</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
@@ -28806,7 +28798,7 @@
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.role?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.firstName?</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr">
@@ -28825,7 +28817,7 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>addressId</t>
+          <t>middleName</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
@@ -28846,7 +28838,7 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.addressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.middleName?</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
@@ -28865,7 +28857,7 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>nodeId</t>
+          <t>surname</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
@@ -28886,7 +28878,7 @@
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.nodeId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.surname?</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr">
@@ -28905,7 +28897,7 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>firstName</t>
+          <t>isActive</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
@@ -28926,7 +28918,7 @@
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.firstName?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.isActive?</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
@@ -28945,7 +28937,7 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>middleName</t>
+          <t>telephoneNumber</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
@@ -28966,7 +28958,7 @@
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.middleName?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.telephoneNumber?</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr">
@@ -28985,12 +28977,12 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>surname</t>
+          <t>customerCompanyCode</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
@@ -29006,7 +28998,7 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.surname?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.customerCompanyCode?</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
@@ -29025,12 +29017,12 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>isActive</t>
+          <t>orderType</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
@@ -29046,7 +29038,7 @@
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.isActive?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderType?</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr">
@@ -29065,12 +29057,12 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>telephoneNumber</t>
+          <t>orderStatus</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
@@ -29086,7 +29078,7 @@
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.telephoneNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStatus?</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
@@ -29105,7 +29097,7 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>customerCompanyCode</t>
+          <t>orderStartDatetime</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
@@ -29126,7 +29118,7 @@
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.customerCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStartDatetime?</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr">
@@ -29145,7 +29137,7 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>orderType</t>
+          <t>requestTicketDateTime</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
@@ -29166,7 +29158,7 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderType?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.requestTicketDateTime?</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
@@ -29185,7 +29177,7 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>orderStatus</t>
+          <t>siteCompanyCode</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
@@ -29206,7 +29198,7 @@
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.siteCompanyCode?</t>
         </is>
       </c>
       <c r="G164" s="4" t="inlineStr">
@@ -29225,7 +29217,7 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>orderStartDatetime</t>
+          <t>assignedPersonCode</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
@@ -29246,7 +29238,7 @@
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStartDatetime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
@@ -29265,7 +29257,7 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>requestTicketDateTime</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
@@ -29286,7 +29278,7 @@
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.requestTicketDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr">
@@ -29305,7 +29297,7 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>siteCompanyCode</t>
+          <t>serialNumber</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
@@ -29326,7 +29318,7 @@
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.siteCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.serialNumber?</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -29345,7 +29337,7 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>assignedPersonCode</t>
+          <t>relCompanyId</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
@@ -29366,7 +29358,7 @@
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr">
@@ -29385,7 +29377,7 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>deviceSerialNumber</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
@@ -29406,7 +29398,7 @@
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.deviceSerialNumber?</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
@@ -29425,12 +29417,12 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>serialNumber</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
@@ -29446,7 +29438,7 @@
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.serialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.orderNumber?</t>
         </is>
       </c>
       <c r="G170" s="4" t="inlineStr">
@@ -29465,12 +29457,12 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>relCompanyId</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
@@ -29486,7 +29478,7 @@
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.location?</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
@@ -29505,12 +29497,12 @@
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>deviceSerialNumber</t>
+          <t>eta</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
@@ -29526,7 +29518,7 @@
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.deviceSerialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.eta?</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr">
@@ -29545,7 +29537,7 @@
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>actualEta</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
@@ -29566,7 +29558,7 @@
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualEta?</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -29585,7 +29577,7 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>actualResolveDateTime</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
@@ -29606,7 +29598,7 @@
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.location?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualResolveDateTime?</t>
         </is>
       </c>
       <c r="G174" s="4" t="inlineStr">
@@ -29625,7 +29617,7 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>eta</t>
+          <t>recallDateTime</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
@@ -29646,7 +29638,7 @@
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.eta?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.recallDateTime?</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
@@ -29665,7 +29657,7 @@
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>actualEta</t>
+          <t>actualRecallDateTime</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
@@ -29686,7 +29678,7 @@
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualEta?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualRecallDateTime?</t>
         </is>
       </c>
       <c r="G176" s="4" t="inlineStr">
@@ -29705,7 +29697,7 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>actualResolveDateTime</t>
+          <t>slaEtaClock</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
@@ -29726,7 +29718,7 @@
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualResolveDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaClock?</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
@@ -29745,7 +29737,7 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>recallDateTime</t>
+          <t>slaResolveClock</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
@@ -29766,7 +29758,7 @@
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.recallDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveClock?</t>
         </is>
       </c>
       <c r="G178" s="4" t="inlineStr">
@@ -29785,7 +29777,7 @@
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>actualRecallDateTime</t>
+          <t>slaFailureCode</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
@@ -29806,7 +29798,7 @@
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualRecallDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaFailureCode?</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
@@ -29825,7 +29817,7 @@
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>slaEtaClock</t>
+          <t>slaEtaHit</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
@@ -29846,7 +29838,7 @@
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaClock?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaHit?</t>
         </is>
       </c>
       <c r="G180" s="4" t="inlineStr">
@@ -29865,7 +29857,7 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>slaResolveClock</t>
+          <t>slaResolvedDateTime</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
@@ -29886,7 +29878,7 @@
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveClock?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolvedDateTime?</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
@@ -29905,12 +29897,12 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>slaFailureCode</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
@@ -29926,7 +29918,7 @@
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaFailureCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderNumber?</t>
         </is>
       </c>
       <c r="G182" s="4" t="inlineStr">
@@ -29945,12 +29937,12 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>slaEtaHit</t>
+          <t>requestId</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
@@ -29966,7 +29958,7 @@
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaHit?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.requestId?</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
@@ -29985,12 +29977,12 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>slaResolvedDateTime</t>
+          <t>customerCompanyCode</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
@@ -30006,7 +29998,7 @@
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.customerCompanyCode?</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr">
@@ -30025,7 +30017,7 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>orderStatus</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
@@ -30046,7 +30038,7 @@
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStatus?</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr">
@@ -30065,7 +30057,7 @@
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>requestId</t>
+          <t>orderStartDatetime</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
@@ -30086,7 +30078,7 @@
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.requestId?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStartDatetime?</t>
         </is>
       </c>
       <c r="G186" s="4" t="inlineStr">
@@ -30105,7 +30097,7 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>customerCompanyCode</t>
+          <t>siteCompanyCode</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
@@ -30126,7 +30118,7 @@
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.customerCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.siteCompanyCode?</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr">
@@ -30145,7 +30137,7 @@
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>orderStatus</t>
+          <t>repairType</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
@@ -30166,7 +30158,7 @@
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairType?</t>
         </is>
       </c>
       <c r="G188" s="4" t="inlineStr">
@@ -30185,7 +30177,7 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>orderStartDatetime</t>
+          <t>partsOrderDateTime</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
@@ -30206,7 +30198,7 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStartDatetime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsOrderDateTime?</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr">
@@ -30225,7 +30217,7 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>siteCompanyCode</t>
+          <t>partsReceivedDateTime</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
@@ -30246,7 +30238,7 @@
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.siteCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsReceivedDateTime?</t>
         </is>
       </c>
       <c r="G190" s="4" t="inlineStr">
@@ -30265,7 +30257,7 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>repairType</t>
+          <t>repairCode</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
@@ -30286,7 +30278,7 @@
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairType?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCode?</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -30305,7 +30297,7 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>partsOrderDateTime</t>
+          <t>repairCompany</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
@@ -30326,7 +30318,7 @@
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsOrderDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCompany?</t>
         </is>
       </c>
       <c r="G192" s="4" t="inlineStr">
@@ -30345,7 +30337,7 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>partsReceivedDateTime</t>
+          <t>raStatus</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
@@ -30366,7 +30358,7 @@
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsReceivedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.raStatus?</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -30385,7 +30377,7 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>repairCode</t>
+          <t>Warehouse</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
@@ -30406,7 +30398,7 @@
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.Warehouse?</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr">
@@ -30425,7 +30417,7 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>repairCompany</t>
+          <t>assignedPerson</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
@@ -30446,7 +30438,7 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCompany?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.assignedPerson?</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -30465,7 +30457,7 @@
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>raStatus</t>
+          <t>orderedPartId</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
@@ -30486,7 +30478,7 @@
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.raStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderedPartId?</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr">
@@ -30505,7 +30497,7 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>actualPartId</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
@@ -30526,7 +30518,7 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.Warehouse?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.actualPartId?</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
@@ -30545,7 +30537,7 @@
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>assignedPerson</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
@@ -30566,7 +30558,7 @@
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.assignedPerson?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.resolvedDateTime?</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr">
@@ -30585,7 +30577,7 @@
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>orderedPartId</t>
+          <t>serialNumber</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
@@ -30606,7 +30598,7 @@
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderedPartId?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.serialNumber?</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
@@ -30625,7 +30617,7 @@
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>actualPartId</t>
+          <t>quantityUsed</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
@@ -30646,7 +30638,7 @@
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.actualPartId?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.quantityUsed?</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr">
@@ -30665,7 +30657,7 @@
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>relCompanyId</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
@@ -30686,7 +30678,7 @@
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.resolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.relCompanyId?</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
@@ -30705,7 +30697,7 @@
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>serialNumber</t>
+          <t>partsUsedDateTime</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
@@ -30726,7 +30718,7 @@
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.serialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsUsedDateTime?</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr">
@@ -30745,7 +30737,7 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>quantityUsed</t>
+          <t>deviceSerialNumber</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
@@ -30766,7 +30758,7 @@
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.quantityUsed?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.deviceSerialNumber?</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -30785,12 +30777,12 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>relCompanyId</t>
+          <t>partCode</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
@@ -30806,7 +30798,7 @@
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.relCompanyId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.partCode?</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr">
@@ -30825,12 +30817,12 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>partsUsedDateTime</t>
+          <t>cost</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
@@ -30846,7 +30838,7 @@
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsUsedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.cost?</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -30865,12 +30857,12 @@
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>deviceSerialNumber</t>
+          <t>currencyCode</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
@@ -30886,7 +30878,7 @@
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.deviceSerialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.currencyCode?</t>
         </is>
       </c>
       <c r="G206" s="4" t="inlineStr">
@@ -30905,7 +30897,7 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>averageCost</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
@@ -30926,7 +30918,7 @@
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.averageCost?</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -30945,12 +30937,12 @@
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>partCode</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
@@ -30966,7 +30958,7 @@
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.cost?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
         </is>
       </c>
       <c r="G208" s="4" t="inlineStr">
@@ -30985,12 +30977,12 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>currencyCode</t>
+          <t>modelCode</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
@@ -31006,7 +30998,7 @@
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.currencyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr">
@@ -31025,12 +31017,12 @@
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>averageCost</t>
+          <t>modelDescription</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
@@ -31046,7 +31038,7 @@
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.averageCost?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
         </is>
       </c>
       <c r="G210" s="4" t="inlineStr">
@@ -31065,12 +31057,12 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>inventoryTransferImoId</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
@@ -31086,7 +31078,7 @@
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.inventoryTransferImoId?</t>
         </is>
       </c>
       <c r="G211" s="4" t="inlineStr">
@@ -31105,12 +31097,12 @@
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>modelCode</t>
+          <t>createdDateTime</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
@@ -31126,7 +31118,7 @@
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.createdDateTime?</t>
         </is>
       </c>
       <c r="G212" s="4" t="inlineStr">
@@ -31145,12 +31137,12 @@
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>modelDescription</t>
+          <t>completedDateTime</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
@@ -31166,7 +31158,7 @@
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.completedDateTime?</t>
         </is>
       </c>
       <c r="G213" s="4" t="inlineStr">
@@ -31185,7 +31177,7 @@
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>inventoryTransferImoId</t>
+          <t>fromWarehouseId</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
@@ -31206,7 +31198,7 @@
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.inventoryTransferImoId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.fromWarehouseId?</t>
         </is>
       </c>
       <c r="G214" s="4" t="inlineStr">
@@ -31225,7 +31217,7 @@
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>createdDateTime</t>
+          <t>toWarehouseId</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
@@ -31246,7 +31238,7 @@
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.createdDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.toWarehouseId?</t>
         </is>
       </c>
       <c r="G215" s="4" t="inlineStr">
@@ -31265,7 +31257,7 @@
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>completedDateTime</t>
+          <t>demandStatus</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
@@ -31286,7 +31278,7 @@
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.completedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.demandStatus?</t>
         </is>
       </c>
       <c r="G216" s="4" t="inlineStr">
@@ -31305,7 +31297,7 @@
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>fromWarehouseId</t>
+          <t>orderStatusIsClosed</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
@@ -31326,7 +31318,7 @@
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.fromWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.orderStatusIsClosed?</t>
         </is>
       </c>
       <c r="G217" s="4" t="inlineStr">
@@ -31345,7 +31337,7 @@
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>toWarehouseId</t>
+          <t>movementType</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
@@ -31366,7 +31358,7 @@
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.toWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
         </is>
       </c>
       <c r="G218" s="4" t="inlineStr">
@@ -31385,7 +31377,7 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>demandStatus</t>
+          <t>addressId</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
@@ -31406,7 +31398,7 @@
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.demandStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
         </is>
       </c>
       <c r="G219" s="4" t="inlineStr">
@@ -31425,7 +31417,7 @@
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>orderStatusIsClosed</t>
+          <t>isResolved</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
@@ -31446,7 +31438,7 @@
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.orderStatusIsClosed?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.isResolved?</t>
         </is>
       </c>
       <c r="G220" s="4" t="inlineStr">
@@ -31465,7 +31457,7 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>movementType</t>
+          <t>partNumber</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
@@ -31486,7 +31478,7 @@
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.partNumber?</t>
         </is>
       </c>
       <c r="G221" s="4" t="inlineStr">
@@ -31505,7 +31497,7 @@
     <row r="222">
       <c r="A222" s="4" t="inlineStr">
         <is>
-          <t>addressId</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="B222" s="4" t="inlineStr">
@@ -31526,7 +31518,7 @@
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.quantity?</t>
         </is>
       </c>
       <c r="G222" s="4" t="inlineStr">
@@ -31545,7 +31537,7 @@
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>isResolved</t>
+          <t>shipListCode</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
@@ -31566,7 +31558,7 @@
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.isResolved?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
         </is>
       </c>
       <c r="G223" s="4" t="inlineStr">
@@ -31583,54 +31575,54 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="4" t="inlineStr">
-        <is>
-          <t>partNumber</t>
-        </is>
-      </c>
-      <c r="B224" s="4" t="inlineStr">
-        <is>
-          <t>InventoryTransfers</t>
-        </is>
-      </c>
-      <c r="C224" s="4" t="inlineStr">
+      <c r="A224" s="3" t="inlineStr">
+        <is>
+          <t>demandStatus</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>PurchaseOrders</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="inlineStr">
         <is>
           <t>Planning V2 template</t>
         </is>
       </c>
-      <c r="D224" s="4" t="inlineStr"/>
-      <c r="E224" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F224" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.partNumber?</t>
-        </is>
-      </c>
-      <c r="G224" s="4" t="inlineStr">
+      <c r="D224" s="3" t="inlineStr"/>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="F224" s="3" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
+        </is>
+      </c>
+      <c r="G224" s="3" t="inlineStr">
         <is>
           <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
         </is>
       </c>
-      <c r="H224" s="4" t="inlineStr"/>
-      <c r="I224" s="4" t="inlineStr"/>
-      <c r="J224" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="H224" s="3" t="inlineStr"/>
+      <c r="I224" s="3" t="inlineStr"/>
+      <c r="J224" s="3" t="inlineStr">
+        <is>
+          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.DocNum and part/SPL Master evidence also matches; current export needs reconciliation.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>partTypeCode</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
@@ -31646,7 +31638,7 @@
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.quantity?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeCode?</t>
         </is>
       </c>
       <c r="G225" s="4" t="inlineStr">
@@ -31665,12 +31657,12 @@
     <row r="226">
       <c r="A226" s="4" t="inlineStr">
         <is>
-          <t>shipListCode</t>
+          <t>description</t>
         </is>
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr">
@@ -31686,7 +31678,7 @@
       </c>
       <c r="F226" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.description?</t>
         </is>
       </c>
       <c r="G226" s="4" t="inlineStr">
@@ -31705,12 +31697,12 @@
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>partTypeCode</t>
+          <t>partNumber</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
@@ -31726,7 +31718,7 @@
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
         </is>
       </c>
       <c r="G227" s="4" t="inlineStr">
@@ -31745,12 +31737,12 @@
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>unitOfMeasure</t>
         </is>
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
@@ -31766,7 +31758,7 @@
       </c>
       <c r="F228" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.description?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
         </is>
       </c>
       <c r="G228" s="4" t="inlineStr">
@@ -31785,7 +31777,7 @@
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>partNumber</t>
+          <t>yield</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
@@ -31806,7 +31798,7 @@
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
         </is>
       </c>
       <c r="G229" s="4" t="inlineStr">
@@ -31825,12 +31817,12 @@
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
         <is>
-          <t>unitOfMeasure</t>
+          <t>warehouseId</t>
         </is>
       </c>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C230" s="4" t="inlineStr">
@@ -31846,7 +31838,7 @@
       </c>
       <c r="F230" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.warehouseId?</t>
         </is>
       </c>
       <c r="G230" s="4" t="inlineStr">
@@ -31865,12 +31857,12 @@
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>yield</t>
+          <t>exclusionType</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
@@ -31886,7 +31878,7 @@
       </c>
       <c r="F231" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusionType?</t>
         </is>
       </c>
       <c r="G231" s="4" t="inlineStr">
@@ -31905,7 +31897,7 @@
     <row r="232">
       <c r="A232" s="4" t="inlineStr">
         <is>
-          <t>warehouseId</t>
+          <t>exclusion</t>
         </is>
       </c>
       <c r="B232" s="4" t="inlineStr">
@@ -31926,7 +31918,7 @@
       </c>
       <c r="F232" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.warehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusion?</t>
         </is>
       </c>
       <c r="G232" s="4" t="inlineStr">
@@ -31942,88 +31934,8 @@
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="4" t="inlineStr">
-        <is>
-          <t>exclusionType</t>
-        </is>
-      </c>
-      <c r="B233" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C233" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D233" s="4" t="inlineStr"/>
-      <c r="E233" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F233" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusionType?</t>
-        </is>
-      </c>
-      <c r="G233" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H233" s="4" t="inlineStr"/>
-      <c r="I233" s="4" t="inlineStr"/>
-      <c r="J233" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="4" t="inlineStr">
-        <is>
-          <t>exclusion</t>
-        </is>
-      </c>
-      <c r="B234" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C234" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D234" s="4" t="inlineStr"/>
-      <c r="E234" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F234" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusion?</t>
-        </is>
-      </c>
-      <c r="G234" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H234" s="4" t="inlineStr"/>
-      <c r="I234" s="4" t="inlineStr"/>
-      <c r="J234" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J234"/>
+  <autoFilter ref="A1:J232"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -32583,31 +32495,27 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>WarehouseStockOnHand</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>WarehouseStockOnHand.csv</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>partCode, warehouseCode, inventoryType, quantityAllocated, quantityOnHand, quantityInbound, quantityOutbound, uniqueId</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>inventoryType; quantityOutbound; uniqueId</t>
-        </is>
-      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>partCode, warehouseCode, quantityAllocated, quantityOnHand, quantityInbound, uniqueId</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -32799,27 +32707,31 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>PurchaseOrders</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>PurchaseOrders.csv</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>purchaseOrderNumber, purchaseOrderStatus, creationDateTime, approvalDateTime, toWarehouseId, vendorId, demandStatus, partNumber, quantity, lineCost, quantityReceived, receivedDateTime</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr"/>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>demandStatus</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">

--- a/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
+++ b/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Target Fields'!$A$1:$S$151</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Template Fields'!$A$1:$H$180</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Evidence'!$A$1:$D$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$J$232</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$J$224</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Output Objects'!$A$1:$E$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Missing Important Fields'!$A$1:$E$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'SAP Investigation Log'!$A$1:$E$10</definedName>
@@ -244,8 +244,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:J232" headerRowCount="1">
-  <autoFilter ref="A1:J232"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:J224" headerRowCount="1">
+  <autoFilter ref="A1:J224"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Field"/>
     <tableColumn id="2" name="Object"/>
@@ -16545,40 +16545,44 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Warehouses</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>addressId</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>External (Client-facing) Id</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>Investigate source</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr"/>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>Expected site/address id linking to the Addresses template. Data dictionary field: warehouse.address_id.</t>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Manual fill workbook:addressId; currently warehouse code per user mapping</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -16617,116 +16621,128 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Warehouses</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>returnWarehouseId</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>External (Client-facing) Id</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>Investigate source</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr"/>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>Expected preferred warehouse for return/faulty stock going to repair or scrap. Data fields: return_warehouse.</t>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Manual fill workbook:returnWarehouseId</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Warehouses</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>supplyWarehouseId</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>External (Client-facing) Id</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>Investigate source</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr"/>
-      <c r="G52" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>Expected preferred replenishment/source warehouse. Data fields: supply_warehouse.</t>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Manual fill workbook:supplyWarehouseId</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Warehouses</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>warehouseTypeId</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>enum&lt;String&gt;</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>[BOOT,DEP,REPAIR]</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>Investigate source</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr"/>
-      <c r="G53" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>Expected site type enum; sample template uses BOOT, DEP, and REPAIR. Data fields mark warehouse_type_id as critical.</t>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Manual fill workbook:warehouseTypeId</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -16799,36 +16815,40 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Warehouses</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>isReplenishable</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr"/>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>Investigate source</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr"/>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>Expected true when the site can be restocked. Data dictionary field: is_replenishable.</t>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Manual fill workbook:isReplenishable</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -16863,108 +16883,120 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Warehouses</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>isBranchStockable</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr"/>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>Investigate source</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr"/>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>Expected true when branch/regional location can accept stock. Data fields: cst_branch_stockable.</t>
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Manual fill workbook:isBranchStockable</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Warehouses</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>isRemote</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr"/>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>Investigate source</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr"/>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>Expected true when this is an outlying/regional location. Data fields: cst_remote.</t>
+      <c r="D59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Manual fill workbook:isRemote</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Warehouses</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>warehouseStatusId</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Enum&lt;String&gt;</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Confirm. May not be required</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>Investigate source</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr"/>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>Expected current/inactive status if required by the importer. Template says confirm; data fields mention cst_active and is_obsolete.</t>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Manual fill workbook:isObsolete inverted to is_active flag (Y active, N obsolete)</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -21439,7 +21471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J232"/>
+  <dimension ref="A1:J224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -28297,12 +28329,12 @@
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>addressId</t>
+          <t>personId</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>Warehouses</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
@@ -28313,12 +28345,12 @@
       <c r="D142" s="4" t="inlineStr"/>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>Investigate source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.addressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.personId?</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
@@ -28330,19 +28362,19 @@
       <c r="I142" s="4" t="inlineStr"/>
       <c r="J142" s="4" t="inlineStr">
         <is>
-          <t>Expected site/address id linking to the Addresses template. Data dictionary field: warehouse.address_id.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>returnWarehouseId</t>
+          <t>role</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Warehouses</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -28353,12 +28385,12 @@
       <c r="D143" s="4" t="inlineStr"/>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>Investigate source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.returnWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.role?</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
@@ -28370,19 +28402,19 @@
       <c r="I143" s="4" t="inlineStr"/>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>Expected preferred warehouse for return/faulty stock going to repair or scrap. Data fields: return_warehouse.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>supplyWarehouseId</t>
+          <t>addressId</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>Warehouses</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -28393,12 +28425,12 @@
       <c r="D144" s="4" t="inlineStr"/>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>Investigate source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.supplyWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.addressId?</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr">
@@ -28410,19 +28442,19 @@
       <c r="I144" s="4" t="inlineStr"/>
       <c r="J144" s="4" t="inlineStr">
         <is>
-          <t>Expected preferred replenishment/source warehouse. Data fields: supply_warehouse.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>warehouseTypeId</t>
+          <t>nodeId</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Warehouses</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -28433,12 +28465,12 @@
       <c r="D145" s="4" t="inlineStr"/>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>Investigate source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.warehouseTypeId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.nodeId?</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
@@ -28450,19 +28482,19 @@
       <c r="I145" s="4" t="inlineStr"/>
       <c r="J145" s="4" t="inlineStr">
         <is>
-          <t>Expected site type enum; sample template uses BOOT, DEP, and REPAIR. Data fields mark warehouse_type_id as critical.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>isReplenishable</t>
+          <t>firstName</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>Warehouses</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -28473,12 +28505,12 @@
       <c r="D146" s="4" t="inlineStr"/>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>Investigate source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.isReplenishable?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.firstName?</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr">
@@ -28490,19 +28522,19 @@
       <c r="I146" s="4" t="inlineStr"/>
       <c r="J146" s="4" t="inlineStr">
         <is>
-          <t>Expected true when the site can be restocked. Data dictionary field: is_replenishable.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>isBranchStockable</t>
+          <t>middleName</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Warehouses</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -28513,12 +28545,12 @@
       <c r="D147" s="4" t="inlineStr"/>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>Investigate source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.isBranchStockable?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.middleName?</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
@@ -28530,19 +28562,19 @@
       <c r="I147" s="4" t="inlineStr"/>
       <c r="J147" s="4" t="inlineStr">
         <is>
-          <t>Expected true when branch/regional location can accept stock. Data fields: cst_branch_stockable.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>isRemote</t>
+          <t>surname</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>Warehouses</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
@@ -28553,12 +28585,12 @@
       <c r="D148" s="4" t="inlineStr"/>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>Investigate source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.isRemote?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.surname?</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr">
@@ -28570,19 +28602,19 @@
       <c r="I148" s="4" t="inlineStr"/>
       <c r="J148" s="4" t="inlineStr">
         <is>
-          <t>Expected true when this is an outlying/regional location. Data fields: cst_remote.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>warehouseStatusId</t>
+          <t>isActive</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Warehouses</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -28593,12 +28625,12 @@
       <c r="D149" s="4" t="inlineStr"/>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>Investigate source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Warehouses.warehouseStatusId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.isActive?</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
@@ -28610,14 +28642,14 @@
       <c r="I149" s="4" t="inlineStr"/>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>Expected current/inactive status if required by the importer. Template says confirm; data fields mention cst_active and is_obsolete.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>personId</t>
+          <t>telephoneNumber</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
@@ -28638,7 +28670,7 @@
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.personId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.telephoneNumber?</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr">
@@ -28657,12 +28689,12 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>customerCompanyCode</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -28678,7 +28710,7 @@
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.role?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.customerCompanyCode?</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
@@ -28697,12 +28729,12 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>addressId</t>
+          <t>orderType</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
@@ -28718,7 +28750,7 @@
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.addressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderType?</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
@@ -28737,12 +28769,12 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>nodeId</t>
+          <t>orderStatus</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -28758,7 +28790,7 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.nodeId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStatus?</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
@@ -28777,12 +28809,12 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>firstName</t>
+          <t>orderStartDatetime</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
@@ -28798,7 +28830,7 @@
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.firstName?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStartDatetime?</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr">
@@ -28817,12 +28849,12 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>middleName</t>
+          <t>requestTicketDateTime</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
@@ -28838,7 +28870,7 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.middleName?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.requestTicketDateTime?</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
@@ -28857,12 +28889,12 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>surname</t>
+          <t>siteCompanyCode</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
@@ -28878,7 +28910,7 @@
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.surname?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.siteCompanyCode?</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr">
@@ -28897,12 +28929,12 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>isActive</t>
+          <t>assignedPersonCode</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
@@ -28918,7 +28950,7 @@
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.isActive?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
@@ -28937,12 +28969,12 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>telephoneNumber</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
@@ -28958,7 +28990,7 @@
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.telephoneNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr">
@@ -28977,7 +29009,7 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>customerCompanyCode</t>
+          <t>serialNumber</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
@@ -28998,7 +29030,7 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.customerCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.serialNumber?</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
@@ -29017,7 +29049,7 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>orderType</t>
+          <t>relCompanyId</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
@@ -29038,7 +29070,7 @@
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderType?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr">
@@ -29057,7 +29089,7 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>orderStatus</t>
+          <t>deviceSerialNumber</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
@@ -29078,7 +29110,7 @@
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.deviceSerialNumber?</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
@@ -29097,12 +29129,12 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>orderStartDatetime</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
@@ -29118,7 +29150,7 @@
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStartDatetime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.orderNumber?</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr">
@@ -29137,12 +29169,12 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>requestTicketDateTime</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
@@ -29158,7 +29190,7 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.requestTicketDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.location?</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
@@ -29177,12 +29209,12 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>siteCompanyCode</t>
+          <t>eta</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
@@ -29198,7 +29230,7 @@
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.siteCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.eta?</t>
         </is>
       </c>
       <c r="G164" s="4" t="inlineStr">
@@ -29217,12 +29249,12 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>assignedPersonCode</t>
+          <t>actualEta</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
@@ -29238,7 +29270,7 @@
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualEta?</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
@@ -29257,12 +29289,12 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>actualResolveDateTime</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
@@ -29278,7 +29310,7 @@
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualResolveDateTime?</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr">
@@ -29297,12 +29329,12 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>serialNumber</t>
+          <t>recallDateTime</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
@@ -29318,7 +29350,7 @@
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.serialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.recallDateTime?</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -29337,12 +29369,12 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>relCompanyId</t>
+          <t>actualRecallDateTime</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
@@ -29358,7 +29390,7 @@
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualRecallDateTime?</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr">
@@ -29377,12 +29409,12 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>deviceSerialNumber</t>
+          <t>slaEtaClock</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
@@ -29398,7 +29430,7 @@
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.deviceSerialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaClock?</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
@@ -29417,7 +29449,7 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>slaResolveClock</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
@@ -29438,7 +29470,7 @@
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveClock?</t>
         </is>
       </c>
       <c r="G170" s="4" t="inlineStr">
@@ -29457,7 +29489,7 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>slaFailureCode</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
@@ -29478,7 +29510,7 @@
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.location?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaFailureCode?</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
@@ -29497,7 +29529,7 @@
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>eta</t>
+          <t>slaEtaHit</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
@@ -29518,7 +29550,7 @@
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.eta?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaHit?</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr">
@@ -29537,7 +29569,7 @@
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>actualEta</t>
+          <t>slaResolvedDateTime</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
@@ -29558,7 +29590,7 @@
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualEta?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolvedDateTime?</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -29577,12 +29609,12 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>actualResolveDateTime</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
@@ -29598,7 +29630,7 @@
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualResolveDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderNumber?</t>
         </is>
       </c>
       <c r="G174" s="4" t="inlineStr">
@@ -29617,12 +29649,12 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>recallDateTime</t>
+          <t>requestId</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
@@ -29638,7 +29670,7 @@
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.recallDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.requestId?</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
@@ -29657,12 +29689,12 @@
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>actualRecallDateTime</t>
+          <t>customerCompanyCode</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
@@ -29678,7 +29710,7 @@
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualRecallDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.customerCompanyCode?</t>
         </is>
       </c>
       <c r="G176" s="4" t="inlineStr">
@@ -29697,12 +29729,12 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>slaEtaClock</t>
+          <t>orderStatus</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
@@ -29718,7 +29750,7 @@
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaClock?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStatus?</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
@@ -29737,12 +29769,12 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>slaResolveClock</t>
+          <t>orderStartDatetime</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
@@ -29758,7 +29790,7 @@
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveClock?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStartDatetime?</t>
         </is>
       </c>
       <c r="G178" s="4" t="inlineStr">
@@ -29777,12 +29809,12 @@
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>slaFailureCode</t>
+          <t>siteCompanyCode</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
@@ -29798,7 +29830,7 @@
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaFailureCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.siteCompanyCode?</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
@@ -29817,12 +29849,12 @@
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>slaEtaHit</t>
+          <t>repairType</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
@@ -29838,7 +29870,7 @@
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaHit?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairType?</t>
         </is>
       </c>
       <c r="G180" s="4" t="inlineStr">
@@ -29857,12 +29889,12 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>slaResolvedDateTime</t>
+          <t>partsOrderDateTime</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
@@ -29878,7 +29910,7 @@
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsOrderDateTime?</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
@@ -29897,7 +29929,7 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>partsReceivedDateTime</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
@@ -29918,7 +29950,7 @@
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsReceivedDateTime?</t>
         </is>
       </c>
       <c r="G182" s="4" t="inlineStr">
@@ -29937,7 +29969,7 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>requestId</t>
+          <t>repairCode</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
@@ -29958,7 +29990,7 @@
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.requestId?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCode?</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
@@ -29977,7 +30009,7 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>customerCompanyCode</t>
+          <t>repairCompany</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
@@ -29998,7 +30030,7 @@
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.customerCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCompany?</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr">
@@ -30017,7 +30049,7 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>orderStatus</t>
+          <t>raStatus</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
@@ -30038,7 +30070,7 @@
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.raStatus?</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr">
@@ -30057,7 +30089,7 @@
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>orderStartDatetime</t>
+          <t>Warehouse</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
@@ -30078,7 +30110,7 @@
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStartDatetime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.Warehouse?</t>
         </is>
       </c>
       <c r="G186" s="4" t="inlineStr">
@@ -30097,7 +30129,7 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>siteCompanyCode</t>
+          <t>assignedPerson</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
@@ -30118,7 +30150,7 @@
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.siteCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.assignedPerson?</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr">
@@ -30137,7 +30169,7 @@
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>repairType</t>
+          <t>orderedPartId</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
@@ -30158,7 +30190,7 @@
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairType?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderedPartId?</t>
         </is>
       </c>
       <c r="G188" s="4" t="inlineStr">
@@ -30177,7 +30209,7 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>partsOrderDateTime</t>
+          <t>actualPartId</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
@@ -30198,7 +30230,7 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsOrderDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.actualPartId?</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr">
@@ -30217,7 +30249,7 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>partsReceivedDateTime</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
@@ -30238,7 +30270,7 @@
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsReceivedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.resolvedDateTime?</t>
         </is>
       </c>
       <c r="G190" s="4" t="inlineStr">
@@ -30257,7 +30289,7 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>repairCode</t>
+          <t>serialNumber</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
@@ -30278,7 +30310,7 @@
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.serialNumber?</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -30297,7 +30329,7 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>repairCompany</t>
+          <t>quantityUsed</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
@@ -30318,7 +30350,7 @@
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCompany?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.quantityUsed?</t>
         </is>
       </c>
       <c r="G192" s="4" t="inlineStr">
@@ -30337,7 +30369,7 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>raStatus</t>
+          <t>relCompanyId</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
@@ -30358,7 +30390,7 @@
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.raStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.relCompanyId?</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -30377,7 +30409,7 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>partsUsedDateTime</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
@@ -30398,7 +30430,7 @@
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.Warehouse?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsUsedDateTime?</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr">
@@ -30417,7 +30449,7 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>assignedPerson</t>
+          <t>deviceSerialNumber</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
@@ -30438,7 +30470,7 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.assignedPerson?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.deviceSerialNumber?</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -30457,12 +30489,12 @@
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>orderedPartId</t>
+          <t>partCode</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
@@ -30478,7 +30510,7 @@
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderedPartId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.partCode?</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr">
@@ -30497,12 +30529,12 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>actualPartId</t>
+          <t>cost</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
@@ -30518,7 +30550,7 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.actualPartId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.cost?</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
@@ -30537,12 +30569,12 @@
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>currencyCode</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
@@ -30558,7 +30590,7 @@
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.resolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.currencyCode?</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr">
@@ -30577,12 +30609,12 @@
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>serialNumber</t>
+          <t>averageCost</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
@@ -30598,7 +30630,7 @@
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.serialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.averageCost?</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
@@ -30617,12 +30649,12 @@
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>quantityUsed</t>
+          <t>partCode</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
@@ -30638,7 +30670,7 @@
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.quantityUsed?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr">
@@ -30657,12 +30689,12 @@
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>relCompanyId</t>
+          <t>modelCode</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
@@ -30678,7 +30710,7 @@
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.relCompanyId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
@@ -30697,12 +30729,12 @@
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>partsUsedDateTime</t>
+          <t>modelDescription</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
@@ -30718,7 +30750,7 @@
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsUsedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr">
@@ -30737,12 +30769,12 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>deviceSerialNumber</t>
+          <t>inventoryTransferImoId</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
@@ -30758,7 +30790,7 @@
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.deviceSerialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.inventoryTransferImoId?</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -30777,12 +30809,12 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>createdDateTime</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
@@ -30798,7 +30830,7 @@
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.createdDateTime?</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr">
@@ -30817,12 +30849,12 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>completedDateTime</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
@@ -30838,7 +30870,7 @@
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.cost?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.completedDateTime?</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -30857,12 +30889,12 @@
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>currencyCode</t>
+          <t>fromWarehouseId</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
@@ -30878,7 +30910,7 @@
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.currencyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.fromWarehouseId?</t>
         </is>
       </c>
       <c r="G206" s="4" t="inlineStr">
@@ -30897,12 +30929,12 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>averageCost</t>
+          <t>toWarehouseId</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
@@ -30918,7 +30950,7 @@
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.averageCost?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.toWarehouseId?</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -30937,12 +30969,12 @@
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>demandStatus</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
@@ -30958,7 +30990,7 @@
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.demandStatus?</t>
         </is>
       </c>
       <c r="G208" s="4" t="inlineStr">
@@ -30977,12 +31009,12 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>modelCode</t>
+          <t>orderStatusIsClosed</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
@@ -30998,7 +31030,7 @@
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.orderStatusIsClosed?</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr">
@@ -31017,12 +31049,12 @@
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>modelDescription</t>
+          <t>movementType</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
@@ -31038,7 +31070,7 @@
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
         </is>
       </c>
       <c r="G210" s="4" t="inlineStr">
@@ -31057,7 +31089,7 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>inventoryTransferImoId</t>
+          <t>addressId</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
@@ -31078,7 +31110,7 @@
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.inventoryTransferImoId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
         </is>
       </c>
       <c r="G211" s="4" t="inlineStr">
@@ -31097,7 +31129,7 @@
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>createdDateTime</t>
+          <t>isResolved</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
@@ -31118,7 +31150,7 @@
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.createdDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.isResolved?</t>
         </is>
       </c>
       <c r="G212" s="4" t="inlineStr">
@@ -31137,7 +31169,7 @@
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>completedDateTime</t>
+          <t>partNumber</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
@@ -31158,7 +31190,7 @@
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.completedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.partNumber?</t>
         </is>
       </c>
       <c r="G213" s="4" t="inlineStr">
@@ -31177,7 +31209,7 @@
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>fromWarehouseId</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
@@ -31198,7 +31230,7 @@
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.fromWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.quantity?</t>
         </is>
       </c>
       <c r="G214" s="4" t="inlineStr">
@@ -31217,7 +31249,7 @@
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>toWarehouseId</t>
+          <t>shipListCode</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
@@ -31238,7 +31270,7 @@
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.toWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
         </is>
       </c>
       <c r="G215" s="4" t="inlineStr">
@@ -31255,54 +31287,54 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="4" t="inlineStr">
+      <c r="A216" s="3" t="inlineStr">
         <is>
           <t>demandStatus</t>
         </is>
       </c>
-      <c r="B216" s="4" t="inlineStr">
-        <is>
-          <t>InventoryTransfers</t>
-        </is>
-      </c>
-      <c r="C216" s="4" t="inlineStr">
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>PurchaseOrders</t>
+        </is>
+      </c>
+      <c r="C216" s="3" t="inlineStr">
         <is>
           <t>Planning V2 template</t>
         </is>
       </c>
-      <c r="D216" s="4" t="inlineStr"/>
-      <c r="E216" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F216" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.demandStatus?</t>
-        </is>
-      </c>
-      <c r="G216" s="4" t="inlineStr">
+      <c r="D216" s="3" t="inlineStr"/>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="F216" s="3" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
+        </is>
+      </c>
+      <c r="G216" s="3" t="inlineStr">
         <is>
           <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
         </is>
       </c>
-      <c r="H216" s="4" t="inlineStr"/>
-      <c r="I216" s="4" t="inlineStr"/>
-      <c r="J216" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="H216" s="3" t="inlineStr"/>
+      <c r="I216" s="3" t="inlineStr"/>
+      <c r="J216" s="3" t="inlineStr">
+        <is>
+          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.DocNum and part/SPL Master evidence also matches; current export needs reconciliation.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>orderStatusIsClosed</t>
+          <t>partTypeCode</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
@@ -31318,7 +31350,7 @@
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.orderStatusIsClosed?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeCode?</t>
         </is>
       </c>
       <c r="G217" s="4" t="inlineStr">
@@ -31337,12 +31369,12 @@
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>movementType</t>
+          <t>description</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
@@ -31358,7 +31390,7 @@
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.description?</t>
         </is>
       </c>
       <c r="G218" s="4" t="inlineStr">
@@ -31377,12 +31409,12 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>addressId</t>
+          <t>partNumber</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
@@ -31398,7 +31430,7 @@
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
         </is>
       </c>
       <c r="G219" s="4" t="inlineStr">
@@ -31417,12 +31449,12 @@
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>isResolved</t>
+          <t>unitOfMeasure</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
@@ -31438,7 +31470,7 @@
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.isResolved?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
         </is>
       </c>
       <c r="G220" s="4" t="inlineStr">
@@ -31457,12 +31489,12 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>partNumber</t>
+          <t>yield</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
@@ -31478,7 +31510,7 @@
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.partNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
         </is>
       </c>
       <c r="G221" s="4" t="inlineStr">
@@ -31497,12 +31529,12 @@
     <row r="222">
       <c r="A222" s="4" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>warehouseId</t>
         </is>
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr">
@@ -31518,7 +31550,7 @@
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.quantity?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.warehouseId?</t>
         </is>
       </c>
       <c r="G222" s="4" t="inlineStr">
@@ -31537,12 +31569,12 @@
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>shipListCode</t>
+          <t>exclusionType</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
@@ -31558,7 +31590,7 @@
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusionType?</t>
         </is>
       </c>
       <c r="G223" s="4" t="inlineStr">
@@ -31575,367 +31607,47 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="3" t="inlineStr">
-        <is>
-          <t>demandStatus</t>
-        </is>
-      </c>
-      <c r="B224" s="3" t="inlineStr">
-        <is>
-          <t>PurchaseOrders</t>
-        </is>
-      </c>
-      <c r="C224" s="3" t="inlineStr">
+      <c r="A224" s="4" t="inlineStr">
+        <is>
+          <t>exclusion</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t>WarehouseExclusions</t>
+        </is>
+      </c>
+      <c r="C224" s="4" t="inlineStr">
         <is>
           <t>Planning V2 template</t>
         </is>
       </c>
-      <c r="D224" s="3" t="inlineStr"/>
-      <c r="E224" s="3" t="inlineStr">
-        <is>
-          <t>Review required</t>
-        </is>
-      </c>
-      <c r="F224" s="3" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
-        </is>
-      </c>
-      <c r="G224" s="3" t="inlineStr">
+      <c r="D224" s="4" t="inlineStr"/>
+      <c r="E224" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F224" s="4" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusion?</t>
+        </is>
+      </c>
+      <c r="G224" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
         </is>
       </c>
-      <c r="H224" s="3" t="inlineStr"/>
-      <c r="I224" s="3" t="inlineStr"/>
-      <c r="J224" s="3" t="inlineStr">
-        <is>
-          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.DocNum and part/SPL Master evidence also matches; current export needs reconciliation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="4" t="inlineStr">
-        <is>
-          <t>partTypeCode</t>
-        </is>
-      </c>
-      <c r="B225" s="4" t="inlineStr">
-        <is>
-          <t>PartTypes</t>
-        </is>
-      </c>
-      <c r="C225" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D225" s="4" t="inlineStr"/>
-      <c r="E225" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F225" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeCode?</t>
-        </is>
-      </c>
-      <c r="G225" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H225" s="4" t="inlineStr"/>
-      <c r="I225" s="4" t="inlineStr"/>
-      <c r="J225" s="4" t="inlineStr">
+      <c r="H224" s="4" t="inlineStr"/>
+      <c r="I224" s="4" t="inlineStr"/>
+      <c r="J224" s="4" t="inlineStr">
         <is>
           <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="4" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="B226" s="4" t="inlineStr">
-        <is>
-          <t>PartTypes</t>
-        </is>
-      </c>
-      <c r="C226" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D226" s="4" t="inlineStr"/>
-      <c r="E226" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F226" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.description?</t>
-        </is>
-      </c>
-      <c r="G226" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H226" s="4" t="inlineStr"/>
-      <c r="I226" s="4" t="inlineStr"/>
-      <c r="J226" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="4" t="inlineStr">
-        <is>
-          <t>partNumber</t>
-        </is>
-      </c>
-      <c r="B227" s="4" t="inlineStr">
-        <is>
-          <t>Yields</t>
-        </is>
-      </c>
-      <c r="C227" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D227" s="4" t="inlineStr"/>
-      <c r="E227" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F227" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
-        </is>
-      </c>
-      <c r="G227" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H227" s="4" t="inlineStr"/>
-      <c r="I227" s="4" t="inlineStr"/>
-      <c r="J227" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="4" t="inlineStr">
-        <is>
-          <t>unitOfMeasure</t>
-        </is>
-      </c>
-      <c r="B228" s="4" t="inlineStr">
-        <is>
-          <t>Yields</t>
-        </is>
-      </c>
-      <c r="C228" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D228" s="4" t="inlineStr"/>
-      <c r="E228" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F228" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
-        </is>
-      </c>
-      <c r="G228" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H228" s="4" t="inlineStr"/>
-      <c r="I228" s="4" t="inlineStr"/>
-      <c r="J228" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="4" t="inlineStr">
-        <is>
-          <t>yield</t>
-        </is>
-      </c>
-      <c r="B229" s="4" t="inlineStr">
-        <is>
-          <t>Yields</t>
-        </is>
-      </c>
-      <c r="C229" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D229" s="4" t="inlineStr"/>
-      <c r="E229" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F229" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
-        </is>
-      </c>
-      <c r="G229" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H229" s="4" t="inlineStr"/>
-      <c r="I229" s="4" t="inlineStr"/>
-      <c r="J229" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="4" t="inlineStr">
-        <is>
-          <t>warehouseId</t>
-        </is>
-      </c>
-      <c r="B230" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C230" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D230" s="4" t="inlineStr"/>
-      <c r="E230" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F230" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.warehouseId?</t>
-        </is>
-      </c>
-      <c r="G230" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H230" s="4" t="inlineStr"/>
-      <c r="I230" s="4" t="inlineStr"/>
-      <c r="J230" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="4" t="inlineStr">
-        <is>
-          <t>exclusionType</t>
-        </is>
-      </c>
-      <c r="B231" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C231" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D231" s="4" t="inlineStr"/>
-      <c r="E231" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F231" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusionType?</t>
-        </is>
-      </c>
-      <c r="G231" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H231" s="4" t="inlineStr"/>
-      <c r="I231" s="4" t="inlineStr"/>
-      <c r="J231" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="4" t="inlineStr">
-        <is>
-          <t>exclusion</t>
-        </is>
-      </c>
-      <c r="B232" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C232" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D232" s="4" t="inlineStr"/>
-      <c r="E232" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F232" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusion?</t>
-        </is>
-      </c>
-      <c r="G232" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H232" s="4" t="inlineStr"/>
-      <c r="I232" s="4" t="inlineStr"/>
-      <c r="J232" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J232"/>
+  <autoFilter ref="A1:J224"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -32468,31 +32180,27 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Warehouses</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Warehouses.csv</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>warehouseId, addressId, returnWarehouseId, supplyWarehouseId, warehouseTypeId, warehouseDescription, isReplenishable, isBranchStockable, isRemote, warehouseStatusId</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>addressId; returnWarehouseId; supplyWarehouseId; warehouseTypeId; isReplenishable; isBranchStockable; isRemote; warehouseStatusId</t>
-        </is>
-      </c>
+      <c r="E21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">

--- a/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
+++ b/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Target Fields'!$A$1:$S$151</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Template Fields'!$A$1:$H$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Template Fields'!$A$1:$H$177</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Evidence'!$A$1:$D$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$J$224</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Output Objects'!$A$1:$E$34</definedName>
@@ -214,8 +214,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TemplateFields" displayName="TemplateFields" ref="A1:H180" headerRowCount="1">
-  <autoFilter ref="A1:H180"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TemplateFields" displayName="TemplateFields" ref="A1:H177" headerRowCount="1">
+  <autoFilter ref="A1:H177"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Template Object"/>
     <tableColumn id="2" name="Field"/>
@@ -14855,12 +14855,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H180"/>
+  <dimension ref="A1:H177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
     <col width="33" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
@@ -14928,7 +14928,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>External (Client-facing) Id</t>
+          <t>Canonical header from Nodes.xlsx</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>External (Client-facing) Id</t>
+          <t>Canonical header from Nodes.xlsx</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -15002,7 +15002,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Nodes.xlsx</t>
+        </is>
+      </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -15034,7 +15038,7 @@
       <c r="C5" s="4" t="inlineStr"/>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>External (Client-facing) Id</t>
+          <t>Canonical header from Customers.xlsx</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -15062,18 +15066,18 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>customerGroupId</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>enum&lt;String&gt;</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr"/>
+          <t>customerName</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Customers.xlsx</t>
+        </is>
+      </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Investigate source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr"/>
@@ -15084,7 +15088,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User has no confirmed source yet for customer grouping.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
@@ -15096,15 +15100,19 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>customerGroupId</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr"/>
+          <t>enum&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Customers.xlsx</t>
+        </is>
+      </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Investigate source</t>
@@ -15118,7 +15126,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Left blank. SAP BusinessPartners can supply names, but the correct Planning V2 customer scope is not confirmed.</t>
+          <t>Left blank. User has no confirmed source yet for customer grouping.</t>
         </is>
       </c>
     </row>
@@ -15138,7 +15146,11 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Customers.xlsx</t>
+        </is>
+      </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Investigate source</t>
@@ -15172,7 +15184,11 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Customers.xlsx</t>
+        </is>
+      </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Investigate source</t>
@@ -15206,7 +15222,11 @@
           <t>Number</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Customers.xlsx</t>
+        </is>
+      </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
           <t>Investigate source</t>
@@ -15240,7 +15260,11 @@
           <t>Number</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Customers.xlsx</t>
+        </is>
+      </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Investigate source</t>
@@ -15274,7 +15298,11 @@
           <t>Number</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Customers.xlsx</t>
+        </is>
+      </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Investigate source</t>
@@ -15308,7 +15336,11 @@
           <t>Number</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Customers.xlsx</t>
+        </is>
+      </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Investigate source</t>
@@ -15340,7 +15372,7 @@
       <c r="C14" s="4" t="inlineStr"/>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>External (Client-facing) Id</t>
+          <t>Canonical header from Vendors.xlsx</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -15368,11 +15400,15 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>vendorName</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Vendors.xlsx</t>
+        </is>
+      </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -15406,7 +15442,11 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr"/>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Vendors.xlsx</t>
+        </is>
+      </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -15440,7 +15480,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from Parts.xlsx</t>
+        </is>
+      </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -15478,7 +15522,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from Parts.xlsx</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -15516,7 +15564,11 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from Parts.xlsx</t>
+        </is>
+      </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -15554,7 +15606,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from Parts.xlsx</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -15592,7 +15648,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from Parts.xlsx</t>
+        </is>
+      </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -15622,7 +15682,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>isBranchStockable</t>
+          <t>isBootStockable</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -15632,7 +15692,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>NOTE: Will vary from customer to customer</t>
+          <t>Canonical header from Parts.xlsx</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -15660,7 +15720,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>isBootStockable</t>
+          <t>isBranchStockable</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -15670,7 +15730,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>NOTE: Will vary from customer to customer</t>
+          <t>Canonical header from Parts.xlsx</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -15706,7 +15766,11 @@
           <t>Enum&lt;String&gt;</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr"/>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Parts.xlsx</t>
+        </is>
+      </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Not available in checked source</t>
@@ -15740,7 +15804,11 @@
           <t>Enum&lt;String&gt;</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Parts.xlsx</t>
+        </is>
+      </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Not available in checked source</t>
@@ -15774,7 +15842,11 @@
           <t>Enum&lt;String&gt;</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr"/>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Parts.xlsx</t>
+        </is>
+      </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -15808,7 +15880,11 @@
           <t>Enum&lt;String&gt;</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr"/>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Parts.xlsx</t>
+        </is>
+      </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Not available in checked source</t>
@@ -15842,7 +15918,11 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Parts.xlsx</t>
+        </is>
+      </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -15876,7 +15956,11 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr"/>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Parts.xlsx</t>
+        </is>
+      </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -15910,7 +15994,11 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr"/>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Canonical header from Parts.xlsx</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Out of v1 scope</t>
@@ -15940,7 +16028,11 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr"/>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Canonical header from Parts.xlsx</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
           <t>Out of v1 scope</t>
@@ -15970,7 +16062,11 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Parts.xlsx</t>
+        </is>
+      </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -16004,7 +16100,11 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr"/>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Canonical header from Parts.xlsx</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
           <t>Out of v1 scope</t>
@@ -16036,7 +16136,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>NOTE: Will vary from customer to customer</t>
+          <t>Canonical header from Parts.xlsx</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -16074,7 +16174,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>NOTE: Will vary from customer to customer</t>
+          <t>Canonical header from Parts.xlsx</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -16110,7 +16210,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Addresses.xlsx</t>
+        </is>
+      </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -16144,7 +16248,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Addresses.xlsx</t>
+        </is>
+      </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -16170,15 +16278,15 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>addressLine1</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr"/>
+          <t>6,0</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr"/>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Addresses.xlsx</t>
+        </is>
+      </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -16212,7 +16320,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Addresses.xlsx</t>
+        </is>
+      </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -16246,7 +16358,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Addresses.xlsx</t>
+        </is>
+      </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -16280,7 +16396,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr"/>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Addresses.xlsx</t>
+        </is>
+      </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -16314,7 +16434,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr"/>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Addresses.xlsx</t>
+        </is>
+      </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -16348,7 +16472,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Addresses.xlsx</t>
+        </is>
+      </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -16382,7 +16510,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr"/>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Addresses.xlsx</t>
+        </is>
+      </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -16416,7 +16548,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr"/>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Addresses.xlsx</t>
+        </is>
+      </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -16450,7 +16586,11 @@
           <t>Enum&lt;String&gt;</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr"/>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Addresses.xlsx</t>
+        </is>
+      </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -16484,7 +16624,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr"/>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Addresses.xlsx</t>
+        </is>
+      </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -16520,7 +16664,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>External (Client-facing) Id (Warehouse Code)</t>
+          <t>Canonical header from Warehouses.xlsx</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -16562,7 +16706,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>External (Client-facing) Id</t>
+          <t>Canonical header from Warehouses.xlsx</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -16604,7 +16748,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>External (Client-facing) Id</t>
+          <t>Canonical header from Warehouses.xlsx</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -16638,7 +16782,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>External (Client-facing) Id</t>
+          <t>Canonical header from Warehouses.xlsx</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -16680,7 +16824,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>External (Client-facing) Id</t>
+          <t>Canonical header from Warehouses.xlsx</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -16722,7 +16866,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>[BOOT,DEP,REPAIR]</t>
+          <t>Canonical header from Warehouses.xlsx</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -16762,7 +16906,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from Warehouses.xlsx</t>
+        </is>
+      </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -16800,7 +16948,11 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr"/>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Canonical header from Warehouses.xlsx</t>
+        </is>
+      </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
           <t>Out of v1 scope</t>
@@ -16830,7 +16982,11 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from Warehouses.xlsx</t>
+        </is>
+      </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -16868,7 +17024,11 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr"/>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Canonical header from Warehouses.xlsx</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
           <t>Out of v1 scope</t>
@@ -16898,7 +17058,11 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from Warehouses.xlsx</t>
+        </is>
+      </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -16936,7 +17100,11 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr"/>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from Warehouses.xlsx</t>
+        </is>
+      </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -16976,7 +17144,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Confirm. May not be required</t>
+          <t>Canonical header from Warehouses.xlsx</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -17008,15 +17176,15 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>partCode</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr"/>
+          <t>partNumber</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr"/>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from Warehouse Stock on Hand.xlsx</t>
+        </is>
+      </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -17054,7 +17222,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from Warehouse Stock on Hand.xlsx</t>
+        </is>
+      </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -17092,7 +17264,11 @@
           <t>Enum&lt;String&gt;</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr"/>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Canonical header from Warehouse Stock on Hand.xlsx</t>
+        </is>
+      </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
           <t>Out of v1 scope</t>
@@ -17122,7 +17298,11 @@
           <t>Double</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from Warehouse Stock on Hand.xlsx</t>
+        </is>
+      </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -17160,7 +17340,11 @@
           <t>Double</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr"/>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from Warehouse Stock on Hand.xlsx</t>
+        </is>
+      </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -17198,7 +17382,11 @@
           <t>Double</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from Warehouse Stock on Hand.xlsx</t>
+        </is>
+      </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -17236,7 +17424,11 @@
           <t>Double</t>
         </is>
       </c>
-      <c r="D67" s="5" t="inlineStr"/>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Canonical header from Warehouse Stock on Hand.xlsx</t>
+        </is>
+      </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
           <t>Out of v1 scope</t>
@@ -17266,7 +17458,11 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr"/>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from Warehouse Stock on Hand.xlsx</t>
+        </is>
+      </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -17304,7 +17500,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr"/>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Employees.xlsx</t>
+        </is>
+      </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -17338,7 +17538,11 @@
           <t>enum&lt;String&gt;</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr"/>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Employees.xlsx</t>
+        </is>
+      </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -17374,7 +17578,7 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>External (Client-facing) Id</t>
+          <t>Canonical header from Employees.xlsx</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -17408,7 +17612,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>External (Client-facing) Id</t>
+          <t>Canonical header from Employees.xlsx</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -17446,7 +17650,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>External (Client-facing) Id</t>
+          <t>Canonical header from Employees.xlsx</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -17482,7 +17686,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr"/>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Employees.xlsx</t>
+        </is>
+      </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -17516,7 +17724,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr"/>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Employees.xlsx</t>
+        </is>
+      </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -17550,7 +17762,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr"/>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Employees.xlsx</t>
+        </is>
+      </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -17584,7 +17800,11 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr"/>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Employees.xlsx</t>
+        </is>
+      </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -17618,7 +17838,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr"/>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Employees.xlsx</t>
+        </is>
+      </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -17637,104 +17861,112 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>Employees</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>whs id</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr"/>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Employees.xlsx</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr"/>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>orderNumber</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr"/>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from PartsUsage.xlsx</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Stock Audit Report 3Y:Document for DN rows</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B80" s="5" t="inlineStr">
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>requestId</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D80" s="5" t="inlineStr"/>
-      <c r="E80" s="5" t="inlineStr">
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Canonical header from PartsUsage.xlsx</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
         <is>
           <t>Out of v1 scope</t>
         </is>
       </c>
-      <c r="F80" s="5" t="inlineStr"/>
-      <c r="G80" s="5" t="inlineStr"/>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="F81" s="5" t="inlineStr"/>
+      <c r="G81" s="5" t="inlineStr"/>
+      <c r="H81" s="5" t="inlineStr">
         <is>
           <t>parts_usage.Request_ID is marked CC8 relevant = No.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="4" t="inlineStr">
-        <is>
-          <t>PartsUsage</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>customerCompanyCode</t>
-        </is>
-      </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr"/>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="inlineStr"/>
-      <c r="G81" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
@@ -17746,15 +17978,15 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>orderType</t>
-        </is>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>Enum&lt;String&gt;</t>
-        </is>
-      </c>
-      <c r="D82" s="4" t="inlineStr"/>
+          <t>OrderType</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr"/>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from PartsUsage.xlsx</t>
+        </is>
+      </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -17780,7 +18012,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>orderStatus</t>
+          <t>customerCompanyCode</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -17788,7 +18020,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr"/>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from PartsUsage.xlsx</t>
+        </is>
+      </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -17822,7 +18058,11 @@
           <t>DateTime</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr"/>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from PartsUsage.xlsx</t>
+        </is>
+      </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -17848,15 +18088,19 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>requestTicketDateTime</t>
+          <t>orderStatus</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>DateTime</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="inlineStr"/>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from PartsUsage.xlsx</t>
+        </is>
+      </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -17882,15 +18126,19 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>siteCompanyCode</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D86" s="4" t="inlineStr"/>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from PartsUsage.xlsx</t>
+        </is>
+      </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -17924,7 +18172,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr"/>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from PartsUsage.xlsx</t>
+        </is>
+      </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -17947,74 +18199,82 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="A88" s="4" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>serialNumber</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr"/>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from PartsUsage.xlsx</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr"/>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>PartsUsage</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>quantityUsed</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Float</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from PartsUsage.xlsx</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>Stock Audit Report 3Y:Whse</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Stock Audit Report 3Y:absolute Quantity for negative DN rows</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>PartsUsage</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>assignedPersonCode</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="inlineStr"/>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr"/>
-      <c r="G89" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H89" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
@@ -18026,15 +18286,19 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>relCompanyId</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>DateTime</t>
-        </is>
-      </c>
-      <c r="D90" s="4" t="inlineStr"/>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from PartsUsage.xlsx</t>
+        </is>
+      </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -18053,36 +18317,44 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="inlineStr">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>serialNumber</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="inlineStr"/>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr"/>
-      <c r="G91" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H91" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>partsUsedDateTime</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from PartsUsage.xlsx</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Stock Audit Report 3Y:Posting Date</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -18094,15 +18366,19 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>quantityUsed</t>
+          <t>Warehouse</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Float</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr"/>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from PartsUsage.xlsx</t>
+        </is>
+      </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -18110,7 +18386,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report 3Y:absolute Quantity for negative DN rows</t>
+          <t>Stock Audit Report 3Y:Whse</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -18132,7 +18408,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>relCompanyId</t>
+          <t>assignedPersonCode</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -18140,7 +18416,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D93" s="4" t="inlineStr"/>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from PartsUsage.xlsx</t>
+        </is>
+      </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -18159,74 +18439,78 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>partsUsedDateTime</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>DateTime</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr"/>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>deviceSerialNumber</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from PartsUsage.xlsx</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr"/>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>PartsUsage</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr"/>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from PartsUsage.xlsx</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>Stock Audit Report 3Y:Posting Date</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Reference masters.csv:SPL Master by used part</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>PartsUsage</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>deviceSerialNumber</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="inlineStr"/>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr"/>
-      <c r="G95" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H95" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
@@ -18246,7 +18530,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D96" s="4" t="inlineStr"/>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from ServiceOrder.xlsx</t>
+        </is>
+      </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -18272,15 +18560,15 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D97" s="4" t="inlineStr"/>
+          <t>RequestID</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr"/>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from ServiceOrder.xlsx</t>
+        </is>
+      </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -18306,15 +18594,19 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>eta</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>DateTime</t>
-        </is>
-      </c>
-      <c r="D98" s="4" t="inlineStr"/>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from ServiceOrder.xlsx</t>
+        </is>
+      </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -18340,7 +18632,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>actualEta</t>
+          <t>eta</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -18348,7 +18640,11 @@
           <t>DateTime</t>
         </is>
       </c>
-      <c r="D99" s="4" t="inlineStr"/>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from ServiceOrder.xlsx</t>
+        </is>
+      </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -18374,7 +18670,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>actualResolveDateTime</t>
+          <t>actualEta</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -18382,7 +18678,11 @@
           <t>DateTime</t>
         </is>
       </c>
-      <c r="D100" s="4" t="inlineStr"/>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from ServiceOrder.xlsx</t>
+        </is>
+      </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -18408,7 +18708,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>recallDateTime</t>
+          <t>actualResolveDateTime</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -18416,7 +18716,11 @@
           <t>DateTime</t>
         </is>
       </c>
-      <c r="D101" s="4" t="inlineStr"/>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from ServiceOrder.xlsx</t>
+        </is>
+      </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -18442,7 +18746,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>actualRecallDateTime</t>
+          <t>recallDateTime</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -18450,7 +18754,11 @@
           <t>DateTime</t>
         </is>
       </c>
-      <c r="D102" s="4" t="inlineStr"/>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from ServiceOrder.xlsx</t>
+        </is>
+      </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -18476,15 +18784,19 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>slaEtaClock</t>
+          <t>actualRecallDateTime</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D103" s="4" t="inlineStr"/>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from ServiceOrder.xlsx</t>
+        </is>
+      </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -18510,7 +18822,7 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>slaResolveClock</t>
+          <t>slaEtaClock</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -18518,7 +18830,11 @@
           <t>Double</t>
         </is>
       </c>
-      <c r="D104" s="4" t="inlineStr"/>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from ServiceOrder.xlsx</t>
+        </is>
+      </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -18544,15 +18860,19 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>slaFailureCode</t>
+          <t>slaResolveClock</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="inlineStr"/>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from ServiceOrder.xlsx</t>
+        </is>
+      </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -18578,15 +18898,19 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>slaEtaHit</t>
+          <t>slaFailureCode</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="D106" s="4" t="inlineStr"/>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from ServiceOrder.xlsx</t>
+        </is>
+      </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -18612,15 +18936,19 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>slaResolvedDateTime</t>
+          <t>slaEtaHit</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>DateTime</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="inlineStr"/>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from ServiceOrder.xlsx</t>
+        </is>
+      </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -18641,20 +18969,20 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
-        </is>
-      </c>
-      <c r="C108" s="4" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D108" s="4" t="inlineStr"/>
+          <t>slaResolveDateTime</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr"/>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from ServiceOrder.xlsx</t>
+        </is>
+      </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -18680,7 +19008,7 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>requestId</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -18688,7 +19016,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D109" s="4" t="inlineStr"/>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from RepairOrders.xlsx</t>
+        </is>
+      </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -18714,7 +19046,7 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>customerCompanyCode</t>
+          <t>requestId</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -18722,7 +19054,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D110" s="4" t="inlineStr"/>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from RepairOrders.xlsx</t>
+        </is>
+      </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -18748,7 +19084,7 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>orderStatus</t>
+          <t>customerCompanyCode</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -18756,7 +19092,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D111" s="4" t="inlineStr"/>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from RepairOrders.xlsx</t>
+        </is>
+      </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -18782,15 +19122,19 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>orderStartDatetime</t>
+          <t>orderStatus</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>DateTime</t>
-        </is>
-      </c>
-      <c r="D112" s="4" t="inlineStr"/>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from RepairOrders.xlsx</t>
+        </is>
+      </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -18816,15 +19160,19 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>siteCompanyCode</t>
+          <t>orderStartDatetime</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D113" s="4" t="inlineStr"/>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from RepairOrders.xlsx</t>
+        </is>
+      </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -18850,7 +19198,7 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>repairType</t>
+          <t>siteCompanyCode</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -18858,7 +19206,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D114" s="4" t="inlineStr"/>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from RepairOrders.xlsx</t>
+        </is>
+      </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -18884,15 +19236,19 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>partsOrderDateTime</t>
+          <t>repairType</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>DateTime</t>
-        </is>
-      </c>
-      <c r="D115" s="4" t="inlineStr"/>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from RepairOrders.xlsx</t>
+        </is>
+      </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -18918,7 +19274,7 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>partsReceivedDateTime</t>
+          <t>partsOrderDateTime</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -18926,7 +19282,11 @@
           <t>DateTime</t>
         </is>
       </c>
-      <c r="D116" s="4" t="inlineStr"/>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from RepairOrders.xlsx</t>
+        </is>
+      </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -18952,15 +19312,19 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>repairCode</t>
+          <t>partsReceivedDateTime</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D117" s="4" t="inlineStr"/>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from RepairOrders.xlsx</t>
+        </is>
+      </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -18986,7 +19350,7 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>repairCompany</t>
+          <t>repairCode</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
@@ -18994,7 +19358,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D118" s="4" t="inlineStr"/>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from RepairOrders.xlsx</t>
+        </is>
+      </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -19020,7 +19388,7 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>raStatus</t>
+          <t>repairCompany</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -19028,7 +19396,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D119" s="4" t="inlineStr"/>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from RepairOrders.xlsx</t>
+        </is>
+      </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -19054,7 +19426,7 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>raStatus</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
@@ -19062,7 +19434,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D120" s="4" t="inlineStr"/>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from RepairOrders.xlsx</t>
+        </is>
+      </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -19088,7 +19464,7 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>assignedPerson</t>
+          <t>Warehouse</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -19096,7 +19472,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D121" s="4" t="inlineStr"/>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from RepairOrders.xlsx</t>
+        </is>
+      </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -19122,7 +19502,7 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>orderedPartId</t>
+          <t>assignedPerson</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -19130,7 +19510,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D122" s="4" t="inlineStr"/>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from RepairOrders.xlsx</t>
+        </is>
+      </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -19156,15 +19540,19 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>actualPartId</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D123" s="4" t="inlineStr"/>
+          <t>DateTime</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from RepairOrders.xlsx</t>
+        </is>
+      </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -19190,15 +19578,19 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>serialNumber</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>DateTime</t>
-        </is>
-      </c>
-      <c r="D124" s="4" t="inlineStr"/>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from RepairOrders.xlsx</t>
+        </is>
+      </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -19224,15 +19616,19 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>serialNumber</t>
+          <t>quantityUsed</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D125" s="4" t="inlineStr"/>
+          <t>Float</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from RepairOrders.xlsx</t>
+        </is>
+      </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -19258,15 +19654,19 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>quantityUsed</t>
+          <t>deviceSerialNumber</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Float</t>
-        </is>
-      </c>
-      <c r="D126" s="4" t="inlineStr"/>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from RepairOrders.xlsx</t>
+        </is>
+      </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -19292,7 +19692,7 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>relCompanyId</t>
+          <t>orderedPartId</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -19300,7 +19700,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D127" s="4" t="inlineStr"/>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from RepairOrders.xlsx</t>
+        </is>
+      </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -19326,15 +19730,19 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>partsUsedDateTime</t>
+          <t>actualPartId</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>DateTime</t>
-        </is>
-      </c>
-      <c r="D128" s="4" t="inlineStr"/>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from RepairOrders.xlsx</t>
+        </is>
+      </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -19355,12 +19763,12 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>deviceSerialNumber</t>
+          <t>partCode</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -19368,7 +19776,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D129" s="4" t="inlineStr"/>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from PartCosts.xlsx</t>
+        </is>
+      </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -19394,15 +19806,19 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>cost</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D130" s="4" t="inlineStr"/>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from PartCosts.xlsx</t>
+        </is>
+      </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -19428,15 +19844,19 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>currencyCode</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D131" s="4" t="inlineStr"/>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from PartCosts.xlsx</t>
+        </is>
+      </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -19462,15 +19882,19 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>currencyCode</t>
+          <t>averageCost</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D132" s="4" t="inlineStr"/>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from PartCosts.xlsx</t>
+        </is>
+      </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -19489,66 +19913,74 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="4" t="inlineStr">
+      <c r="A133" s="5" t="inlineStr">
         <is>
           <t>PartCost</t>
         </is>
       </c>
-      <c r="B133" s="4" t="inlineStr">
-        <is>
-          <t>averageCost</t>
-        </is>
-      </c>
-      <c r="C133" s="4" t="inlineStr">
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>averageRepairCost</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="D133" s="4" t="inlineStr"/>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F133" s="4" t="inlineStr"/>
-      <c r="G133" s="4" t="inlineStr">
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>Canonical header from PartCosts.xlsx</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr"/>
+      <c r="G133" s="5" t="inlineStr"/>
+      <c r="H133" s="5" t="inlineStr">
+        <is>
+          <t>bpart_cost.avg_repair_cost is marked CC8 relevant = No.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>Models</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>partCode</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Models.xlsx</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr"/>
+      <c r="G134" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H133" s="4" t="inlineStr">
+      <c r="H134" s="4" t="inlineStr">
         <is>
           <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>PartCost</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="inlineStr">
-        <is>
-          <t>averageRepairCost</t>
-        </is>
-      </c>
-      <c r="C134" s="5" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D134" s="5" t="inlineStr"/>
-      <c r="E134" s="5" t="inlineStr">
-        <is>
-          <t>Out of v1 scope</t>
-        </is>
-      </c>
-      <c r="F134" s="5" t="inlineStr"/>
-      <c r="G134" s="5" t="inlineStr"/>
-      <c r="H134" s="5" t="inlineStr">
-        <is>
-          <t>bpart_cost.avg_repair_cost is marked CC8 relevant = No.</t>
         </is>
       </c>
     </row>
@@ -19560,7 +19992,7 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>modelCode</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -19568,7 +20000,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D135" s="4" t="inlineStr"/>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Models.xlsx</t>
+        </is>
+      </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -19594,7 +20030,7 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>modelCode</t>
+          <t>modelDescription</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -19602,7 +20038,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D136" s="4" t="inlineStr"/>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Models.xlsx</t>
+        </is>
+      </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -19623,12 +20063,12 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>modelDescription</t>
+          <t>inventoryTransferImoId</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -19636,7 +20076,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D137" s="4" t="inlineStr"/>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Inventory Transfers.xlsx</t>
+        </is>
+      </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -19662,15 +20106,19 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>inventoryTransferImoId</t>
+          <t>createdDateTime</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D138" s="4" t="inlineStr"/>
+          <t>Datetime</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Inventory Transfers.xlsx</t>
+        </is>
+      </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -19696,7 +20144,7 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>createdDateTime</t>
+          <t>completedDateTime</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -19704,7 +20152,11 @@
           <t>Datetime</t>
         </is>
       </c>
-      <c r="D139" s="4" t="inlineStr"/>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Inventory Transfers.xlsx</t>
+        </is>
+      </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -19730,15 +20182,19 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>completedDateTime</t>
+          <t>fromWarehouseId</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>Datetime</t>
-        </is>
-      </c>
-      <c r="D140" s="4" t="inlineStr"/>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Inventory Transfers.xlsx</t>
+        </is>
+      </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -19764,7 +20220,7 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>fromWarehouseId</t>
+          <t>toWarehouseId</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -19772,7 +20228,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D141" s="4" t="inlineStr"/>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Inventory Transfers.xlsx</t>
+        </is>
+      </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -19798,15 +20258,19 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>toWarehouseId</t>
+          <t>demandStatus</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D142" s="4" t="inlineStr"/>
+          <t>Enum&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Inventory Transfers.xlsx</t>
+        </is>
+      </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -19832,15 +20296,19 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>demandStatus</t>
+          <t>orderStatusIsClosed</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Enum&lt;String&gt;</t>
-        </is>
-      </c>
-      <c r="D143" s="4" t="inlineStr"/>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Inventory Transfers.xlsx</t>
+        </is>
+      </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -19866,15 +20334,19 @@
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>orderStatusIsClosed</t>
+          <t>movementType</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="D144" s="4" t="inlineStr"/>
+          <t>Enum&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Inventory Transfers.xlsx</t>
+        </is>
+      </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -19893,32 +20365,40 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="5" t="inlineStr">
+      <c r="A145" s="4" t="inlineStr">
         <is>
           <t>InventoryTransfers</t>
         </is>
       </c>
-      <c r="B145" s="5" t="inlineStr">
-        <is>
-          <t>loClass</t>
-        </is>
-      </c>
-      <c r="C145" s="5" t="inlineStr">
-        <is>
-          <t>Enum&lt;String&gt;</t>
-        </is>
-      </c>
-      <c r="D145" s="5" t="inlineStr"/>
-      <c r="E145" s="5" t="inlineStr">
-        <is>
-          <t>Out of v1 scope</t>
-        </is>
-      </c>
-      <c r="F145" s="5" t="inlineStr"/>
-      <c r="G145" s="5" t="inlineStr"/>
-      <c r="H145" s="5" t="inlineStr">
-        <is>
-          <t>imo.LO_Class is marked CC8 relevant = No.</t>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>addressId</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Inventory Transfers.xlsx</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F145" s="4" t="inlineStr"/>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H145" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
@@ -19930,15 +20410,15 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>movementType</t>
-        </is>
-      </c>
-      <c r="C146" s="4" t="inlineStr">
-        <is>
-          <t>Enum&lt;String&gt;</t>
-        </is>
-      </c>
-      <c r="D146" s="4" t="inlineStr"/>
+          <t>Bpart</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr"/>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Inventory Transfers.xlsx</t>
+        </is>
+      </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -19964,15 +20444,19 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>addressId</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D147" s="4" t="inlineStr"/>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Inventory Transfers.xlsx</t>
+        </is>
+      </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -19998,15 +20482,19 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>isResolved</t>
+          <t>shipListCode</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="D148" s="4" t="inlineStr"/>
+          <t>Enum&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Inventory Transfers.xlsx</t>
+        </is>
+      </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP first</t>
@@ -20025,104 +20513,128 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="4" t="inlineStr">
-        <is>
-          <t>InventoryTransfers</t>
-        </is>
-      </c>
-      <c r="B149" s="4" t="inlineStr">
-        <is>
-          <t>partNumber</t>
-        </is>
-      </c>
-      <c r="C149" s="4" t="inlineStr">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>PurchaseOrders</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>purchaseOrderNumber</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D149" s="4" t="inlineStr"/>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr"/>
-      <c r="G149" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H149" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from Purchase Orders.xlsx</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>SAP Service Layer SQLQueries:OPOR.DocNum</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="4" t="inlineStr">
-        <is>
-          <t>InventoryTransfers</t>
-        </is>
-      </c>
-      <c r="B150" s="4" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="C150" s="4" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D150" s="4" t="inlineStr"/>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr"/>
-      <c r="G150" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H150" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>PurchaseOrders</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>purchaseOrderStatus</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Enum&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from Purchase Orders.xlsx</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>SAP Service Layer SQLQueries:OPOR.DocStatus/CANCELED mapped to template status</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="4" t="inlineStr">
-        <is>
-          <t>InventoryTransfers</t>
-        </is>
-      </c>
-      <c r="B151" s="4" t="inlineStr">
-        <is>
-          <t>shipListCode</t>
-        </is>
-      </c>
-      <c r="C151" s="4" t="inlineStr">
-        <is>
-          <t>Enum&lt;String&gt;</t>
-        </is>
-      </c>
-      <c r="D151" s="4" t="inlineStr"/>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F151" s="4" t="inlineStr"/>
-      <c r="G151" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H151" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>PurchaseOrders</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>creationDateTime</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Datetime</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from Purchase Orders.xlsx</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>SAP Service Layer SQLQueries:OPOR.CreateDate</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -20134,15 +20646,19 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>purchaseOrderNumber</t>
+          <t>approvalDateTime</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr"/>
+          <t>Datetime</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from Purchase Orders.xlsx</t>
+        </is>
+      </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -20150,7 +20666,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>SAP Service Layer SQLQueries:OPOR.DocNum</t>
+          <t>SAP Service Layer SQLQueries:OPOR.DocDate</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -20172,15 +20688,19 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>purchaseOrderStatus</t>
+          <t>toWarehouseId</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Enum&lt;String&gt;</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr"/>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from Purchase Orders.xlsx</t>
+        </is>
+      </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -20188,7 +20708,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>SAP Service Layer SQLQueries:OPOR.DocStatus/CANCELED mapped to template status</t>
+          <t>SAP Service Layer SQLQueries:POR1.WhsCode</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -20210,15 +20730,19 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>creationDateTime</t>
+          <t>vendorId</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Datetime</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr"/>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from Purchase Orders.xlsx</t>
+        </is>
+      </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -20226,7 +20750,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>SAP Service Layer SQLQueries:OPOR.CreateDate</t>
+          <t>SAP Service Layer SQLQueries:OPOR.CardCode</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -20241,40 +20765,40 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+      <c r="A155" s="3" t="inlineStr">
         <is>
           <t>PurchaseOrders</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>approvalDateTime</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>Datetime</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr"/>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t>SAP Service Layer SQLQueries:OPOR.DocDate</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>demandStatus</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>Enum&lt;String&gt;</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>Canonical header from Purchase Orders.xlsx</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr"/>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.DocNum and part/SPL Master evidence also matches; current export needs reconciliation.</t>
         </is>
       </c>
     </row>
@@ -20286,7 +20810,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>toWarehouseId</t>
+          <t>partNumber</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -20294,7 +20818,11 @@
           <t>String</t>
         </is>
       </c>
-      <c r="D156" s="2" t="inlineStr"/>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from Purchase Orders.xlsx</t>
+        </is>
+      </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -20302,7 +20830,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>SAP Service Layer SQLQueries:POR1.WhsCode</t>
+          <t>SAP Service Layer SQLQueries:POR1.ItemCode</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -20324,517 +20852,549 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>vendorId</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from Purchase Orders.xlsx</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>SAP Service Layer SQLQueries:POR1.Quantity</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>PurchaseOrders</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>lineCost</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from Purchase Orders.xlsx</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>SAP Service Layer SQLQueries:POR1.LineTotal</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>PurchaseOrders</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>quantityReceived</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from Purchase Orders.xlsx</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>SAP Service Layer SQLQueries:PDN1.Quantity summed by PO line</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>PurchaseOrders</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>receivedDateTime</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Datetime</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Canonical header from Purchase Orders.xlsx</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>SAP Service Layer SQLQueries:OPDN.DocDate max by PO line</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>PartTypes</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>partType</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr"/>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from partTypes.xlsx</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F161" s="4" t="inlineStr"/>
+      <c r="G161" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H161" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>PartTypes</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>partTypeDescription</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr"/>
+      <c r="D162" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from partTypes.xlsx</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F162" s="4" t="inlineStr"/>
+      <c r="G162" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>PartTypes</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>isReworkable</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr"/>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from partTypes.xlsx</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F163" s="4" t="inlineStr"/>
+      <c r="G163" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H163" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>Yields</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>partNumber</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D157" s="2" t="inlineStr"/>
-      <c r="E157" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="F157" s="2" t="inlineStr">
-        <is>
-          <t>SAP Service Layer SQLQueries:OPOR.CardCode</t>
-        </is>
-      </c>
-      <c r="G157" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H157" s="2" t="inlineStr">
-        <is>
-          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="3" t="inlineStr">
-        <is>
-          <t>PurchaseOrders</t>
-        </is>
-      </c>
-      <c r="B158" s="3" t="inlineStr">
-        <is>
-          <t>demandStatus</t>
-        </is>
-      </c>
-      <c r="C158" s="3" t="inlineStr">
+      <c r="D164" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Yields.xlsx</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F164" s="4" t="inlineStr"/>
+      <c r="G164" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>Yields</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>unitOfMeasure</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
         <is>
           <t>Enum&lt;String&gt;</t>
         </is>
       </c>
-      <c r="D158" s="3" t="inlineStr"/>
-      <c r="E158" s="3" t="inlineStr">
-        <is>
-          <t>Review required</t>
-        </is>
-      </c>
-      <c r="F158" s="3" t="inlineStr"/>
-      <c r="G158" s="3" t="inlineStr">
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Yields.xlsx</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F165" s="4" t="inlineStr"/>
+      <c r="G165" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H158" s="3" t="inlineStr">
-        <is>
-          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.DocNum and part/SPL Master evidence also matches; current export needs reconciliation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="5" t="inlineStr">
-        <is>
-          <t>PurchaseOrders</t>
-        </is>
-      </c>
-      <c r="B159" s="5" t="inlineStr">
-        <is>
-          <t>customerId</t>
-        </is>
-      </c>
-      <c r="C159" s="5" t="inlineStr">
+      <c r="H165" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>Yields</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>yield</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>Double</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Yields.xlsx</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="inlineStr"/>
+      <c r="G166" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="inlineStr">
+        <is>
+          <t>ActionGroups</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>actionGroupId</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D159" s="5" t="inlineStr"/>
-      <c r="E159" s="5" t="inlineStr">
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>Canonical header from ActionGroups.xlsx</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="inlineStr">
         <is>
           <t>Out of v1 scope</t>
         </is>
       </c>
-      <c r="F159" s="5" t="inlineStr"/>
-      <c r="G159" s="5" t="inlineStr"/>
-      <c r="H159" s="5" t="inlineStr">
-        <is>
-          <t>No corresponding purchase_orders field is marked needed for CoCre8 in the edited reference workbook.</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="5" t="inlineStr">
-        <is>
-          <t>PurchaseOrders</t>
-        </is>
-      </c>
-      <c r="B160" s="5" t="inlineStr">
-        <is>
-          <t>requestTicketDateTime</t>
-        </is>
-      </c>
-      <c r="C160" s="5" t="inlineStr">
-        <is>
-          <t>Datetime</t>
-        </is>
-      </c>
-      <c r="D160" s="5" t="inlineStr"/>
-      <c r="E160" s="5" t="inlineStr">
+      <c r="F167" s="5" t="inlineStr"/>
+      <c r="G167" s="5" t="inlineStr"/>
+      <c r="H167" s="5" t="inlineStr">
+        <is>
+          <t>actgr.actgr_id is marked CC8 relevant = No.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="inlineStr">
+        <is>
+          <t>ActionGroups</t>
+        </is>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>nodeId</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>Canonical header from ActionGroups.xlsx</t>
+        </is>
+      </c>
+      <c r="E168" s="5" t="inlineStr">
         <is>
           <t>Out of v1 scope</t>
         </is>
       </c>
-      <c r="F160" s="5" t="inlineStr"/>
-      <c r="G160" s="5" t="inlineStr"/>
-      <c r="H160" s="5" t="inlineStr">
-        <is>
-          <t>No corresponding purchase_orders field is marked needed for CoCre8 in the edited reference workbook.</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="5" t="inlineStr">
-        <is>
-          <t>PurchaseOrders</t>
-        </is>
-      </c>
-      <c r="B161" s="5" t="inlineStr">
-        <is>
-          <t>isResolved</t>
-        </is>
-      </c>
-      <c r="C161" s="5" t="inlineStr">
+      <c r="F168" s="5" t="inlineStr"/>
+      <c r="G168" s="5" t="inlineStr"/>
+      <c r="H168" s="5" t="inlineStr">
+        <is>
+          <t>actgr.node_id is marked CC8 relevant = No.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>ActionGroups</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>actionGroupDescription</t>
+        </is>
+      </c>
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
+        <is>
+          <t>Canonical header from ActionGroups.xlsx</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F169" s="5" t="inlineStr"/>
+      <c r="G169" s="5" t="inlineStr"/>
+      <c r="H169" s="5" t="inlineStr">
+        <is>
+          <t>actgr.descr is marked CC8 relevant = No.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="inlineStr">
+        <is>
+          <t>ActionGroups</t>
+        </is>
+      </c>
+      <c r="B170" s="5" t="inlineStr">
+        <is>
+          <t>assignAnySkill</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D161" s="5" t="inlineStr"/>
-      <c r="E161" s="5" t="inlineStr">
+      <c r="D170" s="5" t="inlineStr">
+        <is>
+          <t>Canonical header from ActionGroups.xlsx</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="inlineStr">
         <is>
           <t>Out of v1 scope</t>
         </is>
       </c>
-      <c r="F161" s="5" t="inlineStr"/>
-      <c r="G161" s="5" t="inlineStr"/>
-      <c r="H161" s="5" t="inlineStr">
-        <is>
-          <t>No corresponding purchase_orders field is marked needed for CoCre8 in the edited reference workbook.</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>PurchaseOrders</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>partNumber</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr"/>
-      <c r="E162" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="F162" s="2" t="inlineStr">
-        <is>
-          <t>SAP Service Layer SQLQueries:POR1.ItemCode</t>
-        </is>
-      </c>
-      <c r="G162" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>PurchaseOrders</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr"/>
-      <c r="E163" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="F163" s="2" t="inlineStr">
-        <is>
-          <t>SAP Service Layer SQLQueries:POR1.Quantity</t>
-        </is>
-      </c>
-      <c r="G163" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>PurchaseOrders</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>lineCost</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr"/>
-      <c r="E164" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>SAP Service Layer SQLQueries:POR1.LineTotal</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>PurchaseOrders</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>quantityReceived</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr"/>
-      <c r="E165" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="F165" s="2" t="inlineStr">
-        <is>
-          <t>SAP Service Layer SQLQueries:PDN1.Quantity summed by PO line</t>
-        </is>
-      </c>
-      <c r="G165" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H165" s="2" t="inlineStr">
-        <is>
-          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>PurchaseOrders</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>receivedDateTime</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>Datetime</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr"/>
-      <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="inlineStr">
-        <is>
-          <t>SAP Service Layer SQLQueries:OPDN.DocDate max by PO line</t>
-        </is>
-      </c>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="4" t="inlineStr">
-        <is>
-          <t>PartTypes</t>
-        </is>
-      </c>
-      <c r="B167" s="4" t="inlineStr">
-        <is>
-          <t>partTypeCode</t>
-        </is>
-      </c>
-      <c r="C167" s="4" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D167" s="4" t="inlineStr"/>
-      <c r="E167" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F167" s="4" t="inlineStr"/>
-      <c r="G167" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H167" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="4" t="inlineStr">
-        <is>
-          <t>PartTypes</t>
-        </is>
-      </c>
-      <c r="B168" s="4" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C168" s="4" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D168" s="4" t="inlineStr"/>
-      <c r="E168" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F168" s="4" t="inlineStr"/>
-      <c r="G168" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H168" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="4" t="inlineStr">
-        <is>
-          <t>Yields</t>
-        </is>
-      </c>
-      <c r="B169" s="4" t="inlineStr">
-        <is>
-          <t>partNumber</t>
-        </is>
-      </c>
-      <c r="C169" s="4" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D169" s="4" t="inlineStr"/>
-      <c r="E169" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F169" s="4" t="inlineStr"/>
-      <c r="G169" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H169" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="4" t="inlineStr">
-        <is>
-          <t>Yields</t>
-        </is>
-      </c>
-      <c r="B170" s="4" t="inlineStr">
-        <is>
-          <t>unitOfMeasure</t>
-        </is>
-      </c>
-      <c r="C170" s="4" t="inlineStr">
-        <is>
-          <t>Enum&lt;String&gt;</t>
-        </is>
-      </c>
-      <c r="D170" s="4" t="inlineStr"/>
-      <c r="E170" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F170" s="4" t="inlineStr"/>
-      <c r="G170" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H170" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="F170" s="5" t="inlineStr"/>
+      <c r="G170" s="5" t="inlineStr"/>
+      <c r="H170" s="5" t="inlineStr">
+        <is>
+          <t>Technician action groups are marked CC8 relevant = No.</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="4" t="inlineStr">
-        <is>
-          <t>Yields</t>
-        </is>
-      </c>
-      <c r="B171" s="4" t="inlineStr">
-        <is>
-          <t>yield</t>
-        </is>
-      </c>
-      <c r="C171" s="4" t="inlineStr">
-        <is>
-          <t>Double</t>
-        </is>
-      </c>
-      <c r="D171" s="4" t="inlineStr"/>
-      <c r="E171" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F171" s="4" t="inlineStr"/>
-      <c r="G171" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H171" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="A171" s="5" t="inlineStr">
+        <is>
+          <t>ActionGroups</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>isUsed</t>
+        </is>
+      </c>
+      <c r="C171" s="5" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>Canonical header from ActionGroups.xlsx</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F171" s="5" t="inlineStr"/>
+      <c r="G171" s="5" t="inlineStr"/>
+      <c r="H171" s="5" t="inlineStr">
+        <is>
+          <t>actgr.is_used is marked CC8 relevant = No.</t>
         </is>
       </c>
     </row>
@@ -20846,15 +21406,19 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>actionGroupId</t>
+          <t>isObsolete</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D172" s="5" t="inlineStr"/>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="D172" s="5" t="inlineStr">
+        <is>
+          <t>Canonical header from ActionGroups.xlsx</t>
+        </is>
+      </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
           <t>Out of v1 scope</t>
@@ -20864,268 +21428,182 @@
       <c r="G172" s="5" t="inlineStr"/>
       <c r="H172" s="5" t="inlineStr">
         <is>
-          <t>actgr.actgr_id is marked CC8 relevant = No.</t>
+          <t>actgr.is_obsolete is marked CC8 relevant = No.</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="5" t="inlineStr">
-        <is>
-          <t>ActionGroups</t>
-        </is>
-      </c>
-      <c r="B173" s="5" t="inlineStr">
-        <is>
-          <t>nodeId</t>
-        </is>
-      </c>
-      <c r="C173" s="5" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D173" s="5" t="inlineStr"/>
-      <c r="E173" s="5" t="inlineStr">
-        <is>
-          <t>Out of v1 scope</t>
-        </is>
-      </c>
-      <c r="F173" s="5" t="inlineStr"/>
-      <c r="G173" s="5" t="inlineStr"/>
-      <c r="H173" s="5" t="inlineStr">
-        <is>
-          <t>actgr.node_id is marked CC8 relevant = No.</t>
+      <c r="A173" s="4" t="inlineStr">
+        <is>
+          <t>WarehouseExclusions</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>Secondary TO</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr"/>
+      <c r="D173" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Warehouse Distribution Exclusions.xlsx</t>
+        </is>
+      </c>
+      <c r="E173" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F173" s="4" t="inlineStr"/>
+      <c r="G173" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H173" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="5" t="inlineStr">
-        <is>
-          <t>ActionGroups</t>
-        </is>
-      </c>
-      <c r="B174" s="5" t="inlineStr">
-        <is>
-          <t>actionGroupDescription</t>
-        </is>
-      </c>
-      <c r="C174" s="5" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D174" s="5" t="inlineStr"/>
-      <c r="E174" s="5" t="inlineStr">
-        <is>
-          <t>Out of v1 scope</t>
-        </is>
-      </c>
-      <c r="F174" s="5" t="inlineStr"/>
-      <c r="G174" s="5" t="inlineStr"/>
-      <c r="H174" s="5" t="inlineStr">
-        <is>
-          <t>actgr.descr is marked CC8 relevant = No.</t>
+      <c r="A174" s="4" t="inlineStr">
+        <is>
+          <t>WarehouseExclusions</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>Secondary FROM</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="inlineStr"/>
+      <c r="D174" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Warehouse Distribution Exclusions.xlsx</t>
+        </is>
+      </c>
+      <c r="E174" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F174" s="4" t="inlineStr"/>
+      <c r="G174" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H174" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="5" t="inlineStr">
-        <is>
-          <t>ActionGroups</t>
-        </is>
-      </c>
-      <c r="B175" s="5" t="inlineStr">
-        <is>
-          <t>assignAnySkill</t>
-        </is>
-      </c>
-      <c r="C175" s="5" t="inlineStr">
-        <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="D175" s="5" t="inlineStr"/>
-      <c r="E175" s="5" t="inlineStr">
-        <is>
-          <t>Out of v1 scope</t>
-        </is>
-      </c>
-      <c r="F175" s="5" t="inlineStr"/>
-      <c r="G175" s="5" t="inlineStr"/>
-      <c r="H175" s="5" t="inlineStr">
-        <is>
-          <t>Technician action groups are marked CC8 relevant = No.</t>
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t>WarehouseExclusions</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>Cross TO</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr"/>
+      <c r="D175" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Warehouse Distribution Exclusions.xlsx</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F175" s="4" t="inlineStr"/>
+      <c r="G175" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H175" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="5" t="inlineStr">
-        <is>
-          <t>ActionGroups</t>
-        </is>
-      </c>
-      <c r="B176" s="5" t="inlineStr">
-        <is>
-          <t>isUsed</t>
-        </is>
-      </c>
-      <c r="C176" s="5" t="inlineStr">
-        <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="D176" s="5" t="inlineStr"/>
-      <c r="E176" s="5" t="inlineStr">
-        <is>
-          <t>Out of v1 scope</t>
-        </is>
-      </c>
-      <c r="F176" s="5" t="inlineStr"/>
-      <c r="G176" s="5" t="inlineStr"/>
-      <c r="H176" s="5" t="inlineStr">
-        <is>
-          <t>actgr.is_used is marked CC8 relevant = No.</t>
+      <c r="A176" s="4" t="inlineStr">
+        <is>
+          <t>WarehouseExclusions</t>
+        </is>
+      </c>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>Cross FROM</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr"/>
+      <c r="D176" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Warehouse Distribution Exclusions.xlsx</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F176" s="4" t="inlineStr"/>
+      <c r="G176" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H176" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="5" t="inlineStr">
-        <is>
-          <t>ActionGroups</t>
-        </is>
-      </c>
-      <c r="B177" s="5" t="inlineStr">
-        <is>
-          <t>isObsolete</t>
-        </is>
-      </c>
-      <c r="C177" s="5" t="inlineStr">
-        <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="D177" s="5" t="inlineStr"/>
-      <c r="E177" s="5" t="inlineStr">
-        <is>
-          <t>Out of v1 scope</t>
-        </is>
-      </c>
-      <c r="F177" s="5" t="inlineStr"/>
-      <c r="G177" s="5" t="inlineStr"/>
-      <c r="H177" s="5" t="inlineStr">
-        <is>
-          <t>actgr.is_obsolete is marked CC8 relevant = No.</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="4" t="inlineStr">
+      <c r="A177" s="4" t="inlineStr">
         <is>
           <t>WarehouseExclusions</t>
         </is>
       </c>
-      <c r="B178" s="4" t="inlineStr">
-        <is>
-          <t>warehouseId</t>
-        </is>
-      </c>
-      <c r="C178" s="4" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D178" s="4" t="inlineStr"/>
-      <c r="E178" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F178" s="4" t="inlineStr"/>
-      <c r="G178" s="4" t="inlineStr">
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>Primary TO</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr"/>
+      <c r="D177" s="4" t="inlineStr">
+        <is>
+          <t>Canonical header from Warehouse Distribution Exclusions.xlsx</t>
+        </is>
+      </c>
+      <c r="E177" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F177" s="4" t="inlineStr"/>
+      <c r="G177" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H178" s="4" t="inlineStr">
+      <c r="H177" s="4" t="inlineStr">
         <is>
           <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="B179" s="4" t="inlineStr">
-        <is>
-          <t>exclusionType</t>
-        </is>
-      </c>
-      <c r="C179" s="4" t="inlineStr">
-        <is>
-          <t>Enum&lt;String&gt;</t>
-        </is>
-      </c>
-      <c r="D179" s="4" t="inlineStr"/>
-      <c r="E179" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F179" s="4" t="inlineStr"/>
-      <c r="G179" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H179" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="B180" s="4" t="inlineStr">
-        <is>
-          <t>exclusion</t>
-        </is>
-      </c>
-      <c r="C180" s="4" t="inlineStr">
-        <is>
-          <t>String / Enum&lt;String&gt;</t>
-        </is>
-      </c>
-      <c r="D180" s="4" t="inlineStr">
-        <is>
-          <t>If the exclusionType above is a location type as opposed to a specific location, then it is limited to a fixed set of location types: [PROJ,DEPOT,REPAIR]</t>
-        </is>
-      </c>
-      <c r="E180" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F180" s="4" t="inlineStr"/>
-      <c r="G180" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H180" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H180"/>
+  <autoFilter ref="A1:H177"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -26969,7 +27447,7 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>customerGroupId</t>
+          <t>customerName</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
@@ -26985,12 +27463,12 @@
       <c r="D108" s="4" t="inlineStr"/>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>Investigate source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Customers.customerGroupId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.customerName?</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
@@ -27002,14 +27480,14 @@
       <c r="I108" s="4" t="inlineStr"/>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User has no confirmed source yet for customer grouping.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>customerGroupId</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -27030,7 +27508,7 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Customers.Description?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.customerGroupId?</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
@@ -27042,7 +27520,7 @@
       <c r="I109" s="4" t="inlineStr"/>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>Left blank. SAP BusinessPartners can supply names, but the correct Planning V2 customer scope is not confirmed.</t>
+          <t>Left blank. User has no confirmed source yet for customer grouping.</t>
         </is>
       </c>
     </row>
@@ -27329,7 +27807,7 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>vendorName</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -27350,7 +27828,7 @@
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Vendors.Description?</t>
+          <t>What confirmed CoCre8/SAP source should populate Vendors.vendorName?</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
@@ -27409,7 +27887,7 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>isBranchStockable</t>
+          <t>isBootStockable</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -27430,7 +27908,7 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isBranchStockable?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isBootStockable?</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
@@ -27449,7 +27927,7 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>isBootStockable</t>
+          <t>isBranchStockable</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
@@ -27470,7 +27948,7 @@
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isBootStockable?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isBranchStockable?</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr">
@@ -27929,7 +28407,7 @@
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>addressLine1</t>
+          <t>6,0</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
@@ -27950,7 +28428,7 @@
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine1?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.6,0?</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr">
@@ -28689,12 +29167,12 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>customerCompanyCode</t>
+          <t>whs id</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -28710,7 +29188,7 @@
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.customerCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.whs id?</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
@@ -28729,7 +29207,7 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>orderType</t>
+          <t>OrderType</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
@@ -28750,7 +29228,7 @@
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderType?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.OrderType?</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
@@ -28769,7 +29247,7 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>orderStatus</t>
+          <t>customerCompanyCode</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
@@ -28790,7 +29268,7 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.customerCompanyCode?</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
@@ -28849,7 +29327,7 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>requestTicketDateTime</t>
+          <t>orderStatus</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
@@ -28870,7 +29348,7 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.requestTicketDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStatus?</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
@@ -28889,7 +29367,7 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>siteCompanyCode</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
@@ -28910,7 +29388,7 @@
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.siteCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr">
@@ -28929,7 +29407,7 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>assignedPersonCode</t>
+          <t>serialNumber</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
@@ -28950,7 +29428,7 @@
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.serialNumber?</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
@@ -28969,7 +29447,7 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>relCompanyId</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
@@ -28990,7 +29468,7 @@
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr">
@@ -29009,7 +29487,7 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>serialNumber</t>
+          <t>assignedPersonCode</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
@@ -29030,7 +29508,7 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.serialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
@@ -29049,7 +29527,7 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>relCompanyId</t>
+          <t>deviceSerialNumber</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
@@ -29070,7 +29548,7 @@
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.deviceSerialNumber?</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr">
@@ -29089,12 +29567,12 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>deviceSerialNumber</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
@@ -29110,7 +29588,7 @@
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.deviceSerialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.orderNumber?</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
@@ -29129,7 +29607,7 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>RequestID</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
@@ -29150,7 +29628,7 @@
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.RequestID?</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr">
@@ -29569,7 +30047,7 @@
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>slaResolvedDateTime</t>
+          <t>slaResolveDateTime</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
@@ -29590,7 +30068,7 @@
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveDateTime?</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -30169,7 +30647,7 @@
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>orderedPartId</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
@@ -30190,7 +30668,7 @@
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderedPartId?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.resolvedDateTime?</t>
         </is>
       </c>
       <c r="G188" s="4" t="inlineStr">
@@ -30209,7 +30687,7 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>actualPartId</t>
+          <t>serialNumber</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
@@ -30230,7 +30708,7 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.actualPartId?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.serialNumber?</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr">
@@ -30249,7 +30727,7 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>quantityUsed</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
@@ -30270,7 +30748,7 @@
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.resolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.quantityUsed?</t>
         </is>
       </c>
       <c r="G190" s="4" t="inlineStr">
@@ -30289,7 +30767,7 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>serialNumber</t>
+          <t>deviceSerialNumber</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
@@ -30310,7 +30788,7 @@
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.serialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.deviceSerialNumber?</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -30329,7 +30807,7 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>quantityUsed</t>
+          <t>orderedPartId</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
@@ -30350,7 +30828,7 @@
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.quantityUsed?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderedPartId?</t>
         </is>
       </c>
       <c r="G192" s="4" t="inlineStr">
@@ -30369,7 +30847,7 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>relCompanyId</t>
+          <t>actualPartId</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
@@ -30390,7 +30868,7 @@
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.relCompanyId?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.actualPartId?</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -30409,12 +30887,12 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>partsUsedDateTime</t>
+          <t>partCode</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
@@ -30430,7 +30908,7 @@
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsUsedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.partCode?</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr">
@@ -30449,12 +30927,12 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>deviceSerialNumber</t>
+          <t>cost</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -30470,7 +30948,7 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.deviceSerialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.cost?</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -30489,7 +30967,7 @@
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>currencyCode</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
@@ -30510,7 +30988,7 @@
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.currencyCode?</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr">
@@ -30529,7 +31007,7 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>averageCost</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
@@ -30550,7 +31028,7 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.cost?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.averageCost?</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
@@ -30569,12 +31047,12 @@
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>currencyCode</t>
+          <t>partCode</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
@@ -30590,7 +31068,7 @@
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.currencyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr">
@@ -30609,12 +31087,12 @@
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>averageCost</t>
+          <t>modelCode</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
@@ -30630,7 +31108,7 @@
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.averageCost?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
@@ -30649,7 +31127,7 @@
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>modelDescription</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
@@ -30670,7 +31148,7 @@
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr">
@@ -30689,12 +31167,12 @@
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>modelCode</t>
+          <t>inventoryTransferImoId</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
@@ -30710,7 +31188,7 @@
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.inventoryTransferImoId?</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
@@ -30729,12 +31207,12 @@
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>modelDescription</t>
+          <t>createdDateTime</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
@@ -30750,7 +31228,7 @@
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.createdDateTime?</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr">
@@ -30769,7 +31247,7 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>inventoryTransferImoId</t>
+          <t>completedDateTime</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
@@ -30790,7 +31268,7 @@
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.inventoryTransferImoId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.completedDateTime?</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -30809,7 +31287,7 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>createdDateTime</t>
+          <t>fromWarehouseId</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
@@ -30830,7 +31308,7 @@
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.createdDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.fromWarehouseId?</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr">
@@ -30849,7 +31327,7 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>completedDateTime</t>
+          <t>toWarehouseId</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
@@ -30870,7 +31348,7 @@
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.completedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.toWarehouseId?</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -30889,7 +31367,7 @@
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>fromWarehouseId</t>
+          <t>demandStatus</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
@@ -30910,7 +31388,7 @@
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.fromWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.demandStatus?</t>
         </is>
       </c>
       <c r="G206" s="4" t="inlineStr">
@@ -30929,7 +31407,7 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>toWarehouseId</t>
+          <t>orderStatusIsClosed</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
@@ -30950,7 +31428,7 @@
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.toWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.orderStatusIsClosed?</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -30969,7 +31447,7 @@
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>demandStatus</t>
+          <t>movementType</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
@@ -30990,7 +31468,7 @@
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.demandStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
         </is>
       </c>
       <c r="G208" s="4" t="inlineStr">
@@ -31009,7 +31487,7 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>orderStatusIsClosed</t>
+          <t>addressId</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
@@ -31030,7 +31508,7 @@
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.orderStatusIsClosed?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr">
@@ -31049,7 +31527,7 @@
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>movementType</t>
+          <t>Bpart</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
@@ -31070,7 +31548,7 @@
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.Bpart?</t>
         </is>
       </c>
       <c r="G210" s="4" t="inlineStr">
@@ -31089,7 +31567,7 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>addressId</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
@@ -31110,7 +31588,7 @@
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.quantity?</t>
         </is>
       </c>
       <c r="G211" s="4" t="inlineStr">
@@ -31129,7 +31607,7 @@
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>isResolved</t>
+          <t>shipListCode</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
@@ -31150,7 +31628,7 @@
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.isResolved?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
         </is>
       </c>
       <c r="G212" s="4" t="inlineStr">
@@ -31167,54 +31645,54 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="4" t="inlineStr">
-        <is>
-          <t>partNumber</t>
-        </is>
-      </c>
-      <c r="B213" s="4" t="inlineStr">
-        <is>
-          <t>InventoryTransfers</t>
-        </is>
-      </c>
-      <c r="C213" s="4" t="inlineStr">
+      <c r="A213" s="3" t="inlineStr">
+        <is>
+          <t>demandStatus</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>PurchaseOrders</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
         <is>
           <t>Planning V2 template</t>
         </is>
       </c>
-      <c r="D213" s="4" t="inlineStr"/>
-      <c r="E213" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F213" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.partNumber?</t>
-        </is>
-      </c>
-      <c r="G213" s="4" t="inlineStr">
+      <c r="D213" s="3" t="inlineStr"/>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="F213" s="3" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
+        </is>
+      </c>
+      <c r="G213" s="3" t="inlineStr">
         <is>
           <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
         </is>
       </c>
-      <c r="H213" s="4" t="inlineStr"/>
-      <c r="I213" s="4" t="inlineStr"/>
-      <c r="J213" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="H213" s="3" t="inlineStr"/>
+      <c r="I213" s="3" t="inlineStr"/>
+      <c r="J213" s="3" t="inlineStr">
+        <is>
+          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.DocNum and part/SPL Master evidence also matches; current export needs reconciliation.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>partType</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
@@ -31230,7 +31708,7 @@
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.quantity?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.partType?</t>
         </is>
       </c>
       <c r="G214" s="4" t="inlineStr">
@@ -31249,12 +31727,12 @@
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>shipListCode</t>
+          <t>partTypeDescription</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
@@ -31270,7 +31748,7 @@
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeDescription?</t>
         </is>
       </c>
       <c r="G215" s="4" t="inlineStr">
@@ -31287,54 +31765,54 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="3" t="inlineStr">
-        <is>
-          <t>demandStatus</t>
-        </is>
-      </c>
-      <c r="B216" s="3" t="inlineStr">
-        <is>
-          <t>PurchaseOrders</t>
-        </is>
-      </c>
-      <c r="C216" s="3" t="inlineStr">
+      <c r="A216" s="4" t="inlineStr">
+        <is>
+          <t>isReworkable</t>
+        </is>
+      </c>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
+          <t>PartTypes</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr">
         <is>
           <t>Planning V2 template</t>
         </is>
       </c>
-      <c r="D216" s="3" t="inlineStr"/>
-      <c r="E216" s="3" t="inlineStr">
-        <is>
-          <t>Review required</t>
-        </is>
-      </c>
-      <c r="F216" s="3" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
-        </is>
-      </c>
-      <c r="G216" s="3" t="inlineStr">
+      <c r="D216" s="4" t="inlineStr"/>
+      <c r="E216" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F216" s="4" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.isReworkable?</t>
+        </is>
+      </c>
+      <c r="G216" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
         </is>
       </c>
-      <c r="H216" s="3" t="inlineStr"/>
-      <c r="I216" s="3" t="inlineStr"/>
-      <c r="J216" s="3" t="inlineStr">
-        <is>
-          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.DocNum and part/SPL Master evidence also matches; current export needs reconciliation.</t>
+      <c r="H216" s="4" t="inlineStr"/>
+      <c r="I216" s="4" t="inlineStr"/>
+      <c r="J216" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>partTypeCode</t>
+          <t>partNumber</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
@@ -31350,7 +31828,7 @@
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
         </is>
       </c>
       <c r="G217" s="4" t="inlineStr">
@@ -31369,12 +31847,12 @@
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>unitOfMeasure</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
@@ -31390,7 +31868,7 @@
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.description?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
         </is>
       </c>
       <c r="G218" s="4" t="inlineStr">
@@ -31409,7 +31887,7 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>partNumber</t>
+          <t>yield</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
@@ -31430,7 +31908,7 @@
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
         </is>
       </c>
       <c r="G219" s="4" t="inlineStr">
@@ -31449,12 +31927,12 @@
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>unitOfMeasure</t>
+          <t>Secondary TO</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
@@ -31470,7 +31948,7 @@
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary TO?</t>
         </is>
       </c>
       <c r="G220" s="4" t="inlineStr">
@@ -31489,12 +31967,12 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>yield</t>
+          <t>Secondary FROM</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
@@ -31510,7 +31988,7 @@
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary FROM?</t>
         </is>
       </c>
       <c r="G221" s="4" t="inlineStr">
@@ -31529,7 +32007,7 @@
     <row r="222">
       <c r="A222" s="4" t="inlineStr">
         <is>
-          <t>warehouseId</t>
+          <t>Cross TO</t>
         </is>
       </c>
       <c r="B222" s="4" t="inlineStr">
@@ -31550,7 +32028,7 @@
       </c>
       <c r="F222" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.warehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross TO?</t>
         </is>
       </c>
       <c r="G222" s="4" t="inlineStr">
@@ -31569,7 +32047,7 @@
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>exclusionType</t>
+          <t>Cross FROM</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
@@ -31590,7 +32068,7 @@
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusionType?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross FROM?</t>
         </is>
       </c>
       <c r="G223" s="4" t="inlineStr">
@@ -31609,7 +32087,7 @@
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
         <is>
-          <t>exclusion</t>
+          <t>Primary TO</t>
         </is>
       </c>
       <c r="B224" s="4" t="inlineStr">
@@ -31630,7 +32108,7 @@
       </c>
       <c r="F224" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.exclusion?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Primary TO?</t>
         </is>
       </c>
       <c r="G224" s="4" t="inlineStr">
@@ -32089,12 +32567,12 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>customerId, customerGroupId, Description, assignAnySkill, isActive, dseSlaCost, dseSlaRevenue, stdResponseTime, stdRepairTime</t>
+          <t>customerId, customerName, customerGroupId, assignAnySkill, isActive, dseSlaCost, dseSlaRevenue, stdResponseTime, stdRepairTime</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>customerId; customerGroupId; Description; assignAnySkill; isActive; dseSlaCost; dseSlaRevenue; stdResponseTime; stdRepairTime</t>
+          <t>customerId; customerName; customerGroupId; assignAnySkill; isActive; dseSlaCost; dseSlaRevenue; stdResponseTime; stdRepairTime</t>
         </is>
       </c>
     </row>
@@ -32116,12 +32594,12 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>vendorId, Description, isActive</t>
+          <t>vendorId, vendorName, isActive</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>vendorId; Description; isActive</t>
+          <t>vendorId; vendorName; isActive</t>
         </is>
       </c>
     </row>
@@ -32143,12 +32621,12 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>SPLMaster, PartNumber, isPrimary, primaryPartNumber, description, isBranchStockable, isBootStockable, productClass, productType, costCategory, partType, isKit, isObsolete, isExcludeFromReplenishment, purchaseLeadTimeDays, isCritical</t>
+          <t>SPLMaster, PartNumber, isPrimary, primaryPartNumber, description, isBootStockable, isBranchStockable, productClass, productType, costCategory, partType, isKit, isObsolete, isExcludeFromReplenishment, purchaseLeadTimeDays, isCritical</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>isBranchStockable; isBootStockable; productClass; productType; costCategory; partType; isKit; isObsolete; isExcludeFromReplenishment; purchaseLeadTimeDays; isCritical</t>
+          <t>isBootStockable; isBranchStockable; productClass; productType; costCategory; partType; isKit; isObsolete; isExcludeFromReplenishment; purchaseLeadTimeDays; isCritical</t>
         </is>
       </c>
     </row>
@@ -32170,12 +32648,12 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>externalAddressId, customerExternalId, addressLine1, addressLine2, addressLine3, city, stateProvince, countryCode, latitude, longitude, timeZone, nodeId</t>
+          <t>externalAddressId, customerExternalId, 6,0, addressLine2, addressLine3, city, stateProvince, countryCode, latitude, longitude, timeZone, nodeId</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>externalAddressId; customerExternalId; addressLine1; addressLine2; addressLine3; city; stateProvince; countryCode; latitude; longitude; timeZone; nodeId</t>
+          <t>externalAddressId; customerExternalId; 6,0; addressLine2; addressLine3; city; stateProvince; countryCode; latitude; longitude; timeZone; nodeId</t>
         </is>
       </c>
     </row>
@@ -32220,7 +32698,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>partCode, warehouseCode, quantityAllocated, quantityOnHand, quantityInbound, uniqueId</t>
+          <t>partNumber, warehouseCode, quantityAllocated, quantityOnHand, quantityInbound, uniqueId</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr"/>
@@ -32243,12 +32721,12 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>personId, role, addressId, nodeId, firstName, middleName, surname, isActive, telephoneNumber</t>
+          <t>personId, role, addressId, nodeId, firstName, middleName, surname, isActive, telephoneNumber, whs id</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>personId; role; addressId; nodeId; firstName; middleName; surname; isActive; telephoneNumber</t>
+          <t>personId; role; addressId; nodeId; firstName; middleName; surname; isActive; telephoneNumber; whs id</t>
         </is>
       </c>
     </row>
@@ -32270,12 +32748,12 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>orderNumber, customerCompanyCode, orderType, orderStatus, orderStartDatetime, requestTicketDateTime, siteCompanyCode, partCode, Warehouse, assignedPersonCode, resolvedDateTime, serialNumber, quantityUsed, relCompanyId, partsUsedDateTime, deviceSerialNumber</t>
+          <t>orderNumber, OrderType, customerCompanyCode, orderStartDatetime, orderStatus, resolvedDateTime, partCode, serialNumber, quantityUsed, relCompanyId, partsUsedDateTime, Warehouse, assignedPersonCode, deviceSerialNumber, Master</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>customerCompanyCode; orderType; orderStatus; orderStartDatetime; requestTicketDateTime; siteCompanyCode; assignedPersonCode; resolvedDateTime; serialNumber; relCompanyId; deviceSerialNumber</t>
+          <t>OrderType; customerCompanyCode; orderStartDatetime; orderStatus; resolvedDateTime; serialNumber; relCompanyId; assignedPersonCode; deviceSerialNumber</t>
         </is>
       </c>
     </row>
@@ -32297,12 +32775,12 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>orderNumber, location, eta, actualEta, actualResolveDateTime, recallDateTime, actualRecallDateTime, slaEtaClock, slaResolveClock, slaFailureCode, slaEtaHit, slaResolvedDateTime</t>
+          <t>orderNumber, RequestID, location, eta, actualEta, actualResolveDateTime, recallDateTime, actualRecallDateTime, slaEtaClock, slaResolveClock, slaFailureCode, slaEtaHit, slaResolveDateTime</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>orderNumber; location; eta; actualEta; actualResolveDateTime; recallDateTime; actualRecallDateTime; slaEtaClock; slaResolveClock; slaFailureCode; slaEtaHit; slaResolvedDateTime</t>
+          <t>orderNumber; RequestID; location; eta; actualEta; actualResolveDateTime; recallDateTime; actualRecallDateTime; slaEtaClock; slaResolveClock; slaFailureCode; slaEtaHit; slaResolveDateTime</t>
         </is>
       </c>
     </row>
@@ -32324,12 +32802,12 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>orderNumber, requestId, customerCompanyCode, orderStatus, orderStartDatetime, siteCompanyCode, repairType, partsOrderDateTime, partsReceivedDateTime, repairCode, repairCompany, raStatus, Warehouse, assignedPerson, orderedPartId, actualPartId, resolvedDateTime, serialNumber, quantityUsed, relCompanyId, partsUsedDateTime, deviceSerialNumber</t>
+          <t>orderNumber, requestId, customerCompanyCode, orderStatus, orderStartDatetime, siteCompanyCode, repairType, partsOrderDateTime, partsReceivedDateTime, repairCode, repairCompany, raStatus, Warehouse, assignedPerson, resolvedDateTime, serialNumber, quantityUsed, deviceSerialNumber, orderedPartId, actualPartId</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>orderNumber; requestId; customerCompanyCode; orderStatus; orderStartDatetime; siteCompanyCode; repairType; partsOrderDateTime; partsReceivedDateTime; repairCode; repairCompany; raStatus; Warehouse; assignedPerson; orderedPartId; actualPartId; resolvedDateTime; serialNumber; quantityUsed; relCompanyId; partsUsedDateTime; deviceSerialNumber</t>
+          <t>orderNumber; requestId; customerCompanyCode; orderStatus; orderStartDatetime; siteCompanyCode; repairType; partsOrderDateTime; partsReceivedDateTime; repairCode; repairCompany; raStatus; Warehouse; assignedPerson; resolvedDateTime; serialNumber; quantityUsed; deviceSerialNumber; orderedPartId; actualPartId</t>
         </is>
       </c>
     </row>
@@ -32405,12 +32883,12 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>inventoryTransferImoId, createdDateTime, completedDateTime, fromWarehouseId, toWarehouseId, demandStatus, orderStatusIsClosed, movementType, addressId, isResolved, partNumber, quantity, shipListCode</t>
+          <t>inventoryTransferImoId, createdDateTime, completedDateTime, fromWarehouseId, toWarehouseId, demandStatus, orderStatusIsClosed, movementType, addressId, Bpart, quantity, shipListCode</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>inventoryTransferImoId; createdDateTime; completedDateTime; fromWarehouseId; toWarehouseId; demandStatus; orderStatusIsClosed; movementType; addressId; isResolved; partNumber; quantity; shipListCode</t>
+          <t>inventoryTransferImoId; createdDateTime; completedDateTime; fromWarehouseId; toWarehouseId; demandStatus; orderStatusIsClosed; movementType; addressId; Bpart; quantity; shipListCode</t>
         </is>
       </c>
     </row>
@@ -32459,12 +32937,12 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>partTypeCode, description</t>
+          <t>partType, partTypeDescription, isReworkable</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>partTypeCode; description</t>
+          <t>partType; partTypeDescription; isReworkable</t>
         </is>
       </c>
     </row>
@@ -32532,12 +33010,12 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>warehouseId, exclusionType, exclusion</t>
+          <t>Secondary TO, Secondary FROM, Cross TO, Cross FROM, Primary TO</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>warehouseId; exclusionType; exclusion</t>
+          <t>Secondary TO; Secondary FROM; Cross TO; Cross FROM; Primary TO</t>
         </is>
       </c>
     </row>

--- a/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
+++ b/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Target Fields'!$A$1:$S$151</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Template Fields'!$A$1:$H$177</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Evidence'!$A$1:$D$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$J$224</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$J$219</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Output Objects'!$A$1:$E$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Missing Important Fields'!$A$1:$E$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'SAP Investigation Log'!$A$1:$E$10</definedName>
@@ -244,8 +244,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:J224" headerRowCount="1">
-  <autoFilter ref="A1:J224"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:J219" headerRowCount="1">
+  <autoFilter ref="A1:J219"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Field"/>
     <tableColumn id="2" name="Object"/>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report 3Y:Document for DN rows</t>
+          <t>CoCre8 HelpDesk issue tracker:Call Number</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -18005,116 +18005,128 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>customerCompanyCode</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Canonical header from PartsUsage.xlsx</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr"/>
-      <c r="G83" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>CoCre8 HelpDesk issue tracker:CustomerNormalized/Customer</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>orderStartDatetime</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Canonical header from PartsUsage.xlsx</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr"/>
-      <c r="G84" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>CoCre8 HelpDesk issue tracker:Created</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="inlineStr">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B85" s="4" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>orderStatus</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D85" s="4" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Canonical header from PartsUsage.xlsx</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr"/>
-      <c r="G85" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H85" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>CoCre8 HelpDesk issue tracker:Status</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -18184,7 +18196,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report 3Y:Item No.</t>
+          <t>CoCre8 HelpDesk issue tracker:DispatchPartNo when present, otherwise Part Nr</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -18199,40 +18211,44 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B88" s="4" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>serialNumber</t>
         </is>
       </c>
-      <c r="C88" s="4" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D88" s="4" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Canonical header from PartsUsage.xlsx</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr"/>
-      <c r="G88" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>CoCre8 HelpDesk issue tracker:Serial Nr</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -18264,7 +18280,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report 3Y:absolute Quantity for negative DN rows</t>
+          <t>CoCre8 HelpDesk issue tracker:Quantity</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -18344,7 +18360,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report 3Y:Posting Date</t>
+          <t>CoCre8 HelpDesk issue tracker:Created used as demand/usage date</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -18386,7 +18402,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report 3Y:Whse</t>
+          <t>CoCre8 HelpDesk issue tracker:DispatchWarehouse</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -18439,40 +18455,44 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B94" s="4" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>deviceSerialNumber</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr">
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Canonical header from PartsUsage.xlsx</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr"/>
-      <c r="G94" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>CoCre8 HelpDesk issue tracker:Serial Nr</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -18500,7 +18520,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Reference masters.csv:SPL Master by used part</t>
+          <t>CoCre8 HelpDesk issue tracker:SPLMaster or masters.csv by part</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -21949,7 +21969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J224"/>
+  <dimension ref="A1:J219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -29247,7 +29267,7 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>customerCompanyCode</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
@@ -29268,7 +29288,7 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.customerCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
@@ -29287,7 +29307,7 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>orderStartDatetime</t>
+          <t>relCompanyId</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
@@ -29308,7 +29328,7 @@
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStartDatetime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr">
@@ -29327,7 +29347,7 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>orderStatus</t>
+          <t>assignedPersonCode</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
@@ -29348,7 +29368,7 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
@@ -29367,12 +29387,12 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
@@ -29388,7 +29408,7 @@
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.orderNumber?</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr">
@@ -29407,12 +29427,12 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>serialNumber</t>
+          <t>RequestID</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
@@ -29428,7 +29448,7 @@
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.serialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.RequestID?</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
@@ -29447,12 +29467,12 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>relCompanyId</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
@@ -29468,7 +29488,7 @@
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.location?</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr">
@@ -29487,12 +29507,12 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>assignedPersonCode</t>
+          <t>eta</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
@@ -29508,7 +29528,7 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.eta?</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
@@ -29527,12 +29547,12 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>deviceSerialNumber</t>
+          <t>actualEta</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
@@ -29548,7 +29568,7 @@
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.deviceSerialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualEta?</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr">
@@ -29567,7 +29587,7 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>actualResolveDateTime</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
@@ -29588,7 +29608,7 @@
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualResolveDateTime?</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
@@ -29607,7 +29627,7 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>RequestID</t>
+          <t>recallDateTime</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
@@ -29628,7 +29648,7 @@
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.RequestID?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.recallDateTime?</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr">
@@ -29647,7 +29667,7 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>actualRecallDateTime</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
@@ -29668,7 +29688,7 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.location?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualRecallDateTime?</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
@@ -29687,7 +29707,7 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>eta</t>
+          <t>slaEtaClock</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
@@ -29708,7 +29728,7 @@
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.eta?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaClock?</t>
         </is>
       </c>
       <c r="G164" s="4" t="inlineStr">
@@ -29727,7 +29747,7 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>actualEta</t>
+          <t>slaResolveClock</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
@@ -29748,7 +29768,7 @@
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualEta?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveClock?</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
@@ -29767,7 +29787,7 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>actualResolveDateTime</t>
+          <t>slaFailureCode</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
@@ -29788,7 +29808,7 @@
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualResolveDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaFailureCode?</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr">
@@ -29807,7 +29827,7 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>recallDateTime</t>
+          <t>slaEtaHit</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
@@ -29828,7 +29848,7 @@
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.recallDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaHit?</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -29847,7 +29867,7 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>actualRecallDateTime</t>
+          <t>slaResolveDateTime</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
@@ -29868,7 +29888,7 @@
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualRecallDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveDateTime?</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr">
@@ -29887,12 +29907,12 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>slaEtaClock</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
@@ -29908,7 +29928,7 @@
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaClock?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderNumber?</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
@@ -29927,12 +29947,12 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>slaResolveClock</t>
+          <t>requestId</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
@@ -29948,7 +29968,7 @@
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveClock?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.requestId?</t>
         </is>
       </c>
       <c r="G170" s="4" t="inlineStr">
@@ -29967,12 +29987,12 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>slaFailureCode</t>
+          <t>customerCompanyCode</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
@@ -29988,7 +30008,7 @@
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaFailureCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.customerCompanyCode?</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
@@ -30007,12 +30027,12 @@
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>slaEtaHit</t>
+          <t>orderStatus</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
@@ -30028,7 +30048,7 @@
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaHit?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStatus?</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr">
@@ -30047,12 +30067,12 @@
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>slaResolveDateTime</t>
+          <t>orderStartDatetime</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
@@ -30068,7 +30088,7 @@
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStartDatetime?</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -30087,7 +30107,7 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>siteCompanyCode</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
@@ -30108,7 +30128,7 @@
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.siteCompanyCode?</t>
         </is>
       </c>
       <c r="G174" s="4" t="inlineStr">
@@ -30127,7 +30147,7 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>requestId</t>
+          <t>repairType</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
@@ -30148,7 +30168,7 @@
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.requestId?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairType?</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
@@ -30167,7 +30187,7 @@
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>customerCompanyCode</t>
+          <t>partsOrderDateTime</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
@@ -30188,7 +30208,7 @@
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.customerCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsOrderDateTime?</t>
         </is>
       </c>
       <c r="G176" s="4" t="inlineStr">
@@ -30207,7 +30227,7 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>orderStatus</t>
+          <t>partsReceivedDateTime</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
@@ -30228,7 +30248,7 @@
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsReceivedDateTime?</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
@@ -30247,7 +30267,7 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>orderStartDatetime</t>
+          <t>repairCode</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
@@ -30268,7 +30288,7 @@
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStartDatetime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCode?</t>
         </is>
       </c>
       <c r="G178" s="4" t="inlineStr">
@@ -30287,7 +30307,7 @@
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>siteCompanyCode</t>
+          <t>repairCompany</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
@@ -30308,7 +30328,7 @@
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.siteCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCompany?</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
@@ -30327,7 +30347,7 @@
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>repairType</t>
+          <t>raStatus</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
@@ -30348,7 +30368,7 @@
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairType?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.raStatus?</t>
         </is>
       </c>
       <c r="G180" s="4" t="inlineStr">
@@ -30367,7 +30387,7 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>partsOrderDateTime</t>
+          <t>Warehouse</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
@@ -30388,7 +30408,7 @@
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsOrderDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.Warehouse?</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
@@ -30407,7 +30427,7 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>partsReceivedDateTime</t>
+          <t>assignedPerson</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
@@ -30428,7 +30448,7 @@
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsReceivedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.assignedPerson?</t>
         </is>
       </c>
       <c r="G182" s="4" t="inlineStr">
@@ -30447,7 +30467,7 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>repairCode</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
@@ -30468,7 +30488,7 @@
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.resolvedDateTime?</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
@@ -30487,7 +30507,7 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>repairCompany</t>
+          <t>serialNumber</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
@@ -30508,7 +30528,7 @@
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCompany?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.serialNumber?</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr">
@@ -30527,7 +30547,7 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>raStatus</t>
+          <t>quantityUsed</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
@@ -30548,7 +30568,7 @@
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.raStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.quantityUsed?</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr">
@@ -30567,7 +30587,7 @@
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>deviceSerialNumber</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
@@ -30588,7 +30608,7 @@
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.Warehouse?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.deviceSerialNumber?</t>
         </is>
       </c>
       <c r="G186" s="4" t="inlineStr">
@@ -30607,7 +30627,7 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>assignedPerson</t>
+          <t>orderedPartId</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
@@ -30628,7 +30648,7 @@
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.assignedPerson?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderedPartId?</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr">
@@ -30647,7 +30667,7 @@
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>actualPartId</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
@@ -30668,7 +30688,7 @@
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.resolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.actualPartId?</t>
         </is>
       </c>
       <c r="G188" s="4" t="inlineStr">
@@ -30687,12 +30707,12 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>serialNumber</t>
+          <t>partCode</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
@@ -30708,7 +30728,7 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.serialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.partCode?</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr">
@@ -30727,12 +30747,12 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>quantityUsed</t>
+          <t>cost</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
@@ -30748,7 +30768,7 @@
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.quantityUsed?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.cost?</t>
         </is>
       </c>
       <c r="G190" s="4" t="inlineStr">
@@ -30767,12 +30787,12 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>deviceSerialNumber</t>
+          <t>currencyCode</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
@@ -30788,7 +30808,7 @@
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.deviceSerialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.currencyCode?</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -30807,12 +30827,12 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>orderedPartId</t>
+          <t>averageCost</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
@@ -30828,7 +30848,7 @@
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderedPartId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.averageCost?</t>
         </is>
       </c>
       <c r="G192" s="4" t="inlineStr">
@@ -30847,12 +30867,12 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>actualPartId</t>
+          <t>partCode</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
@@ -30868,7 +30888,7 @@
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.actualPartId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -30887,12 +30907,12 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>modelCode</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
@@ -30908,7 +30928,7 @@
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr">
@@ -30927,12 +30947,12 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>modelDescription</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -30948,7 +30968,7 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.cost?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -30967,12 +30987,12 @@
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>currencyCode</t>
+          <t>inventoryTransferImoId</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
@@ -30988,7 +31008,7 @@
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.currencyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.inventoryTransferImoId?</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr">
@@ -31007,12 +31027,12 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>averageCost</t>
+          <t>createdDateTime</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
@@ -31028,7 +31048,7 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.averageCost?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.createdDateTime?</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
@@ -31047,12 +31067,12 @@
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>completedDateTime</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
@@ -31068,7 +31088,7 @@
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.completedDateTime?</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr">
@@ -31087,12 +31107,12 @@
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>modelCode</t>
+          <t>fromWarehouseId</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
@@ -31108,7 +31128,7 @@
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.fromWarehouseId?</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
@@ -31127,12 +31147,12 @@
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>modelDescription</t>
+          <t>toWarehouseId</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
@@ -31148,7 +31168,7 @@
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.toWarehouseId?</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr">
@@ -31167,7 +31187,7 @@
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>inventoryTransferImoId</t>
+          <t>demandStatus</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
@@ -31188,7 +31208,7 @@
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.inventoryTransferImoId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.demandStatus?</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
@@ -31207,7 +31227,7 @@
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>createdDateTime</t>
+          <t>orderStatusIsClosed</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
@@ -31228,7 +31248,7 @@
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.createdDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.orderStatusIsClosed?</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr">
@@ -31247,7 +31267,7 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>completedDateTime</t>
+          <t>movementType</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
@@ -31268,7 +31288,7 @@
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.completedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -31287,7 +31307,7 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>fromWarehouseId</t>
+          <t>addressId</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
@@ -31308,7 +31328,7 @@
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.fromWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr">
@@ -31327,7 +31347,7 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>toWarehouseId</t>
+          <t>Bpart</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
@@ -31348,7 +31368,7 @@
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.toWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.Bpart?</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -31367,7 +31387,7 @@
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>demandStatus</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
@@ -31388,7 +31408,7 @@
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.demandStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.quantity?</t>
         </is>
       </c>
       <c r="G206" s="4" t="inlineStr">
@@ -31407,7 +31427,7 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>orderStatusIsClosed</t>
+          <t>shipListCode</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
@@ -31428,7 +31448,7 @@
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.orderStatusIsClosed?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -31445,54 +31465,54 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="4" t="inlineStr">
-        <is>
-          <t>movementType</t>
-        </is>
-      </c>
-      <c r="B208" s="4" t="inlineStr">
-        <is>
-          <t>InventoryTransfers</t>
-        </is>
-      </c>
-      <c r="C208" s="4" t="inlineStr">
+      <c r="A208" s="3" t="inlineStr">
+        <is>
+          <t>demandStatus</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>PurchaseOrders</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
         <is>
           <t>Planning V2 template</t>
         </is>
       </c>
-      <c r="D208" s="4" t="inlineStr"/>
-      <c r="E208" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F208" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
-        </is>
-      </c>
-      <c r="G208" s="4" t="inlineStr">
+      <c r="D208" s="3" t="inlineStr"/>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="F208" s="3" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
+        </is>
+      </c>
+      <c r="G208" s="3" t="inlineStr">
         <is>
           <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
         </is>
       </c>
-      <c r="H208" s="4" t="inlineStr"/>
-      <c r="I208" s="4" t="inlineStr"/>
-      <c r="J208" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="H208" s="3" t="inlineStr"/>
+      <c r="I208" s="3" t="inlineStr"/>
+      <c r="J208" s="3" t="inlineStr">
+        <is>
+          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.DocNum and part/SPL Master evidence also matches; current export needs reconciliation.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>addressId</t>
+          <t>partType</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
@@ -31508,7 +31528,7 @@
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.partType?</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr">
@@ -31527,12 +31547,12 @@
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>Bpart</t>
+          <t>partTypeDescription</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
@@ -31548,7 +31568,7 @@
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.Bpart?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeDescription?</t>
         </is>
       </c>
       <c r="G210" s="4" t="inlineStr">
@@ -31567,12 +31587,12 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>isReworkable</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
@@ -31588,7 +31608,7 @@
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.quantity?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.isReworkable?</t>
         </is>
       </c>
       <c r="G211" s="4" t="inlineStr">
@@ -31607,12 +31627,12 @@
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>shipListCode</t>
+          <t>partNumber</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
@@ -31628,7 +31648,7 @@
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
         </is>
       </c>
       <c r="G212" s="4" t="inlineStr">
@@ -31645,54 +31665,54 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="3" t="inlineStr">
-        <is>
-          <t>demandStatus</t>
-        </is>
-      </c>
-      <c r="B213" s="3" t="inlineStr">
-        <is>
-          <t>PurchaseOrders</t>
-        </is>
-      </c>
-      <c r="C213" s="3" t="inlineStr">
+      <c r="A213" s="4" t="inlineStr">
+        <is>
+          <t>unitOfMeasure</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>Yields</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
         <is>
           <t>Planning V2 template</t>
         </is>
       </c>
-      <c r="D213" s="3" t="inlineStr"/>
-      <c r="E213" s="3" t="inlineStr">
-        <is>
-          <t>Review required</t>
-        </is>
-      </c>
-      <c r="F213" s="3" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
-        </is>
-      </c>
-      <c r="G213" s="3" t="inlineStr">
+      <c r="D213" s="4" t="inlineStr"/>
+      <c r="E213" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F213" s="4" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
+        </is>
+      </c>
+      <c r="G213" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
         </is>
       </c>
-      <c r="H213" s="3" t="inlineStr"/>
-      <c r="I213" s="3" t="inlineStr"/>
-      <c r="J213" s="3" t="inlineStr">
-        <is>
-          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.DocNum and part/SPL Master evidence also matches; current export needs reconciliation.</t>
+      <c r="H213" s="4" t="inlineStr"/>
+      <c r="I213" s="4" t="inlineStr"/>
+      <c r="J213" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>partType</t>
+          <t>yield</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
@@ -31708,7 +31728,7 @@
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.partType?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
         </is>
       </c>
       <c r="G214" s="4" t="inlineStr">
@@ -31727,12 +31747,12 @@
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>partTypeDescription</t>
+          <t>Secondary TO</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
@@ -31748,7 +31768,7 @@
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeDescription?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary TO?</t>
         </is>
       </c>
       <c r="G215" s="4" t="inlineStr">
@@ -31767,12 +31787,12 @@
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>isReworkable</t>
+          <t>Secondary FROM</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
@@ -31788,7 +31808,7 @@
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.isReworkable?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary FROM?</t>
         </is>
       </c>
       <c r="G216" s="4" t="inlineStr">
@@ -31807,12 +31827,12 @@
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>partNumber</t>
+          <t>Cross TO</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
@@ -31828,7 +31848,7 @@
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross TO?</t>
         </is>
       </c>
       <c r="G217" s="4" t="inlineStr">
@@ -31847,12 +31867,12 @@
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>unitOfMeasure</t>
+          <t>Cross FROM</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
@@ -31868,7 +31888,7 @@
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross FROM?</t>
         </is>
       </c>
       <c r="G218" s="4" t="inlineStr">
@@ -31887,12 +31907,12 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>yield</t>
+          <t>Primary TO</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
@@ -31908,7 +31928,7 @@
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Primary TO?</t>
         </is>
       </c>
       <c r="G219" s="4" t="inlineStr">
@@ -31924,208 +31944,8 @@
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="4" t="inlineStr">
-        <is>
-          <t>Secondary TO</t>
-        </is>
-      </c>
-      <c r="B220" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C220" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D220" s="4" t="inlineStr"/>
-      <c r="E220" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F220" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary TO?</t>
-        </is>
-      </c>
-      <c r="G220" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H220" s="4" t="inlineStr"/>
-      <c r="I220" s="4" t="inlineStr"/>
-      <c r="J220" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="4" t="inlineStr">
-        <is>
-          <t>Secondary FROM</t>
-        </is>
-      </c>
-      <c r="B221" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C221" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D221" s="4" t="inlineStr"/>
-      <c r="E221" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F221" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary FROM?</t>
-        </is>
-      </c>
-      <c r="G221" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H221" s="4" t="inlineStr"/>
-      <c r="I221" s="4" t="inlineStr"/>
-      <c r="J221" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="4" t="inlineStr">
-        <is>
-          <t>Cross TO</t>
-        </is>
-      </c>
-      <c r="B222" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C222" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D222" s="4" t="inlineStr"/>
-      <c r="E222" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F222" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross TO?</t>
-        </is>
-      </c>
-      <c r="G222" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H222" s="4" t="inlineStr"/>
-      <c r="I222" s="4" t="inlineStr"/>
-      <c r="J222" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="4" t="inlineStr">
-        <is>
-          <t>Cross FROM</t>
-        </is>
-      </c>
-      <c r="B223" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C223" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D223" s="4" t="inlineStr"/>
-      <c r="E223" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F223" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross FROM?</t>
-        </is>
-      </c>
-      <c r="G223" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H223" s="4" t="inlineStr"/>
-      <c r="I223" s="4" t="inlineStr"/>
-      <c r="J223" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="4" t="inlineStr">
-        <is>
-          <t>Primary TO</t>
-        </is>
-      </c>
-      <c r="B224" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C224" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D224" s="4" t="inlineStr"/>
-      <c r="E224" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F224" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Primary TO?</t>
-        </is>
-      </c>
-      <c r="G224" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H224" s="4" t="inlineStr"/>
-      <c r="I224" s="4" t="inlineStr"/>
-      <c r="J224" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J224"/>
+  <autoFilter ref="A1:J219"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -32753,7 +32573,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>OrderType; customerCompanyCode; orderStartDatetime; orderStatus; resolvedDateTime; serialNumber; relCompanyId; assignedPersonCode; deviceSerialNumber</t>
+          <t>OrderType; resolvedDateTime; relCompanyId; assignedPersonCode</t>
         </is>
       </c>
     </row>

--- a/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
+++ b/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Target Fields'!$A$1:$S$151</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Template Fields'!$A$1:$H$177</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Evidence'!$A$1:$D$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$J$219</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$J$224</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Output Objects'!$A$1:$E$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Missing Important Fields'!$A$1:$E$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'SAP Investigation Log'!$A$1:$E$10</definedName>
@@ -244,8 +244,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:J219" headerRowCount="1">
-  <autoFilter ref="A1:J219"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:J224" headerRowCount="1">
+  <autoFilter ref="A1:J224"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Field"/>
     <tableColumn id="2" name="Object"/>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>CoCre8 HelpDesk issue tracker:Call Number</t>
+          <t>Stock Audit Report 3Y:Document for DN rows</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -18005,128 +18005,116 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>customerCompanyCode</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="D83" s="4" t="inlineStr">
         <is>
           <t>Canonical header from PartsUsage.xlsx</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>CoCre8 HelpDesk issue tracker:CustomerNormalized/Customer</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr"/>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>orderStartDatetime</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D84" s="4" t="inlineStr">
         <is>
           <t>Canonical header from PartsUsage.xlsx</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>CoCre8 HelpDesk issue tracker:Created</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr"/>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t>orderStatus</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="D85" s="4" t="inlineStr">
         <is>
           <t>Canonical header from PartsUsage.xlsx</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>CoCre8 HelpDesk issue tracker:Status</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr"/>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
@@ -18196,7 +18184,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>CoCre8 HelpDesk issue tracker:DispatchPartNo when present, otherwise Part Nr</t>
+          <t>Stock Audit Report 3Y:Item No.</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -18211,44 +18199,40 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="A88" s="4" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t>serialNumber</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C88" s="4" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="D88" s="4" t="inlineStr">
         <is>
           <t>Canonical header from PartsUsage.xlsx</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>CoCre8 HelpDesk issue tracker:Serial Nr</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr"/>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
@@ -18280,7 +18264,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>CoCre8 HelpDesk issue tracker:Quantity</t>
+          <t>Stock Audit Report 3Y:absolute Quantity for negative DN rows</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -18360,7 +18344,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>CoCre8 HelpDesk issue tracker:Created used as demand/usage date</t>
+          <t>Stock Audit Report 3Y:Posting Date</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -18402,7 +18386,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>CoCre8 HelpDesk issue tracker:DispatchWarehouse</t>
+          <t>Stock Audit Report 3Y:Whse</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -18455,44 +18439,40 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B94" s="4" t="inlineStr">
         <is>
           <t>deviceSerialNumber</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="C94" s="4" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="D94" s="4" t="inlineStr">
         <is>
           <t>Canonical header from PartsUsage.xlsx</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>CoCre8 HelpDesk issue tracker:Serial Nr</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr"/>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
@@ -18520,7 +18500,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>CoCre8 HelpDesk issue tracker:SPLMaster or masters.csv by part</t>
+          <t>Reference masters.csv:SPL Master by used part</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -21969,7 +21949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J219"/>
+  <dimension ref="A1:J224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -29267,7 +29247,7 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>customerCompanyCode</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
@@ -29288,7 +29268,7 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.customerCompanyCode?</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
@@ -29307,7 +29287,7 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>relCompanyId</t>
+          <t>orderStartDatetime</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
@@ -29328,7 +29308,7 @@
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStartDatetime?</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr">
@@ -29347,7 +29327,7 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>assignedPersonCode</t>
+          <t>orderStatus</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
@@ -29368,7 +29348,7 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStatus?</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
@@ -29387,12 +29367,12 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
@@ -29408,7 +29388,7 @@
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr">
@@ -29427,12 +29407,12 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>RequestID</t>
+          <t>serialNumber</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
@@ -29448,7 +29428,7 @@
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.RequestID?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.serialNumber?</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
@@ -29467,12 +29447,12 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>relCompanyId</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
@@ -29488,7 +29468,7 @@
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.location?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr">
@@ -29507,12 +29487,12 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>eta</t>
+          <t>assignedPersonCode</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
@@ -29528,7 +29508,7 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.eta?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
@@ -29547,12 +29527,12 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>actualEta</t>
+          <t>deviceSerialNumber</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
@@ -29568,7 +29548,7 @@
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualEta?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.deviceSerialNumber?</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr">
@@ -29587,7 +29567,7 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>actualResolveDateTime</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
@@ -29608,7 +29588,7 @@
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualResolveDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.orderNumber?</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
@@ -29627,7 +29607,7 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>recallDateTime</t>
+          <t>RequestID</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
@@ -29648,7 +29628,7 @@
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.recallDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.RequestID?</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr">
@@ -29667,7 +29647,7 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>actualRecallDateTime</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
@@ -29688,7 +29668,7 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualRecallDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.location?</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
@@ -29707,7 +29687,7 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>slaEtaClock</t>
+          <t>eta</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
@@ -29728,7 +29708,7 @@
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaClock?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.eta?</t>
         </is>
       </c>
       <c r="G164" s="4" t="inlineStr">
@@ -29747,7 +29727,7 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>slaResolveClock</t>
+          <t>actualEta</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
@@ -29768,7 +29748,7 @@
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveClock?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualEta?</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
@@ -29787,7 +29767,7 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>slaFailureCode</t>
+          <t>actualResolveDateTime</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
@@ -29808,7 +29788,7 @@
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaFailureCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualResolveDateTime?</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr">
@@ -29827,7 +29807,7 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>slaEtaHit</t>
+          <t>recallDateTime</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
@@ -29848,7 +29828,7 @@
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaHit?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.recallDateTime?</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -29867,7 +29847,7 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>slaResolveDateTime</t>
+          <t>actualRecallDateTime</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
@@ -29888,7 +29868,7 @@
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualRecallDateTime?</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr">
@@ -29907,12 +29887,12 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>slaEtaClock</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
@@ -29928,7 +29908,7 @@
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaClock?</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
@@ -29947,12 +29927,12 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>requestId</t>
+          <t>slaResolveClock</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
@@ -29968,7 +29948,7 @@
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.requestId?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveClock?</t>
         </is>
       </c>
       <c r="G170" s="4" t="inlineStr">
@@ -29987,12 +29967,12 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>customerCompanyCode</t>
+          <t>slaFailureCode</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
@@ -30008,7 +29988,7 @@
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.customerCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaFailureCode?</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
@@ -30027,12 +30007,12 @@
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>orderStatus</t>
+          <t>slaEtaHit</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
@@ -30048,7 +30028,7 @@
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaHit?</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr">
@@ -30067,12 +30047,12 @@
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>orderStartDatetime</t>
+          <t>slaResolveDateTime</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
@@ -30088,7 +30068,7 @@
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStartDatetime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveDateTime?</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -30107,7 +30087,7 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>siteCompanyCode</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
@@ -30128,7 +30108,7 @@
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.siteCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderNumber?</t>
         </is>
       </c>
       <c r="G174" s="4" t="inlineStr">
@@ -30147,7 +30127,7 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>repairType</t>
+          <t>requestId</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
@@ -30168,7 +30148,7 @@
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairType?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.requestId?</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
@@ -30187,7 +30167,7 @@
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>partsOrderDateTime</t>
+          <t>customerCompanyCode</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
@@ -30208,7 +30188,7 @@
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsOrderDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.customerCompanyCode?</t>
         </is>
       </c>
       <c r="G176" s="4" t="inlineStr">
@@ -30227,7 +30207,7 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>partsReceivedDateTime</t>
+          <t>orderStatus</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
@@ -30248,7 +30228,7 @@
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsReceivedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStatus?</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
@@ -30267,7 +30247,7 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>repairCode</t>
+          <t>orderStartDatetime</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
@@ -30288,7 +30268,7 @@
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStartDatetime?</t>
         </is>
       </c>
       <c r="G178" s="4" t="inlineStr">
@@ -30307,7 +30287,7 @@
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>repairCompany</t>
+          <t>siteCompanyCode</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
@@ -30328,7 +30308,7 @@
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCompany?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.siteCompanyCode?</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
@@ -30347,7 +30327,7 @@
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>raStatus</t>
+          <t>repairType</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
@@ -30368,7 +30348,7 @@
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.raStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairType?</t>
         </is>
       </c>
       <c r="G180" s="4" t="inlineStr">
@@ -30387,7 +30367,7 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>partsOrderDateTime</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
@@ -30408,7 +30388,7 @@
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.Warehouse?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsOrderDateTime?</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
@@ -30427,7 +30407,7 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>assignedPerson</t>
+          <t>partsReceivedDateTime</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
@@ -30448,7 +30428,7 @@
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.assignedPerson?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsReceivedDateTime?</t>
         </is>
       </c>
       <c r="G182" s="4" t="inlineStr">
@@ -30467,7 +30447,7 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>repairCode</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
@@ -30488,7 +30468,7 @@
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.resolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCode?</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
@@ -30507,7 +30487,7 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>serialNumber</t>
+          <t>repairCompany</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
@@ -30528,7 +30508,7 @@
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.serialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCompany?</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr">
@@ -30547,7 +30527,7 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>quantityUsed</t>
+          <t>raStatus</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
@@ -30568,7 +30548,7 @@
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.quantityUsed?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.raStatus?</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr">
@@ -30587,7 +30567,7 @@
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>deviceSerialNumber</t>
+          <t>Warehouse</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
@@ -30608,7 +30588,7 @@
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.deviceSerialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.Warehouse?</t>
         </is>
       </c>
       <c r="G186" s="4" t="inlineStr">
@@ -30627,7 +30607,7 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>orderedPartId</t>
+          <t>assignedPerson</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
@@ -30648,7 +30628,7 @@
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderedPartId?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.assignedPerson?</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr">
@@ -30667,7 +30647,7 @@
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>actualPartId</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
@@ -30688,7 +30668,7 @@
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.actualPartId?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.resolvedDateTime?</t>
         </is>
       </c>
       <c r="G188" s="4" t="inlineStr">
@@ -30707,12 +30687,12 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>serialNumber</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
@@ -30728,7 +30708,7 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.serialNumber?</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr">
@@ -30747,12 +30727,12 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>quantityUsed</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
@@ -30768,7 +30748,7 @@
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.cost?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.quantityUsed?</t>
         </is>
       </c>
       <c r="G190" s="4" t="inlineStr">
@@ -30787,12 +30767,12 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>currencyCode</t>
+          <t>deviceSerialNumber</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
@@ -30808,7 +30788,7 @@
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.currencyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.deviceSerialNumber?</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -30827,12 +30807,12 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>averageCost</t>
+          <t>orderedPartId</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
@@ -30848,7 +30828,7 @@
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.averageCost?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderedPartId?</t>
         </is>
       </c>
       <c r="G192" s="4" t="inlineStr">
@@ -30867,12 +30847,12 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>actualPartId</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
@@ -30888,7 +30868,7 @@
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.actualPartId?</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -30907,12 +30887,12 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>modelCode</t>
+          <t>partCode</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
@@ -30928,7 +30908,7 @@
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.partCode?</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr">
@@ -30947,12 +30927,12 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>modelDescription</t>
+          <t>cost</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -30968,7 +30948,7 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.cost?</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -30987,12 +30967,12 @@
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>inventoryTransferImoId</t>
+          <t>currencyCode</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
@@ -31008,7 +30988,7 @@
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.inventoryTransferImoId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.currencyCode?</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr">
@@ -31027,12 +31007,12 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>createdDateTime</t>
+          <t>averageCost</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
@@ -31048,7 +31028,7 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.createdDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.averageCost?</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
@@ -31067,12 +31047,12 @@
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>completedDateTime</t>
+          <t>partCode</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
@@ -31088,7 +31068,7 @@
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.completedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr">
@@ -31107,12 +31087,12 @@
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>fromWarehouseId</t>
+          <t>modelCode</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
@@ -31128,7 +31108,7 @@
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.fromWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
@@ -31147,12 +31127,12 @@
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>toWarehouseId</t>
+          <t>modelDescription</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
@@ -31168,7 +31148,7 @@
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.toWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr">
@@ -31187,7 +31167,7 @@
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>demandStatus</t>
+          <t>inventoryTransferImoId</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
@@ -31208,7 +31188,7 @@
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.demandStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.inventoryTransferImoId?</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
@@ -31227,7 +31207,7 @@
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>orderStatusIsClosed</t>
+          <t>createdDateTime</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
@@ -31248,7 +31228,7 @@
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.orderStatusIsClosed?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.createdDateTime?</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr">
@@ -31267,7 +31247,7 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>movementType</t>
+          <t>completedDateTime</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
@@ -31288,7 +31268,7 @@
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.completedDateTime?</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -31307,7 +31287,7 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>addressId</t>
+          <t>fromWarehouseId</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
@@ -31328,7 +31308,7 @@
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.fromWarehouseId?</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr">
@@ -31347,7 +31327,7 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>Bpart</t>
+          <t>toWarehouseId</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
@@ -31368,7 +31348,7 @@
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.Bpart?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.toWarehouseId?</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -31387,7 +31367,7 @@
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>demandStatus</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
@@ -31408,7 +31388,7 @@
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.quantity?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.demandStatus?</t>
         </is>
       </c>
       <c r="G206" s="4" t="inlineStr">
@@ -31427,7 +31407,7 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>shipListCode</t>
+          <t>orderStatusIsClosed</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
@@ -31448,7 +31428,7 @@
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.orderStatusIsClosed?</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -31465,54 +31445,54 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="3" t="inlineStr">
-        <is>
-          <t>demandStatus</t>
-        </is>
-      </c>
-      <c r="B208" s="3" t="inlineStr">
-        <is>
-          <t>PurchaseOrders</t>
-        </is>
-      </c>
-      <c r="C208" s="3" t="inlineStr">
+      <c r="A208" s="4" t="inlineStr">
+        <is>
+          <t>movementType</t>
+        </is>
+      </c>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>InventoryTransfers</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
         <is>
           <t>Planning V2 template</t>
         </is>
       </c>
-      <c r="D208" s="3" t="inlineStr"/>
-      <c r="E208" s="3" t="inlineStr">
-        <is>
-          <t>Review required</t>
-        </is>
-      </c>
-      <c r="F208" s="3" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
-        </is>
-      </c>
-      <c r="G208" s="3" t="inlineStr">
+      <c r="D208" s="4" t="inlineStr"/>
+      <c r="E208" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F208" s="4" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
+        </is>
+      </c>
+      <c r="G208" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
         </is>
       </c>
-      <c r="H208" s="3" t="inlineStr"/>
-      <c r="I208" s="3" t="inlineStr"/>
-      <c r="J208" s="3" t="inlineStr">
-        <is>
-          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.DocNum and part/SPL Master evidence also matches; current export needs reconciliation.</t>
+      <c r="H208" s="4" t="inlineStr"/>
+      <c r="I208" s="4" t="inlineStr"/>
+      <c r="J208" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>partType</t>
+          <t>addressId</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
@@ -31528,7 +31508,7 @@
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.partType?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr">
@@ -31547,12 +31527,12 @@
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>partTypeDescription</t>
+          <t>Bpart</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
@@ -31568,7 +31548,7 @@
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeDescription?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.Bpart?</t>
         </is>
       </c>
       <c r="G210" s="4" t="inlineStr">
@@ -31587,12 +31567,12 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>isReworkable</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
@@ -31608,7 +31588,7 @@
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.isReworkable?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.quantity?</t>
         </is>
       </c>
       <c r="G211" s="4" t="inlineStr">
@@ -31627,12 +31607,12 @@
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>partNumber</t>
+          <t>shipListCode</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
@@ -31648,7 +31628,7 @@
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
         </is>
       </c>
       <c r="G212" s="4" t="inlineStr">
@@ -31665,54 +31645,54 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="4" t="inlineStr">
-        <is>
-          <t>unitOfMeasure</t>
-        </is>
-      </c>
-      <c r="B213" s="4" t="inlineStr">
-        <is>
-          <t>Yields</t>
-        </is>
-      </c>
-      <c r="C213" s="4" t="inlineStr">
+      <c r="A213" s="3" t="inlineStr">
+        <is>
+          <t>demandStatus</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>PurchaseOrders</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
         <is>
           <t>Planning V2 template</t>
         </is>
       </c>
-      <c r="D213" s="4" t="inlineStr"/>
-      <c r="E213" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F213" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
-        </is>
-      </c>
-      <c r="G213" s="4" t="inlineStr">
+      <c r="D213" s="3" t="inlineStr"/>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="F213" s="3" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
+        </is>
+      </c>
+      <c r="G213" s="3" t="inlineStr">
         <is>
           <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
         </is>
       </c>
-      <c r="H213" s="4" t="inlineStr"/>
-      <c r="I213" s="4" t="inlineStr"/>
-      <c r="J213" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="H213" s="3" t="inlineStr"/>
+      <c r="I213" s="3" t="inlineStr"/>
+      <c r="J213" s="3" t="inlineStr">
+        <is>
+          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.DocNum and part/SPL Master evidence also matches; current export needs reconciliation.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>yield</t>
+          <t>partType</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
@@ -31728,7 +31708,7 @@
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.partType?</t>
         </is>
       </c>
       <c r="G214" s="4" t="inlineStr">
@@ -31747,12 +31727,12 @@
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>Secondary TO</t>
+          <t>partTypeDescription</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>WarehouseExclusions</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
@@ -31768,7 +31748,7 @@
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary TO?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeDescription?</t>
         </is>
       </c>
       <c r="G215" s="4" t="inlineStr">
@@ -31787,12 +31767,12 @@
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>Secondary FROM</t>
+          <t>isReworkable</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>WarehouseExclusions</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
@@ -31808,7 +31788,7 @@
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary FROM?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.isReworkable?</t>
         </is>
       </c>
       <c r="G216" s="4" t="inlineStr">
@@ -31827,12 +31807,12 @@
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>Cross TO</t>
+          <t>partNumber</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>WarehouseExclusions</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
@@ -31848,7 +31828,7 @@
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross TO?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
         </is>
       </c>
       <c r="G217" s="4" t="inlineStr">
@@ -31867,12 +31847,12 @@
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>Cross FROM</t>
+          <t>unitOfMeasure</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>WarehouseExclusions</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
@@ -31888,7 +31868,7 @@
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross FROM?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
         </is>
       </c>
       <c r="G218" s="4" t="inlineStr">
@@ -31907,12 +31887,12 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>Primary TO</t>
+          <t>yield</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>WarehouseExclusions</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
@@ -31928,7 +31908,7 @@
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Primary TO?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
         </is>
       </c>
       <c r="G219" s="4" t="inlineStr">
@@ -31944,8 +31924,208 @@
         </is>
       </c>
     </row>
+    <row r="220">
+      <c r="A220" s="4" t="inlineStr">
+        <is>
+          <t>Secondary TO</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t>WarehouseExclusions</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>Planning V2 template</t>
+        </is>
+      </c>
+      <c r="D220" s="4" t="inlineStr"/>
+      <c r="E220" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F220" s="4" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary TO?</t>
+        </is>
+      </c>
+      <c r="G220" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
+        </is>
+      </c>
+      <c r="H220" s="4" t="inlineStr"/>
+      <c r="I220" s="4" t="inlineStr"/>
+      <c r="J220" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="inlineStr">
+        <is>
+          <t>Secondary FROM</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t>WarehouseExclusions</t>
+        </is>
+      </c>
+      <c r="C221" s="4" t="inlineStr">
+        <is>
+          <t>Planning V2 template</t>
+        </is>
+      </c>
+      <c r="D221" s="4" t="inlineStr"/>
+      <c r="E221" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F221" s="4" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary FROM?</t>
+        </is>
+      </c>
+      <c r="G221" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
+        </is>
+      </c>
+      <c r="H221" s="4" t="inlineStr"/>
+      <c r="I221" s="4" t="inlineStr"/>
+      <c r="J221" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="4" t="inlineStr">
+        <is>
+          <t>Cross TO</t>
+        </is>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>WarehouseExclusions</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t>Planning V2 template</t>
+        </is>
+      </c>
+      <c r="D222" s="4" t="inlineStr"/>
+      <c r="E222" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F222" s="4" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross TO?</t>
+        </is>
+      </c>
+      <c r="G222" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
+        </is>
+      </c>
+      <c r="H222" s="4" t="inlineStr"/>
+      <c r="I222" s="4" t="inlineStr"/>
+      <c r="J222" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="4" t="inlineStr">
+        <is>
+          <t>Cross FROM</t>
+        </is>
+      </c>
+      <c r="B223" s="4" t="inlineStr">
+        <is>
+          <t>WarehouseExclusions</t>
+        </is>
+      </c>
+      <c r="C223" s="4" t="inlineStr">
+        <is>
+          <t>Planning V2 template</t>
+        </is>
+      </c>
+      <c r="D223" s="4" t="inlineStr"/>
+      <c r="E223" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F223" s="4" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross FROM?</t>
+        </is>
+      </c>
+      <c r="G223" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
+        </is>
+      </c>
+      <c r="H223" s="4" t="inlineStr"/>
+      <c r="I223" s="4" t="inlineStr"/>
+      <c r="J223" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="inlineStr">
+        <is>
+          <t>Primary TO</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t>WarehouseExclusions</t>
+        </is>
+      </c>
+      <c r="C224" s="4" t="inlineStr">
+        <is>
+          <t>Planning V2 template</t>
+        </is>
+      </c>
+      <c r="D224" s="4" t="inlineStr"/>
+      <c r="E224" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F224" s="4" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Primary TO?</t>
+        </is>
+      </c>
+      <c r="G224" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
+        </is>
+      </c>
+      <c r="H224" s="4" t="inlineStr"/>
+      <c r="I224" s="4" t="inlineStr"/>
+      <c r="J224" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J219"/>
+  <autoFilter ref="A1:J224"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -32573,7 +32753,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>OrderType; resolvedDateTime; relCompanyId; assignedPersonCode</t>
+          <t>OrderType; customerCompanyCode; orderStartDatetime; orderStatus; resolvedDateTime; serialNumber; relCompanyId; assignedPersonCode; deviceSerialNumber</t>
         </is>
       </c>
     </row>

--- a/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
+++ b/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Target Fields'!$A$1:$S$151</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Template Fields'!$A$1:$H$177</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Evidence'!$A$1:$D$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$J$224</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$J$221</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Output Objects'!$A$1:$E$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Missing Important Fields'!$A$1:$E$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'SAP Investigation Log'!$A$1:$E$10</definedName>
@@ -244,8 +244,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:J224" headerRowCount="1">
-  <autoFilter ref="A1:J224"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:J221" headerRowCount="1">
+  <autoFilter ref="A1:J221"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Field"/>
     <tableColumn id="2" name="Object"/>
@@ -8139,12 +8139,12 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>Manual SAP stock audit report</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report</t>
+          <t>ODLN/DLN1 Delivery Notes</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
       <c r="R81" s="2" t="inlineStr"/>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>Usage is allowed from the manually generated SAP Stock Audit Report; work-order linkage may need SAP verification.</t>
+          <t>Delivery Notes are the source of truth for actual part usage; call/customer/serial values are enriched from ODLN.NumAtCard and ODLN.Comments when present.</t>
         </is>
       </c>
     </row>
@@ -8228,12 +8228,12 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>Manual SAP stock audit report</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report</t>
+          <t>ODLN/DLN1 Delivery Notes</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -8255,7 +8255,7 @@
       <c r="R82" s="2" t="inlineStr"/>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>Usage is allowed from the manually generated SAP Stock Audit Report; work-order linkage may need SAP verification.</t>
+          <t>Delivery Notes are the source of truth for actual part usage; call/customer/serial values are enriched from ODLN.NumAtCard and ODLN.Comments when present.</t>
         </is>
       </c>
     </row>
@@ -8317,12 +8317,12 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>Manual SAP stock audit report</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report</t>
+          <t>ODLN/DLN1 Delivery Notes</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -8344,7 +8344,7 @@
       <c r="R83" s="2" t="inlineStr"/>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>Usage is allowed from the manually generated SAP Stock Audit Report; work-order linkage may need SAP verification.</t>
+          <t>Delivery Notes are the source of truth for actual part usage; call/customer/serial values are enriched from ODLN.NumAtCard and ODLN.Comments when present.</t>
         </is>
       </c>
     </row>
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>Manual SAP stock audit report</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report</t>
+          <t>ODLN/DLN1 Delivery Notes</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -8530,7 +8530,7 @@
       <c r="R85" s="2" t="inlineStr"/>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>Usage is allowed from the manually generated SAP Stock Audit Report; work-order linkage may need SAP verification.</t>
+          <t>Delivery Notes are the source of truth for actual part usage; call/customer/serial values are enriched from ODLN.NumAtCard and ODLN.Comments when present.</t>
         </is>
       </c>
     </row>
@@ -8685,12 +8685,12 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>Manual SAP stock audit report</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report</t>
+          <t>ODLN/DLN1 Delivery Notes</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -8712,7 +8712,7 @@
       <c r="R87" s="2" t="inlineStr"/>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>Usage is allowed from the manually generated SAP Stock Audit Report; work-order linkage may need SAP verification.</t>
+          <t>Delivery Notes are the source of truth for actual part usage; call/customer/serial values are enriched from ODLN.NumAtCard and ODLN.Comments when present.</t>
         </is>
       </c>
     </row>
@@ -8774,12 +8774,12 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>Manual SAP stock audit report</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report</t>
+          <t>ODLN/DLN1 Delivery Notes</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       <c r="R88" s="2" t="inlineStr"/>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>Usage is allowed from the manually generated SAP Stock Audit Report; work-order linkage may need SAP verification.</t>
+          <t>Delivery Notes are the source of truth for actual part usage; call/customer/serial values are enriched from ODLN.NumAtCard and ODLN.Comments when present.</t>
         </is>
       </c>
     </row>
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>Manual SAP stock audit report</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report</t>
+          <t>ODLN/DLN1 Delivery Notes</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -8991,7 +8991,7 @@
       <c r="R90" s="2" t="inlineStr"/>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>Usage is allowed from the manually generated SAP Stock Audit Report; work-order linkage may need SAP verification.</t>
+          <t>Delivery Notes are the source of truth for actual part usage; call/customer/serial values are enriched from ODLN.NumAtCard and ODLN.Comments when present.</t>
         </is>
       </c>
     </row>
@@ -9053,12 +9053,12 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Manual SAP stock audit report</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report</t>
+          <t>ODLN/DLN1 Delivery Notes</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -9084,7 +9084,7 @@
       <c r="R91" s="2" t="inlineStr"/>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>Usage is allowed from the manually generated SAP Stock Audit Report; work-order linkage may need SAP verification.</t>
+          <t>Delivery Notes are the source of truth for actual part usage; call/customer/serial values are enriched from ODLN.NumAtCard and ODLN.Comments when present.</t>
         </is>
       </c>
     </row>
@@ -9146,12 +9146,12 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>Manual SAP stock audit report</t>
+          <t>SAP Service Layer</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report</t>
+          <t>ODLN/DLN1 Delivery Notes</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -9177,7 +9177,7 @@
       <c r="R92" s="2" t="inlineStr"/>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>Usage is allowed from the manually generated SAP Stock Audit Report; work-order linkage may need SAP verification.</t>
+          <t>Delivery Notes are the source of truth for actual part usage; call/customer/serial values are enriched from ODLN.NumAtCard and ODLN.Comments when present.</t>
         </is>
       </c>
     </row>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report 3Y:Document for DN rows</t>
+          <t>SAP Service Layer SQLQueries:ODLN.NumAtCard or parsed Call Nr from ODLN.Comments</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -18005,40 +18005,44 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>customerCompanyCode</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Canonical header from PartsUsage.xlsx</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr"/>
-      <c r="G83" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>SAP Service Layer SQLQueries:parsed Customer from ODLN.Comments where present</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -18184,7 +18188,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report 3Y:Item No.</t>
+          <t>SAP Service Layer SQLQueries:DLN1.ItemCode actual delivered part</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -18199,40 +18203,44 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B88" s="4" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>serialNumber</t>
         </is>
       </c>
-      <c r="C88" s="4" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D88" s="4" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Canonical header from PartsUsage.xlsx</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr"/>
-      <c r="G88" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>SAP Service Layer SQLQueries:parsed Serial number from ODLN.Comments where present</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -18264,7 +18272,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report 3Y:absolute Quantity for negative DN rows</t>
+          <t>SAP Service Layer SQLQueries:DLN1.Quantity</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -18344,7 +18352,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report 3Y:Posting Date</t>
+          <t>SAP Service Layer SQLQueries:ODLN.DocDate</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -18386,7 +18394,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Stock Audit Report 3Y:Whse</t>
+          <t>SAP Service Layer SQLQueries:DLN1.WhsCode</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -18439,40 +18447,44 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B94" s="4" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>deviceSerialNumber</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr">
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Canonical header from PartsUsage.xlsx</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr"/>
-      <c r="G94" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>SAP Service Layer SQLQueries:parsed Serial number from ODLN.Comments where present</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -21949,7 +21961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J224"/>
+  <dimension ref="A1:J221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -29247,7 +29259,7 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>customerCompanyCode</t>
+          <t>orderStartDatetime</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
@@ -29268,7 +29280,7 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.customerCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStartDatetime?</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
@@ -29287,7 +29299,7 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>orderStartDatetime</t>
+          <t>orderStatus</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
@@ -29308,7 +29320,7 @@
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStartDatetime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStatus?</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr">
@@ -29327,7 +29339,7 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>orderStatus</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
@@ -29348,7 +29360,7 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
@@ -29367,7 +29379,7 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>relCompanyId</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
@@ -29388,7 +29400,7 @@
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr">
@@ -29407,7 +29419,7 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>serialNumber</t>
+          <t>assignedPersonCode</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
@@ -29428,7 +29440,7 @@
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.serialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
@@ -29447,12 +29459,12 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>relCompanyId</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
@@ -29468,7 +29480,7 @@
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.orderNumber?</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr">
@@ -29487,12 +29499,12 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>assignedPersonCode</t>
+          <t>RequestID</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
@@ -29508,7 +29520,7 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.RequestID?</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
@@ -29527,12 +29539,12 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>deviceSerialNumber</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
@@ -29548,7 +29560,7 @@
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.deviceSerialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.location?</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr">
@@ -29567,7 +29579,7 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>eta</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
@@ -29588,7 +29600,7 @@
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.eta?</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
@@ -29607,7 +29619,7 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>RequestID</t>
+          <t>actualEta</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
@@ -29628,7 +29640,7 @@
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.RequestID?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualEta?</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr">
@@ -29647,7 +29659,7 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>actualResolveDateTime</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
@@ -29668,7 +29680,7 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.location?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualResolveDateTime?</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
@@ -29687,7 +29699,7 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>eta</t>
+          <t>recallDateTime</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
@@ -29708,7 +29720,7 @@
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.eta?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.recallDateTime?</t>
         </is>
       </c>
       <c r="G164" s="4" t="inlineStr">
@@ -29727,7 +29739,7 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>actualEta</t>
+          <t>actualRecallDateTime</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
@@ -29748,7 +29760,7 @@
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualEta?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualRecallDateTime?</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
@@ -29767,7 +29779,7 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>actualResolveDateTime</t>
+          <t>slaEtaClock</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
@@ -29788,7 +29800,7 @@
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualResolveDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaClock?</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr">
@@ -29807,7 +29819,7 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>recallDateTime</t>
+          <t>slaResolveClock</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
@@ -29828,7 +29840,7 @@
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.recallDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveClock?</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -29847,7 +29859,7 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>actualRecallDateTime</t>
+          <t>slaFailureCode</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
@@ -29868,7 +29880,7 @@
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualRecallDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaFailureCode?</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr">
@@ -29887,7 +29899,7 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>slaEtaClock</t>
+          <t>slaEtaHit</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
@@ -29908,7 +29920,7 @@
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaClock?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaHit?</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
@@ -29927,7 +29939,7 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>slaResolveClock</t>
+          <t>slaResolveDateTime</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
@@ -29948,7 +29960,7 @@
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveClock?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveDateTime?</t>
         </is>
       </c>
       <c r="G170" s="4" t="inlineStr">
@@ -29967,12 +29979,12 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>slaFailureCode</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
@@ -29988,7 +30000,7 @@
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaFailureCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderNumber?</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
@@ -30007,12 +30019,12 @@
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>slaEtaHit</t>
+          <t>requestId</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
@@ -30028,7 +30040,7 @@
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaHit?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.requestId?</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr">
@@ -30047,12 +30059,12 @@
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>slaResolveDateTime</t>
+          <t>customerCompanyCode</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
@@ -30068,7 +30080,7 @@
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.customerCompanyCode?</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -30087,7 +30099,7 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>orderStatus</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
@@ -30108,7 +30120,7 @@
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStatus?</t>
         </is>
       </c>
       <c r="G174" s="4" t="inlineStr">
@@ -30127,7 +30139,7 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>requestId</t>
+          <t>orderStartDatetime</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
@@ -30148,7 +30160,7 @@
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.requestId?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStartDatetime?</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
@@ -30167,7 +30179,7 @@
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>customerCompanyCode</t>
+          <t>siteCompanyCode</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
@@ -30188,7 +30200,7 @@
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.customerCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.siteCompanyCode?</t>
         </is>
       </c>
       <c r="G176" s="4" t="inlineStr">
@@ -30207,7 +30219,7 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>orderStatus</t>
+          <t>repairType</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
@@ -30228,7 +30240,7 @@
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairType?</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
@@ -30247,7 +30259,7 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>orderStartDatetime</t>
+          <t>partsOrderDateTime</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
@@ -30268,7 +30280,7 @@
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStartDatetime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsOrderDateTime?</t>
         </is>
       </c>
       <c r="G178" s="4" t="inlineStr">
@@ -30287,7 +30299,7 @@
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>siteCompanyCode</t>
+          <t>partsReceivedDateTime</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
@@ -30308,7 +30320,7 @@
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.siteCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsReceivedDateTime?</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
@@ -30327,7 +30339,7 @@
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>repairType</t>
+          <t>repairCode</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
@@ -30348,7 +30360,7 @@
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairType?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCode?</t>
         </is>
       </c>
       <c r="G180" s="4" t="inlineStr">
@@ -30367,7 +30379,7 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>partsOrderDateTime</t>
+          <t>repairCompany</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
@@ -30388,7 +30400,7 @@
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsOrderDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCompany?</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
@@ -30407,7 +30419,7 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>partsReceivedDateTime</t>
+          <t>raStatus</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
@@ -30428,7 +30440,7 @@
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsReceivedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.raStatus?</t>
         </is>
       </c>
       <c r="G182" s="4" t="inlineStr">
@@ -30447,7 +30459,7 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>repairCode</t>
+          <t>Warehouse</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
@@ -30468,7 +30480,7 @@
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.Warehouse?</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
@@ -30487,7 +30499,7 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>repairCompany</t>
+          <t>assignedPerson</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
@@ -30508,7 +30520,7 @@
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCompany?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.assignedPerson?</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr">
@@ -30527,7 +30539,7 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>raStatus</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
@@ -30548,7 +30560,7 @@
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.raStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.resolvedDateTime?</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr">
@@ -30567,7 +30579,7 @@
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>serialNumber</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
@@ -30588,7 +30600,7 @@
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.Warehouse?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.serialNumber?</t>
         </is>
       </c>
       <c r="G186" s="4" t="inlineStr">
@@ -30607,7 +30619,7 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>assignedPerson</t>
+          <t>quantityUsed</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
@@ -30628,7 +30640,7 @@
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.assignedPerson?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.quantityUsed?</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr">
@@ -30647,7 +30659,7 @@
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>deviceSerialNumber</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
@@ -30668,7 +30680,7 @@
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.resolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.deviceSerialNumber?</t>
         </is>
       </c>
       <c r="G188" s="4" t="inlineStr">
@@ -30687,7 +30699,7 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>serialNumber</t>
+          <t>orderedPartId</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
@@ -30708,7 +30720,7 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.serialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderedPartId?</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr">
@@ -30727,7 +30739,7 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>quantityUsed</t>
+          <t>actualPartId</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
@@ -30748,7 +30760,7 @@
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.quantityUsed?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.actualPartId?</t>
         </is>
       </c>
       <c r="G190" s="4" t="inlineStr">
@@ -30767,12 +30779,12 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>deviceSerialNumber</t>
+          <t>partCode</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
@@ -30788,7 +30800,7 @@
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.deviceSerialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.partCode?</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -30807,12 +30819,12 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>orderedPartId</t>
+          <t>cost</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
@@ -30828,7 +30840,7 @@
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderedPartId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.cost?</t>
         </is>
       </c>
       <c r="G192" s="4" t="inlineStr">
@@ -30847,12 +30859,12 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>actualPartId</t>
+          <t>currencyCode</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>PartCost</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
@@ -30868,7 +30880,7 @@
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.actualPartId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.currencyCode?</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -30887,7 +30899,7 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>averageCost</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
@@ -30908,7 +30920,7 @@
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartCost.averageCost?</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr">
@@ -30927,12 +30939,12 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>partCode</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -30948,7 +30960,7 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.cost?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -30967,12 +30979,12 @@
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>currencyCode</t>
+          <t>modelCode</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
@@ -30988,7 +31000,7 @@
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.currencyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr">
@@ -31007,12 +31019,12 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>averageCost</t>
+          <t>modelDescription</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
@@ -31028,7 +31040,7 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.averageCost?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
@@ -31047,12 +31059,12 @@
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>inventoryTransferImoId</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
@@ -31068,7 +31080,7 @@
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.inventoryTransferImoId?</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr">
@@ -31087,12 +31099,12 @@
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>modelCode</t>
+          <t>createdDateTime</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
@@ -31108,7 +31120,7 @@
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.createdDateTime?</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
@@ -31127,12 +31139,12 @@
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>modelDescription</t>
+          <t>completedDateTime</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
@@ -31148,7 +31160,7 @@
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.completedDateTime?</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr">
@@ -31167,7 +31179,7 @@
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>inventoryTransferImoId</t>
+          <t>fromWarehouseId</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
@@ -31188,7 +31200,7 @@
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.inventoryTransferImoId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.fromWarehouseId?</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
@@ -31207,7 +31219,7 @@
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>createdDateTime</t>
+          <t>toWarehouseId</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
@@ -31228,7 +31240,7 @@
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.createdDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.toWarehouseId?</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr">
@@ -31247,7 +31259,7 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>completedDateTime</t>
+          <t>demandStatus</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
@@ -31268,7 +31280,7 @@
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.completedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.demandStatus?</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -31287,7 +31299,7 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>fromWarehouseId</t>
+          <t>orderStatusIsClosed</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
@@ -31308,7 +31320,7 @@
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.fromWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.orderStatusIsClosed?</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr">
@@ -31327,7 +31339,7 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>toWarehouseId</t>
+          <t>movementType</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
@@ -31348,7 +31360,7 @@
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.toWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -31367,7 +31379,7 @@
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>demandStatus</t>
+          <t>addressId</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
@@ -31388,7 +31400,7 @@
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.demandStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
         </is>
       </c>
       <c r="G206" s="4" t="inlineStr">
@@ -31407,7 +31419,7 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>orderStatusIsClosed</t>
+          <t>Bpart</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
@@ -31428,7 +31440,7 @@
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.orderStatusIsClosed?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.Bpart?</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -31447,7 +31459,7 @@
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>movementType</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
@@ -31468,7 +31480,7 @@
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.quantity?</t>
         </is>
       </c>
       <c r="G208" s="4" t="inlineStr">
@@ -31487,7 +31499,7 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>addressId</t>
+          <t>shipListCode</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
@@ -31508,7 +31520,7 @@
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr">
@@ -31525,54 +31537,54 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="4" t="inlineStr">
-        <is>
-          <t>Bpart</t>
-        </is>
-      </c>
-      <c r="B210" s="4" t="inlineStr">
-        <is>
-          <t>InventoryTransfers</t>
-        </is>
-      </c>
-      <c r="C210" s="4" t="inlineStr">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>demandStatus</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>PurchaseOrders</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
         <is>
           <t>Planning V2 template</t>
         </is>
       </c>
-      <c r="D210" s="4" t="inlineStr"/>
-      <c r="E210" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F210" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.Bpart?</t>
-        </is>
-      </c>
-      <c r="G210" s="4" t="inlineStr">
+      <c r="D210" s="3" t="inlineStr"/>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="F210" s="3" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
+        </is>
+      </c>
+      <c r="G210" s="3" t="inlineStr">
         <is>
           <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
         </is>
       </c>
-      <c r="H210" s="4" t="inlineStr"/>
-      <c r="I210" s="4" t="inlineStr"/>
-      <c r="J210" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="H210" s="3" t="inlineStr"/>
+      <c r="I210" s="3" t="inlineStr"/>
+      <c r="J210" s="3" t="inlineStr">
+        <is>
+          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.DocNum and part/SPL Master evidence also matches; current export needs reconciliation.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>partType</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
@@ -31588,7 +31600,7 @@
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.quantity?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.partType?</t>
         </is>
       </c>
       <c r="G211" s="4" t="inlineStr">
@@ -31607,12 +31619,12 @@
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>shipListCode</t>
+          <t>partTypeDescription</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
@@ -31628,7 +31640,7 @@
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeDescription?</t>
         </is>
       </c>
       <c r="G212" s="4" t="inlineStr">
@@ -31645,54 +31657,54 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="3" t="inlineStr">
-        <is>
-          <t>demandStatus</t>
-        </is>
-      </c>
-      <c r="B213" s="3" t="inlineStr">
-        <is>
-          <t>PurchaseOrders</t>
-        </is>
-      </c>
-      <c r="C213" s="3" t="inlineStr">
+      <c r="A213" s="4" t="inlineStr">
+        <is>
+          <t>isReworkable</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>PartTypes</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
         <is>
           <t>Planning V2 template</t>
         </is>
       </c>
-      <c r="D213" s="3" t="inlineStr"/>
-      <c r="E213" s="3" t="inlineStr">
-        <is>
-          <t>Review required</t>
-        </is>
-      </c>
-      <c r="F213" s="3" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
-        </is>
-      </c>
-      <c r="G213" s="3" t="inlineStr">
+      <c r="D213" s="4" t="inlineStr"/>
+      <c r="E213" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F213" s="4" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.isReworkable?</t>
+        </is>
+      </c>
+      <c r="G213" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
         </is>
       </c>
-      <c r="H213" s="3" t="inlineStr"/>
-      <c r="I213" s="3" t="inlineStr"/>
-      <c r="J213" s="3" t="inlineStr">
-        <is>
-          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.DocNum and part/SPL Master evidence also matches; current export needs reconciliation.</t>
+      <c r="H213" s="4" t="inlineStr"/>
+      <c r="I213" s="4" t="inlineStr"/>
+      <c r="J213" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>partType</t>
+          <t>partNumber</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
@@ -31708,7 +31720,7 @@
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.partType?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
         </is>
       </c>
       <c r="G214" s="4" t="inlineStr">
@@ -31727,12 +31739,12 @@
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>partTypeDescription</t>
+          <t>unitOfMeasure</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
@@ -31748,7 +31760,7 @@
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeDescription?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
         </is>
       </c>
       <c r="G215" s="4" t="inlineStr">
@@ -31767,12 +31779,12 @@
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>isReworkable</t>
+          <t>yield</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
@@ -31788,7 +31800,7 @@
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.isReworkable?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
         </is>
       </c>
       <c r="G216" s="4" t="inlineStr">
@@ -31807,12 +31819,12 @@
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>partNumber</t>
+          <t>Secondary TO</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
@@ -31828,7 +31840,7 @@
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary TO?</t>
         </is>
       </c>
       <c r="G217" s="4" t="inlineStr">
@@ -31847,12 +31859,12 @@
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>unitOfMeasure</t>
+          <t>Secondary FROM</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
@@ -31868,7 +31880,7 @@
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary FROM?</t>
         </is>
       </c>
       <c r="G218" s="4" t="inlineStr">
@@ -31887,12 +31899,12 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>yield</t>
+          <t>Cross TO</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
@@ -31908,7 +31920,7 @@
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross TO?</t>
         </is>
       </c>
       <c r="G219" s="4" t="inlineStr">
@@ -31927,7 +31939,7 @@
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>Secondary TO</t>
+          <t>Cross FROM</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
@@ -31948,7 +31960,7 @@
       </c>
       <c r="F220" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary TO?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross FROM?</t>
         </is>
       </c>
       <c r="G220" s="4" t="inlineStr">
@@ -31967,7 +31979,7 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>Secondary FROM</t>
+          <t>Primary TO</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
@@ -31988,7 +32000,7 @@
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary FROM?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Primary TO?</t>
         </is>
       </c>
       <c r="G221" s="4" t="inlineStr">
@@ -32004,128 +32016,8 @@
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="4" t="inlineStr">
-        <is>
-          <t>Cross TO</t>
-        </is>
-      </c>
-      <c r="B222" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C222" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D222" s="4" t="inlineStr"/>
-      <c r="E222" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F222" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross TO?</t>
-        </is>
-      </c>
-      <c r="G222" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H222" s="4" t="inlineStr"/>
-      <c r="I222" s="4" t="inlineStr"/>
-      <c r="J222" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="4" t="inlineStr">
-        <is>
-          <t>Cross FROM</t>
-        </is>
-      </c>
-      <c r="B223" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C223" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D223" s="4" t="inlineStr"/>
-      <c r="E223" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F223" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross FROM?</t>
-        </is>
-      </c>
-      <c r="G223" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H223" s="4" t="inlineStr"/>
-      <c r="I223" s="4" t="inlineStr"/>
-      <c r="J223" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="4" t="inlineStr">
-        <is>
-          <t>Primary TO</t>
-        </is>
-      </c>
-      <c r="B224" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C224" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D224" s="4" t="inlineStr"/>
-      <c r="E224" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F224" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Primary TO?</t>
-        </is>
-      </c>
-      <c r="G224" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H224" s="4" t="inlineStr"/>
-      <c r="I224" s="4" t="inlineStr"/>
-      <c r="J224" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J224"/>
+  <autoFilter ref="A1:J221"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -32753,7 +32645,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>OrderType; customerCompanyCode; orderStartDatetime; orderStatus; resolvedDateTime; serialNumber; relCompanyId; assignedPersonCode; deviceSerialNumber</t>
+          <t>OrderType; orderStartDatetime; orderStatus; resolvedDateTime; relCompanyId; assignedPersonCode</t>
         </is>
       </c>
     </row>

--- a/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
+++ b/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
@@ -20552,7 +20552,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>SAP Service Layer SQLQueries:OPOR.DocNum</t>
+          <t>SAP Service Layer SQLQueries:OPOR.NumAtCard, falling back to OPOR.DocNum</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -20810,7 +20810,7 @@
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.DocNum and part/SPL Master evidence also matches; current export needs reconciliation.</t>
+          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.NumAtCard and part/SPL Master evidence also matches.</t>
         </is>
       </c>
     </row>
@@ -31572,7 +31572,7 @@
       <c r="I210" s="3" t="inlineStr"/>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.DocNum and part/SPL Master evidence also matches; current export needs reconciliation.</t>
+          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.NumAtCard and part/SPL Master evidence also matches.</t>
         </is>
       </c>
     </row>

--- a/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
+++ b/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
@@ -20926,7 +20926,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>SAP Service Layer SQLQueries:POR1.LineTotal</t>
+          <t>SPI_DATA.csv:ListPrice multiplied by 0.72 CoCre8 cost factor</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">

--- a/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
+++ b/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Target Fields'!$A$1:$S$151</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Template Fields'!$A$1:$H$177</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Evidence'!$A$1:$D$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Evidence'!$A$1:$D$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$J$221</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Output Objects'!$A$1:$E$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Missing Important Fields'!$A$1:$E$88</definedName>
@@ -231,8 +231,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourceEvidence" displayName="SourceEvidence" ref="A1:D14" headerRowCount="1">
-  <autoFilter ref="A1:D14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourceEvidence" displayName="SourceEvidence" ref="A1:D15" headerRowCount="1">
+  <autoFilter ref="A1:D15"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Source"/>
     <tableColumn id="2" name="Path"/>
@@ -20926,7 +20926,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>SPI_DATA.csv:ListPrice multiplied by 0.72 CoCre8 cost factor</t>
+          <t>Current SPI_DATA.csv then Reference/SPI_Historical newest-first:ListPrice multiplied by 0.72 CoCre8 cost factor</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -21629,7 +21629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -21773,12 +21773,12 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>MinStock3 usage</t>
+          <t>Historical SPI prices</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>C:\dev\cc8\MinStock3\enrich_dimensions.py</t>
+          <t>Reference\SPI_Historical</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -21788,63 +21788,63 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Stock audit DN rows aggregate annual usage.</t>
+          <t>Older SPI CSV/XLSX files backfill ListPrice where the current SPI file has deleted parts; current SPI is preferred, then historical files newest-first.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Planning V2 live stock extract</t>
+          <t>MinStock3 usage</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Service Layer SQLQueries on OITW/OITM</t>
+          <t>C:\dev\cc8\MinStock3\enrich_dimensions.py</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Current stock metrics are fetched live from OITW: OnHand, IsCommited, OnOrder, MinStock, MaxStock, AvgPrice.</t>
+          <t>Stock audit DN rows aggregate annual usage.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Manual stock audit report</t>
+          <t>Planning V2 live stock extract</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>C:\dev\cc8\Exco\source_data\Stock Audit Report.txt</t>
+          <t>Service Layer SQLQueries on OITW/OITM</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Allowed manual SAP report source for usage once mapped to the template.</t>
+          <t>Current stock metrics are fetched live from OITW: OnHand, IsCommited, OnOrder, MinStock, MaxStock, AvgPrice.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Reference target fields</t>
+          <t>Manual stock audit report</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Reference\SPL Planning Data Fields edited.xlsx</t>
+          <t>C:\dev\cc8\Exco\source_data\Stock Audit Report.txt</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -21854,19 +21854,19 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Planning V2 target field metadata and CC8 relevance hints.</t>
+          <t>Allowed manual SAP report source for usage once mapped to the template.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Planning V2 sample templates</t>
+          <t>Reference target fields</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Samples\Templates raw.xlsx</t>
+          <t>Reference\SPL Planning Data Fields edited.xlsx</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -21876,19 +21876,19 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Canonical onboarding template fields used for template-shaped CSV outputs.</t>
+          <t>Planning V2 target field metadata and CC8 relevance hints.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>CoCre8 HelpDesk issue tracker</t>
+          <t>Planning V2 sample templates</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>C:\Users\richa\Downloads\CoCre8 Issue Tracker V3.2.csv</t>
+          <t>Samples\Templates raw.xlsx</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -21898,19 +21898,19 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>External SharePoint-list export used only for strict ticket/PO evidence; not committed to git.</t>
+          <t>Canonical onboarding template fields used for template-shaped CSV outputs.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>HelpDesk Power Automate flow</t>
+          <t>CoCre8 HelpDesk issue tracker</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Reference\HelpdeskFlow.txt</t>
+          <t>C:\Users\richa\Downloads\CoCre8 Issue Tracker V3.2.csv</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -21920,34 +21920,56 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Reference flow for ticket lifecycle and improvement recommendations.</t>
+          <t>External SharePoint-list export used only for strict ticket/PO evidence; not committed to git.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
+          <t>HelpDesk Power Automate flow</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Reference\HelpdeskFlow.txt</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Reference flow for ticket lifecycle and improvement recommendations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
           <t>Live SAP item group check</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>MinStock3 SAP Service Layer credentials</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>Checked Items and ItemGroups while VPN was connected. ItemGroups are broad customer/manufacturer groups such as FUJITSU, ACER, and CHOICE; sampled item master fields ItemType, ItemClass, and MaterialType are generic SAP classifications.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D14"/>
+  <autoFilter ref="A1:D15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
+++ b/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
@@ -20552,7 +20552,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>SAP Service Layer SQLQueries:OPOR.NumAtCard, falling back to OPOR.DocNum</t>
+          <t>SAP Service Layer SQLQueries:OPOR.NumAtCard, falling back only to PO-like reference parsed from OPOR.Comments</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">

--- a/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
+++ b/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Target Fields'!$A$1:$S$151</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Template Fields'!$A$1:$H$177</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Evidence'!$A$1:$D$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$J$221</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$J$217</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Output Objects'!$A$1:$E$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Missing Important Fields'!$A$1:$E$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'SAP Investigation Log'!$A$1:$E$10</definedName>
@@ -244,8 +244,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:J221" headerRowCount="1">
-  <autoFilter ref="A1:J221"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:J217" headerRowCount="1">
+  <autoFilter ref="A1:J217"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Field"/>
     <tableColumn id="2" name="Object"/>
@@ -19773,154 +19773,170 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="4" t="inlineStr">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>PartCost</t>
         </is>
       </c>
-      <c r="B129" s="4" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>partCode</t>
         </is>
       </c>
-      <c r="C129" s="4" t="inlineStr">
+      <c r="C129" s="2" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D129" s="4" t="inlineStr">
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Canonical header from PartCosts.xlsx</t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F129" s="4" t="inlineStr"/>
-      <c r="G129" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H129" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Actual SAP/Fujitsu part id from live SAP parts and PO lines</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="4" t="inlineStr">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>PartCost</t>
         </is>
       </c>
-      <c r="B130" s="4" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>cost</t>
         </is>
       </c>
-      <c r="C130" s="4" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="D130" s="4" t="inlineStr">
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Canonical header from PartCosts.xlsx</t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr"/>
-      <c r="G130" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H130" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Current SPI_DATA.csv then Reference/SPI_Historical newest-first:ListPrice multiplied by 0.72, selected as of last PO month where possible</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="4" t="inlineStr">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>PartCost</t>
         </is>
       </c>
-      <c r="B131" s="4" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>currencyCode</t>
         </is>
       </c>
-      <c r="C131" s="4" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D131" s="4" t="inlineStr">
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Canonical header from PartCosts.xlsx</t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F131" s="4" t="inlineStr"/>
-      <c r="G131" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H131" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Business rule: EUR for SPI CoCre8 costs</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="4" t="inlineStr">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>PartCost</t>
         </is>
       </c>
-      <c r="B132" s="4" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>averageCost</t>
         </is>
       </c>
-      <c r="C132" s="4" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="D132" s="4" t="inlineStr">
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Canonical header from PartCosts.xlsx</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F132" s="4" t="inlineStr"/>
-      <c r="G132" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H132" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>PO quantity-weighted average of SPI-derived CoCre8 costs across SAP PO history</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -21983,7 +21999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J221"/>
+  <dimension ref="A1:J217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -30806,7 +30822,7 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
@@ -30822,7 +30838,7 @@
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -30841,12 +30857,12 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>cost</t>
+          <t>modelCode</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
@@ -30862,7 +30878,7 @@
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.cost?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
         </is>
       </c>
       <c r="G192" s="4" t="inlineStr">
@@ -30881,12 +30897,12 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>currencyCode</t>
+          <t>modelDescription</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
@@ -30902,7 +30918,7 @@
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.currencyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -30921,12 +30937,12 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>averageCost</t>
+          <t>inventoryTransferImoId</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>PartCost</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
@@ -30942,7 +30958,7 @@
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartCost.averageCost?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.inventoryTransferImoId?</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr">
@@ -30961,12 +30977,12 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>createdDateTime</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -30982,7 +30998,7 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.createdDateTime?</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -31001,12 +31017,12 @@
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>modelCode</t>
+          <t>completedDateTime</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
@@ -31022,7 +31038,7 @@
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.completedDateTime?</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr">
@@ -31041,12 +31057,12 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>modelDescription</t>
+          <t>fromWarehouseId</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
@@ -31062,7 +31078,7 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.fromWarehouseId?</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
@@ -31081,7 +31097,7 @@
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>inventoryTransferImoId</t>
+          <t>toWarehouseId</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
@@ -31102,7 +31118,7 @@
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.inventoryTransferImoId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.toWarehouseId?</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr">
@@ -31121,7 +31137,7 @@
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>createdDateTime</t>
+          <t>demandStatus</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
@@ -31142,7 +31158,7 @@
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.createdDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.demandStatus?</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
@@ -31161,7 +31177,7 @@
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>completedDateTime</t>
+          <t>orderStatusIsClosed</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
@@ -31182,7 +31198,7 @@
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.completedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.orderStatusIsClosed?</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr">
@@ -31201,7 +31217,7 @@
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>fromWarehouseId</t>
+          <t>movementType</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
@@ -31222,7 +31238,7 @@
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.fromWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
@@ -31241,7 +31257,7 @@
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>toWarehouseId</t>
+          <t>addressId</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
@@ -31262,7 +31278,7 @@
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.toWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr">
@@ -31281,7 +31297,7 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>demandStatus</t>
+          <t>Bpart</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
@@ -31302,7 +31318,7 @@
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.demandStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.Bpart?</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -31321,7 +31337,7 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>orderStatusIsClosed</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
@@ -31342,7 +31358,7 @@
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.orderStatusIsClosed?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.quantity?</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr">
@@ -31361,7 +31377,7 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>movementType</t>
+          <t>shipListCode</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
@@ -31382,7 +31398,7 @@
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -31399,54 +31415,54 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="4" t="inlineStr">
-        <is>
-          <t>addressId</t>
-        </is>
-      </c>
-      <c r="B206" s="4" t="inlineStr">
-        <is>
-          <t>InventoryTransfers</t>
-        </is>
-      </c>
-      <c r="C206" s="4" t="inlineStr">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t>demandStatus</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>PurchaseOrders</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
         <is>
           <t>Planning V2 template</t>
         </is>
       </c>
-      <c r="D206" s="4" t="inlineStr"/>
-      <c r="E206" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F206" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
-        </is>
-      </c>
-      <c r="G206" s="4" t="inlineStr">
+      <c r="D206" s="3" t="inlineStr"/>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
+        </is>
+      </c>
+      <c r="G206" s="3" t="inlineStr">
         <is>
           <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
         </is>
       </c>
-      <c r="H206" s="4" t="inlineStr"/>
-      <c r="I206" s="4" t="inlineStr"/>
-      <c r="J206" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="H206" s="3" t="inlineStr"/>
+      <c r="I206" s="3" t="inlineStr"/>
+      <c r="J206" s="3" t="inlineStr">
+        <is>
+          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.NumAtCard and part/SPL Master evidence also matches.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>Bpart</t>
+          <t>partType</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
@@ -31462,7 +31478,7 @@
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.Bpart?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.partType?</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -31481,12 +31497,12 @@
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>partTypeDescription</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
@@ -31502,7 +31518,7 @@
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.quantity?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeDescription?</t>
         </is>
       </c>
       <c r="G208" s="4" t="inlineStr">
@@ -31521,12 +31537,12 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>shipListCode</t>
+          <t>isReworkable</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
@@ -31542,7 +31558,7 @@
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.isReworkable?</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr">
@@ -31559,54 +31575,54 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="3" t="inlineStr">
-        <is>
-          <t>demandStatus</t>
-        </is>
-      </c>
-      <c r="B210" s="3" t="inlineStr">
-        <is>
-          <t>PurchaseOrders</t>
-        </is>
-      </c>
-      <c r="C210" s="3" t="inlineStr">
+      <c r="A210" s="4" t="inlineStr">
+        <is>
+          <t>partNumber</t>
+        </is>
+      </c>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>Yields</t>
+        </is>
+      </c>
+      <c r="C210" s="4" t="inlineStr">
         <is>
           <t>Planning V2 template</t>
         </is>
       </c>
-      <c r="D210" s="3" t="inlineStr"/>
-      <c r="E210" s="3" t="inlineStr">
-        <is>
-          <t>Review required</t>
-        </is>
-      </c>
-      <c r="F210" s="3" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
-        </is>
-      </c>
-      <c r="G210" s="3" t="inlineStr">
+      <c r="D210" s="4" t="inlineStr"/>
+      <c r="E210" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F210" s="4" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
+        </is>
+      </c>
+      <c r="G210" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
         </is>
       </c>
-      <c r="H210" s="3" t="inlineStr"/>
-      <c r="I210" s="3" t="inlineStr"/>
-      <c r="J210" s="3" t="inlineStr">
-        <is>
-          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.NumAtCard and part/SPL Master evidence also matches.</t>
+      <c r="H210" s="4" t="inlineStr"/>
+      <c r="I210" s="4" t="inlineStr"/>
+      <c r="J210" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>partType</t>
+          <t>unitOfMeasure</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
@@ -31622,7 +31638,7 @@
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.partType?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
         </is>
       </c>
       <c r="G211" s="4" t="inlineStr">
@@ -31641,12 +31657,12 @@
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>partTypeDescription</t>
+          <t>yield</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
@@ -31662,7 +31678,7 @@
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeDescription?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
         </is>
       </c>
       <c r="G212" s="4" t="inlineStr">
@@ -31681,12 +31697,12 @@
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>isReworkable</t>
+          <t>Secondary TO</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
@@ -31702,7 +31718,7 @@
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.isReworkable?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary TO?</t>
         </is>
       </c>
       <c r="G213" s="4" t="inlineStr">
@@ -31721,12 +31737,12 @@
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>partNumber</t>
+          <t>Secondary FROM</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
@@ -31742,7 +31758,7 @@
       </c>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary FROM?</t>
         </is>
       </c>
       <c r="G214" s="4" t="inlineStr">
@@ -31761,12 +31777,12 @@
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>unitOfMeasure</t>
+          <t>Cross TO</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
@@ -31782,7 +31798,7 @@
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross TO?</t>
         </is>
       </c>
       <c r="G215" s="4" t="inlineStr">
@@ -31801,12 +31817,12 @@
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>yield</t>
+          <t>Cross FROM</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
@@ -31822,7 +31838,7 @@
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross FROM?</t>
         </is>
       </c>
       <c r="G216" s="4" t="inlineStr">
@@ -31841,7 +31857,7 @@
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>Secondary TO</t>
+          <t>Primary TO</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
@@ -31862,7 +31878,7 @@
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary TO?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Primary TO?</t>
         </is>
       </c>
       <c r="G217" s="4" t="inlineStr">
@@ -31878,168 +31894,8 @@
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="4" t="inlineStr">
-        <is>
-          <t>Secondary FROM</t>
-        </is>
-      </c>
-      <c r="B218" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C218" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D218" s="4" t="inlineStr"/>
-      <c r="E218" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F218" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary FROM?</t>
-        </is>
-      </c>
-      <c r="G218" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H218" s="4" t="inlineStr"/>
-      <c r="I218" s="4" t="inlineStr"/>
-      <c r="J218" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="4" t="inlineStr">
-        <is>
-          <t>Cross TO</t>
-        </is>
-      </c>
-      <c r="B219" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C219" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D219" s="4" t="inlineStr"/>
-      <c r="E219" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F219" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross TO?</t>
-        </is>
-      </c>
-      <c r="G219" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H219" s="4" t="inlineStr"/>
-      <c r="I219" s="4" t="inlineStr"/>
-      <c r="J219" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="4" t="inlineStr">
-        <is>
-          <t>Cross FROM</t>
-        </is>
-      </c>
-      <c r="B220" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C220" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D220" s="4" t="inlineStr"/>
-      <c r="E220" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F220" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross FROM?</t>
-        </is>
-      </c>
-      <c r="G220" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H220" s="4" t="inlineStr"/>
-      <c r="I220" s="4" t="inlineStr"/>
-      <c r="J220" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="4" t="inlineStr">
-        <is>
-          <t>Primary TO</t>
-        </is>
-      </c>
-      <c r="B221" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C221" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D221" s="4" t="inlineStr"/>
-      <c r="E221" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F221" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Primary TO?</t>
-        </is>
-      </c>
-      <c r="G221" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H221" s="4" t="inlineStr"/>
-      <c r="I221" s="4" t="inlineStr"/>
-      <c r="J221" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J221"/>
+  <autoFilter ref="A1:J217"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -32726,31 +32582,27 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>PartCost</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>PartCost.csv</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Pending/header only</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>partCode, cost, currencyCode, averageCost</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>partCode; cost; currencyCode; averageCost</t>
-        </is>
-      </c>
+      <c r="E27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">

--- a/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
+++ b/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Target Fields'!$A$1:$S$151</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Template Fields'!$A$1:$H$177</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Evidence'!$A$1:$D$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$J$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$J$212</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Output Objects'!$A$1:$E$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Missing Important Fields'!$A$1:$E$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'SAP Investigation Log'!$A$1:$E$10</definedName>
@@ -244,8 +244,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:J217" headerRowCount="1">
-  <autoFilter ref="A1:J217"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:J212" headerRowCount="1">
+  <autoFilter ref="A1:J212"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Field"/>
     <tableColumn id="2" name="Object"/>
@@ -15576,7 +15576,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>SPI_DATA.csv:Main alternative par equals material/part number</t>
+          <t>SPI_DATA.csv:Main alternative par equals material/part number; defaults true when no main alternative is listed</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15618,7 +15618,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>SPI_DATA.csv:Main alternative par</t>
+          <t>SPI_DATA.csv:Main alternative par; defaults to own part number when no main alternative is listed</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15675,78 +15675,86 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Parts</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>isBootStockable</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Canonical header from Parts.xlsx</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Business rule: N for all CoCre8 stock</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Parts</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>isBranchStockable</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Canonical header from Parts.xlsx</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Business rule: Y for all CoCre8 stock</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -15941,40 +15949,44 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Parts</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>isObsolete</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Canonical header from Parts.xlsx</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr"/>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Business rule: N for all CoCre8 stock for now</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -16047,40 +16059,44 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Parts</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>isExcludeFromReplenishment</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Canonical header from Parts.xlsx</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr"/>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Business rule: N for all CoCre8 stock for now</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -16119,40 +16135,44 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Parts</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>purchaseLeadTimeDays</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Number</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Canonical header from Parts.xlsx</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr"/>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Business rule: default 3 days; 180 days when description contains BBU</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -21999,7 +22019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J217"/>
+  <dimension ref="A1:J212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -27937,7 +27957,7 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>isBootStockable</t>
+          <t>productClass</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -27953,12 +27973,12 @@
       <c r="D119" s="4" t="inlineStr"/>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Not available in checked source</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isBootStockable?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.productClass?</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
@@ -27970,14 +27990,14 @@
       <c r="I119" s="4" t="inlineStr"/>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+          <t>Left blank. Live SAP item master check found broad ItemGroups such as FUJITSU/ACER/CHOICE and generic ItemType/ItemClass/MaterialType values, not Planning V2 class/type semantics.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>isBranchStockable</t>
+          <t>productType</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
@@ -27993,12 +28013,12 @@
       <c r="D120" s="4" t="inlineStr"/>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Not available in checked source</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isBranchStockable?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.productType?</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr">
@@ -28010,14 +28030,14 @@
       <c r="I120" s="4" t="inlineStr"/>
       <c r="J120" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+          <t>Left blank. Live SAP item master check found broad ItemGroups such as FUJITSU/ACER/CHOICE and generic ItemType/ItemClass/MaterialType values, not Planning V2 class/type semantics.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>productClass</t>
+          <t>costCategory</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -28033,12 +28053,12 @@
       <c r="D121" s="4" t="inlineStr"/>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>Not available in checked source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.productClass?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.costCategory?</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
@@ -28050,14 +28070,14 @@
       <c r="I121" s="4" t="inlineStr"/>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>Left blank. Live SAP item master check found broad ItemGroups such as FUJITSU/ACER/CHOICE and generic ItemType/ItemClass/MaterialType values, not Planning V2 class/type semantics.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>productType</t>
+          <t>partType</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
@@ -28078,7 +28098,7 @@
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.productType?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.partType?</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr">
@@ -28097,7 +28117,7 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>costCategory</t>
+          <t>isKit</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
@@ -28118,7 +28138,7 @@
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.costCategory?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isKit?</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
@@ -28137,7 +28157,7 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>partType</t>
+          <t>isCritical</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
@@ -28153,12 +28173,12 @@
       <c r="D124" s="4" t="inlineStr"/>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>Not available in checked source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.partType?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isCritical?</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr">
@@ -28170,19 +28190,19 @@
       <c r="I124" s="4" t="inlineStr"/>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>Left blank. Live SAP item master check found broad ItemGroups such as FUJITSU/ACER/CHOICE and generic ItemType/ItemClass/MaterialType values, not Planning V2 class/type semantics.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>isKit</t>
+          <t>externalAddressId</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Parts</t>
+          <t>Addresses</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -28198,7 +28218,7 @@
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isKit?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.externalAddressId?</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
@@ -28210,19 +28230,19 @@
       <c r="I125" s="4" t="inlineStr"/>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>isObsolete</t>
+          <t>customerExternalId</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>Parts</t>
+          <t>Addresses</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
@@ -28238,7 +28258,7 @@
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isObsolete?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.customerExternalId?</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr">
@@ -28250,19 +28270,19 @@
       <c r="I126" s="4" t="inlineStr"/>
       <c r="J126" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>isExcludeFromReplenishment</t>
+          <t>6,0</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Parts</t>
+          <t>Addresses</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -28278,7 +28298,7 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isExcludeFromReplenishment?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.6,0?</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
@@ -28290,19 +28310,19 @@
       <c r="I127" s="4" t="inlineStr"/>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>purchaseLeadTimeDays</t>
+          <t>addressLine2</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>Parts</t>
+          <t>Addresses</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
@@ -28318,7 +28338,7 @@
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.purchaseLeadTimeDays?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine2?</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr">
@@ -28330,19 +28350,19 @@
       <c r="I128" s="4" t="inlineStr"/>
       <c r="J128" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>isCritical</t>
+          <t>addressLine3</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Parts</t>
+          <t>Addresses</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -28358,7 +28378,7 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isCritical?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine3?</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
@@ -28370,14 +28390,14 @@
       <c r="I129" s="4" t="inlineStr"/>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>externalAddressId</t>
+          <t>city</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
@@ -28398,7 +28418,7 @@
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.externalAddressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.city?</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr">
@@ -28417,7 +28437,7 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>customerExternalId</t>
+          <t>stateProvince</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
@@ -28438,7 +28458,7 @@
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.customerExternalId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.stateProvince?</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
@@ -28457,7 +28477,7 @@
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>6,0</t>
+          <t>countryCode</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
@@ -28478,7 +28498,7 @@
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.6,0?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.countryCode?</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr">
@@ -28497,7 +28517,7 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>addressLine2</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -28518,7 +28538,7 @@
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine2?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.latitude?</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
@@ -28537,7 +28557,7 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>addressLine3</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
@@ -28558,7 +28578,7 @@
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine3?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.longitude?</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr">
@@ -28577,7 +28597,7 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>timeZone</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -28598,7 +28618,7 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.city?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.timeZone?</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
@@ -28617,7 +28637,7 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>stateProvince</t>
+          <t>nodeId</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
@@ -28638,7 +28658,7 @@
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.stateProvince?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.nodeId?</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr">
@@ -28657,12 +28677,12 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>countryCode</t>
+          <t>personId</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Addresses</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -28678,7 +28698,7 @@
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.countryCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.personId?</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
@@ -28697,12 +28717,12 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>role</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>Addresses</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -28718,7 +28738,7 @@
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.latitude?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.role?</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr">
@@ -28737,12 +28757,12 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>addressId</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Addresses</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -28758,7 +28778,7 @@
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.longitude?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.addressId?</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
@@ -28777,12 +28797,12 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>timeZone</t>
+          <t>nodeId</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>Addresses</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -28798,7 +28818,7 @@
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.timeZone?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.nodeId?</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr">
@@ -28817,12 +28837,12 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>nodeId</t>
+          <t>firstName</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Addresses</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -28838,7 +28858,7 @@
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.nodeId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.firstName?</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
@@ -28857,7 +28877,7 @@
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>personId</t>
+          <t>middleName</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
@@ -28878,7 +28898,7 @@
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.personId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.middleName?</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
@@ -28897,7 +28917,7 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>surname</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
@@ -28918,7 +28938,7 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.role?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.surname?</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
@@ -28937,7 +28957,7 @@
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>addressId</t>
+          <t>isActive</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
@@ -28958,7 +28978,7 @@
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.addressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.isActive?</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr">
@@ -28977,7 +28997,7 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>nodeId</t>
+          <t>telephoneNumber</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
@@ -28998,7 +29018,7 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.nodeId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.telephoneNumber?</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
@@ -29017,7 +29037,7 @@
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>firstName</t>
+          <t>whs id</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
@@ -29038,7 +29058,7 @@
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.firstName?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.whs id?</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr">
@@ -29057,12 +29077,12 @@
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>middleName</t>
+          <t>OrderType</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -29078,7 +29098,7 @@
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.middleName?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.OrderType?</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
@@ -29097,12 +29117,12 @@
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>surname</t>
+          <t>orderStartDatetime</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
@@ -29118,7 +29138,7 @@
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.surname?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStartDatetime?</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr">
@@ -29137,12 +29157,12 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>isActive</t>
+          <t>orderStatus</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -29158,7 +29178,7 @@
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.isActive?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStatus?</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
@@ -29177,12 +29197,12 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>telephoneNumber</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
@@ -29198,7 +29218,7 @@
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.telephoneNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr">
@@ -29217,12 +29237,12 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>whs id</t>
+          <t>relCompanyId</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -29238,7 +29258,7 @@
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.whs id?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
@@ -29257,7 +29277,7 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>OrderType</t>
+          <t>assignedPersonCode</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
@@ -29278,7 +29298,7 @@
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.OrderType?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
@@ -29297,12 +29317,12 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>orderStartDatetime</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -29318,7 +29338,7 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStartDatetime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.orderNumber?</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
@@ -29337,12 +29357,12 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>orderStatus</t>
+          <t>RequestID</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
@@ -29358,7 +29378,7 @@
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.RequestID?</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr">
@@ -29377,12 +29397,12 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
@@ -29398,7 +29418,7 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.location?</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
@@ -29417,12 +29437,12 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>relCompanyId</t>
+          <t>eta</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
@@ -29438,7 +29458,7 @@
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.eta?</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr">
@@ -29457,12 +29477,12 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>assignedPersonCode</t>
+          <t>actualEta</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
@@ -29478,7 +29498,7 @@
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualEta?</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
@@ -29497,7 +29517,7 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>actualResolveDateTime</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
@@ -29518,7 +29538,7 @@
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualResolveDateTime?</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr">
@@ -29537,7 +29557,7 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>RequestID</t>
+          <t>recallDateTime</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
@@ -29558,7 +29578,7 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.RequestID?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.recallDateTime?</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
@@ -29577,7 +29597,7 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>actualRecallDateTime</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
@@ -29598,7 +29618,7 @@
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.location?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualRecallDateTime?</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr">
@@ -29617,7 +29637,7 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>eta</t>
+          <t>slaEtaClock</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
@@ -29638,7 +29658,7 @@
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.eta?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaClock?</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
@@ -29657,7 +29677,7 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>actualEta</t>
+          <t>slaResolveClock</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
@@ -29678,7 +29698,7 @@
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualEta?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveClock?</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr">
@@ -29697,7 +29717,7 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>actualResolveDateTime</t>
+          <t>slaFailureCode</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
@@ -29718,7 +29738,7 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualResolveDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaFailureCode?</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
@@ -29737,7 +29757,7 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>recallDateTime</t>
+          <t>slaEtaHit</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
@@ -29758,7 +29778,7 @@
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.recallDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaHit?</t>
         </is>
       </c>
       <c r="G164" s="4" t="inlineStr">
@@ -29777,7 +29797,7 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>actualRecallDateTime</t>
+          <t>slaResolveDateTime</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
@@ -29798,7 +29818,7 @@
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualRecallDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveDateTime?</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
@@ -29817,12 +29837,12 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>slaEtaClock</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
@@ -29838,7 +29858,7 @@
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaClock?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderNumber?</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr">
@@ -29857,12 +29877,12 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>slaResolveClock</t>
+          <t>requestId</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
@@ -29878,7 +29898,7 @@
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveClock?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.requestId?</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -29897,12 +29917,12 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>slaFailureCode</t>
+          <t>customerCompanyCode</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
@@ -29918,7 +29938,7 @@
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaFailureCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.customerCompanyCode?</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr">
@@ -29937,12 +29957,12 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>slaEtaHit</t>
+          <t>orderStatus</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
@@ -29958,7 +29978,7 @@
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaHit?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStatus?</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
@@ -29977,12 +29997,12 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>slaResolveDateTime</t>
+          <t>orderStartDatetime</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
@@ -29998,7 +30018,7 @@
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStartDatetime?</t>
         </is>
       </c>
       <c r="G170" s="4" t="inlineStr">
@@ -30017,7 +30037,7 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>siteCompanyCode</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
@@ -30038,7 +30058,7 @@
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.siteCompanyCode?</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
@@ -30057,7 +30077,7 @@
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>requestId</t>
+          <t>repairType</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
@@ -30078,7 +30098,7 @@
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.requestId?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairType?</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr">
@@ -30097,7 +30117,7 @@
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>customerCompanyCode</t>
+          <t>partsOrderDateTime</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
@@ -30118,7 +30138,7 @@
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.customerCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsOrderDateTime?</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -30137,7 +30157,7 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>orderStatus</t>
+          <t>partsReceivedDateTime</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
@@ -30158,7 +30178,7 @@
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsReceivedDateTime?</t>
         </is>
       </c>
       <c r="G174" s="4" t="inlineStr">
@@ -30177,7 +30197,7 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>orderStartDatetime</t>
+          <t>repairCode</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
@@ -30198,7 +30218,7 @@
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStartDatetime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCode?</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
@@ -30217,7 +30237,7 @@
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>siteCompanyCode</t>
+          <t>repairCompany</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
@@ -30238,7 +30258,7 @@
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.siteCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCompany?</t>
         </is>
       </c>
       <c r="G176" s="4" t="inlineStr">
@@ -30257,7 +30277,7 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>repairType</t>
+          <t>raStatus</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
@@ -30278,7 +30298,7 @@
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairType?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.raStatus?</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
@@ -30297,7 +30317,7 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>partsOrderDateTime</t>
+          <t>Warehouse</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
@@ -30318,7 +30338,7 @@
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsOrderDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.Warehouse?</t>
         </is>
       </c>
       <c r="G178" s="4" t="inlineStr">
@@ -30337,7 +30357,7 @@
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>partsReceivedDateTime</t>
+          <t>assignedPerson</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
@@ -30358,7 +30378,7 @@
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsReceivedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.assignedPerson?</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
@@ -30377,7 +30397,7 @@
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>repairCode</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
@@ -30398,7 +30418,7 @@
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.resolvedDateTime?</t>
         </is>
       </c>
       <c r="G180" s="4" t="inlineStr">
@@ -30417,7 +30437,7 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>repairCompany</t>
+          <t>serialNumber</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
@@ -30438,7 +30458,7 @@
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCompany?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.serialNumber?</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
@@ -30457,7 +30477,7 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>raStatus</t>
+          <t>quantityUsed</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
@@ -30478,7 +30498,7 @@
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.raStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.quantityUsed?</t>
         </is>
       </c>
       <c r="G182" s="4" t="inlineStr">
@@ -30497,7 +30517,7 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>deviceSerialNumber</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
@@ -30518,7 +30538,7 @@
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.Warehouse?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.deviceSerialNumber?</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
@@ -30537,7 +30557,7 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>assignedPerson</t>
+          <t>orderedPartId</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
@@ -30558,7 +30578,7 @@
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.assignedPerson?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderedPartId?</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr">
@@ -30577,7 +30597,7 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>actualPartId</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
@@ -30598,7 +30618,7 @@
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.resolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.actualPartId?</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr">
@@ -30617,12 +30637,12 @@
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>serialNumber</t>
+          <t>partCode</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
@@ -30638,7 +30658,7 @@
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.serialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
         </is>
       </c>
       <c r="G186" s="4" t="inlineStr">
@@ -30657,12 +30677,12 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>quantityUsed</t>
+          <t>modelCode</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
@@ -30678,7 +30698,7 @@
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.quantityUsed?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr">
@@ -30697,12 +30717,12 @@
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>deviceSerialNumber</t>
+          <t>modelDescription</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
@@ -30718,7 +30738,7 @@
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.deviceSerialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
         </is>
       </c>
       <c r="G188" s="4" t="inlineStr">
@@ -30737,12 +30757,12 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>orderedPartId</t>
+          <t>inventoryTransferImoId</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
@@ -30758,7 +30778,7 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderedPartId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.inventoryTransferImoId?</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr">
@@ -30777,12 +30797,12 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>actualPartId</t>
+          <t>createdDateTime</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
@@ -30798,7 +30818,7 @@
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.actualPartId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.createdDateTime?</t>
         </is>
       </c>
       <c r="G190" s="4" t="inlineStr">
@@ -30817,12 +30837,12 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>completedDateTime</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
@@ -30838,7 +30858,7 @@
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.completedDateTime?</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -30857,12 +30877,12 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>modelCode</t>
+          <t>fromWarehouseId</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
@@ -30878,7 +30898,7 @@
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.fromWarehouseId?</t>
         </is>
       </c>
       <c r="G192" s="4" t="inlineStr">
@@ -30897,12 +30917,12 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>modelDescription</t>
+          <t>toWarehouseId</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
@@ -30918,7 +30938,7 @@
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.toWarehouseId?</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -30937,7 +30957,7 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>inventoryTransferImoId</t>
+          <t>demandStatus</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
@@ -30958,7 +30978,7 @@
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.inventoryTransferImoId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.demandStatus?</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr">
@@ -30977,7 +30997,7 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>createdDateTime</t>
+          <t>orderStatusIsClosed</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
@@ -30998,7 +31018,7 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.createdDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.orderStatusIsClosed?</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -31017,7 +31037,7 @@
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>completedDateTime</t>
+          <t>movementType</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
@@ -31038,7 +31058,7 @@
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.completedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr">
@@ -31057,7 +31077,7 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>fromWarehouseId</t>
+          <t>addressId</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
@@ -31078,7 +31098,7 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.fromWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
@@ -31097,7 +31117,7 @@
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>toWarehouseId</t>
+          <t>Bpart</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
@@ -31118,7 +31138,7 @@
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.toWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.Bpart?</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr">
@@ -31137,7 +31157,7 @@
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>demandStatus</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
@@ -31158,7 +31178,7 @@
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.demandStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.quantity?</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
@@ -31177,7 +31197,7 @@
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>orderStatusIsClosed</t>
+          <t>shipListCode</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
@@ -31198,7 +31218,7 @@
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.orderStatusIsClosed?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr">
@@ -31215,54 +31235,54 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="4" t="inlineStr">
-        <is>
-          <t>movementType</t>
-        </is>
-      </c>
-      <c r="B201" s="4" t="inlineStr">
-        <is>
-          <t>InventoryTransfers</t>
-        </is>
-      </c>
-      <c r="C201" s="4" t="inlineStr">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>demandStatus</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>PurchaseOrders</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
         <is>
           <t>Planning V2 template</t>
         </is>
       </c>
-      <c r="D201" s="4" t="inlineStr"/>
-      <c r="E201" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F201" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
-        </is>
-      </c>
-      <c r="G201" s="4" t="inlineStr">
+      <c r="D201" s="3" t="inlineStr"/>
+      <c r="E201" s="3" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="F201" s="3" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
+        </is>
+      </c>
+      <c r="G201" s="3" t="inlineStr">
         <is>
           <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
         </is>
       </c>
-      <c r="H201" s="4" t="inlineStr"/>
-      <c r="I201" s="4" t="inlineStr"/>
-      <c r="J201" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="H201" s="3" t="inlineStr"/>
+      <c r="I201" s="3" t="inlineStr"/>
+      <c r="J201" s="3" t="inlineStr">
+        <is>
+          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.NumAtCard and part/SPL Master evidence also matches.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>addressId</t>
+          <t>partType</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
@@ -31278,7 +31298,7 @@
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.partType?</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr">
@@ -31297,12 +31317,12 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>Bpart</t>
+          <t>partTypeDescription</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
@@ -31318,7 +31338,7 @@
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.Bpart?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeDescription?</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -31337,12 +31357,12 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>isReworkable</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
@@ -31358,7 +31378,7 @@
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.quantity?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.isReworkable?</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr">
@@ -31377,12 +31397,12 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>shipListCode</t>
+          <t>partNumber</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
@@ -31398,7 +31418,7 @@
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -31415,54 +31435,54 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="3" t="inlineStr">
-        <is>
-          <t>demandStatus</t>
-        </is>
-      </c>
-      <c r="B206" s="3" t="inlineStr">
-        <is>
-          <t>PurchaseOrders</t>
-        </is>
-      </c>
-      <c r="C206" s="3" t="inlineStr">
+      <c r="A206" s="4" t="inlineStr">
+        <is>
+          <t>unitOfMeasure</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>Yields</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="inlineStr">
         <is>
           <t>Planning V2 template</t>
         </is>
       </c>
-      <c r="D206" s="3" t="inlineStr"/>
-      <c r="E206" s="3" t="inlineStr">
-        <is>
-          <t>Review required</t>
-        </is>
-      </c>
-      <c r="F206" s="3" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
-        </is>
-      </c>
-      <c r="G206" s="3" t="inlineStr">
+      <c r="D206" s="4" t="inlineStr"/>
+      <c r="E206" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F206" s="4" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
+        </is>
+      </c>
+      <c r="G206" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
         </is>
       </c>
-      <c r="H206" s="3" t="inlineStr"/>
-      <c r="I206" s="3" t="inlineStr"/>
-      <c r="J206" s="3" t="inlineStr">
-        <is>
-          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.NumAtCard and part/SPL Master evidence also matches.</t>
+      <c r="H206" s="4" t="inlineStr"/>
+      <c r="I206" s="4" t="inlineStr"/>
+      <c r="J206" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>partType</t>
+          <t>yield</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
@@ -31478,7 +31498,7 @@
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.partType?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -31497,12 +31517,12 @@
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>partTypeDescription</t>
+          <t>Secondary TO</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
@@ -31518,7 +31538,7 @@
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeDescription?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary TO?</t>
         </is>
       </c>
       <c r="G208" s="4" t="inlineStr">
@@ -31537,12 +31557,12 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>isReworkable</t>
+          <t>Secondary FROM</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
@@ -31558,7 +31578,7 @@
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.isReworkable?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary FROM?</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr">
@@ -31577,12 +31597,12 @@
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>partNumber</t>
+          <t>Cross TO</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
@@ -31598,7 +31618,7 @@
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross TO?</t>
         </is>
       </c>
       <c r="G210" s="4" t="inlineStr">
@@ -31617,12 +31637,12 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>unitOfMeasure</t>
+          <t>Cross FROM</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
@@ -31638,7 +31658,7 @@
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross FROM?</t>
         </is>
       </c>
       <c r="G211" s="4" t="inlineStr">
@@ -31657,12 +31677,12 @@
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>yield</t>
+          <t>Primary TO</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
@@ -31678,7 +31698,7 @@
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Primary TO?</t>
         </is>
       </c>
       <c r="G212" s="4" t="inlineStr">
@@ -31694,208 +31714,8 @@
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="4" t="inlineStr">
-        <is>
-          <t>Secondary TO</t>
-        </is>
-      </c>
-      <c r="B213" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C213" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D213" s="4" t="inlineStr"/>
-      <c r="E213" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F213" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary TO?</t>
-        </is>
-      </c>
-      <c r="G213" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H213" s="4" t="inlineStr"/>
-      <c r="I213" s="4" t="inlineStr"/>
-      <c r="J213" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="4" t="inlineStr">
-        <is>
-          <t>Secondary FROM</t>
-        </is>
-      </c>
-      <c r="B214" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C214" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D214" s="4" t="inlineStr"/>
-      <c r="E214" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F214" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary FROM?</t>
-        </is>
-      </c>
-      <c r="G214" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H214" s="4" t="inlineStr"/>
-      <c r="I214" s="4" t="inlineStr"/>
-      <c r="J214" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="4" t="inlineStr">
-        <is>
-          <t>Cross TO</t>
-        </is>
-      </c>
-      <c r="B215" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C215" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D215" s="4" t="inlineStr"/>
-      <c r="E215" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F215" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross TO?</t>
-        </is>
-      </c>
-      <c r="G215" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H215" s="4" t="inlineStr"/>
-      <c r="I215" s="4" t="inlineStr"/>
-      <c r="J215" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="4" t="inlineStr">
-        <is>
-          <t>Cross FROM</t>
-        </is>
-      </c>
-      <c r="B216" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C216" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D216" s="4" t="inlineStr"/>
-      <c r="E216" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F216" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross FROM?</t>
-        </is>
-      </c>
-      <c r="G216" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H216" s="4" t="inlineStr"/>
-      <c r="I216" s="4" t="inlineStr"/>
-      <c r="J216" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="4" t="inlineStr">
-        <is>
-          <t>Primary TO</t>
-        </is>
-      </c>
-      <c r="B217" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C217" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D217" s="4" t="inlineStr"/>
-      <c r="E217" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F217" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Primary TO?</t>
-        </is>
-      </c>
-      <c r="G217" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H217" s="4" t="inlineStr"/>
-      <c r="I217" s="4" t="inlineStr"/>
-      <c r="J217" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J217"/>
+  <autoFilter ref="A1:J212"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -32396,7 +32216,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>isBootStockable; isBranchStockable; productClass; productType; costCategory; partType; isKit; isObsolete; isExcludeFromReplenishment; purchaseLeadTimeDays; isCritical</t>
+          <t>productClass; productType; costCategory; partType; isKit; isCritical</t>
         </is>
       </c>
     </row>

--- a/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
+++ b/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Target Fields'!$A$1:$S$151</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Template Fields'!$A$1:$H$177</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Evidence'!$A$1:$D$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$J$212</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$J$210</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Output Objects'!$A$1:$E$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Missing Important Fields'!$A$1:$E$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'SAP Investigation Log'!$A$1:$E$10</definedName>
@@ -244,8 +244,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:J212" headerRowCount="1">
-  <autoFilter ref="A1:J212"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:J210" headerRowCount="1">
+  <autoFilter ref="A1:J210"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Field"/>
     <tableColumn id="2" name="Object"/>
@@ -18067,78 +18067,86 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>orderStartDatetime</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Canonical header from PartsUsage.xlsx</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr"/>
-      <c r="G84" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>HelpDesk issue tracker Created date by unambiguous call-number match</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="inlineStr">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B85" s="4" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>orderStatus</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D85" s="4" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Canonical header from PartsUsage.xlsx</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="inlineStr"/>
-      <c r="G85" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H85" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>HelpDesk issue tracker Status by unambiguous call-number match</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -22019,7 +22027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J212"/>
+  <dimension ref="A1:J210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -29117,7 +29125,7 @@
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>orderStartDatetime</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
@@ -29138,7 +29146,7 @@
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStartDatetime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr">
@@ -29157,7 +29165,7 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>orderStatus</t>
+          <t>relCompanyId</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
@@ -29178,7 +29186,7 @@
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.orderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
@@ -29197,7 +29205,7 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>assignedPersonCode</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
@@ -29218,7 +29226,7 @@
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr">
@@ -29237,12 +29245,12 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>relCompanyId</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -29258,7 +29266,7 @@
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.orderNumber?</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
@@ -29277,12 +29285,12 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>assignedPersonCode</t>
+          <t>RequestID</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
@@ -29298,7 +29306,7 @@
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.RequestID?</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
@@ -29317,7 +29325,7 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
@@ -29338,7 +29346,7 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.location?</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
@@ -29357,7 +29365,7 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>RequestID</t>
+          <t>eta</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
@@ -29378,7 +29386,7 @@
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.RequestID?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.eta?</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr">
@@ -29397,7 +29405,7 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>actualEta</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
@@ -29418,7 +29426,7 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.location?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualEta?</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
@@ -29437,7 +29445,7 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>eta</t>
+          <t>actualResolveDateTime</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
@@ -29458,7 +29466,7 @@
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.eta?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualResolveDateTime?</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr">
@@ -29477,7 +29485,7 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>actualEta</t>
+          <t>recallDateTime</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
@@ -29498,7 +29506,7 @@
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualEta?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.recallDateTime?</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
@@ -29517,7 +29525,7 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>actualResolveDateTime</t>
+          <t>actualRecallDateTime</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
@@ -29538,7 +29546,7 @@
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualResolveDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualRecallDateTime?</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr">
@@ -29557,7 +29565,7 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>recallDateTime</t>
+          <t>slaEtaClock</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
@@ -29578,7 +29586,7 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.recallDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaClock?</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
@@ -29597,7 +29605,7 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>actualRecallDateTime</t>
+          <t>slaResolveClock</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
@@ -29618,7 +29626,7 @@
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualRecallDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveClock?</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr">
@@ -29637,7 +29645,7 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>slaEtaClock</t>
+          <t>slaFailureCode</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
@@ -29658,7 +29666,7 @@
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaClock?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaFailureCode?</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
@@ -29677,7 +29685,7 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>slaResolveClock</t>
+          <t>slaEtaHit</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
@@ -29698,7 +29706,7 @@
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveClock?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaHit?</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr">
@@ -29717,7 +29725,7 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>slaFailureCode</t>
+          <t>slaResolveDateTime</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
@@ -29738,7 +29746,7 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaFailureCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveDateTime?</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
@@ -29757,12 +29765,12 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>slaEtaHit</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
@@ -29778,7 +29786,7 @@
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaHit?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderNumber?</t>
         </is>
       </c>
       <c r="G164" s="4" t="inlineStr">
@@ -29797,12 +29805,12 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>slaResolveDateTime</t>
+          <t>requestId</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
@@ -29818,7 +29826,7 @@
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.requestId?</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
@@ -29837,7 +29845,7 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>customerCompanyCode</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
@@ -29858,7 +29866,7 @@
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.customerCompanyCode?</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr">
@@ -29877,7 +29885,7 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>requestId</t>
+          <t>orderStatus</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
@@ -29898,7 +29906,7 @@
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.requestId?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStatus?</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -29917,7 +29925,7 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>customerCompanyCode</t>
+          <t>orderStartDatetime</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
@@ -29938,7 +29946,7 @@
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.customerCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStartDatetime?</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr">
@@ -29957,7 +29965,7 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>orderStatus</t>
+          <t>siteCompanyCode</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
@@ -29978,7 +29986,7 @@
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.siteCompanyCode?</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
@@ -29997,7 +30005,7 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>orderStartDatetime</t>
+          <t>repairType</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
@@ -30018,7 +30026,7 @@
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStartDatetime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairType?</t>
         </is>
       </c>
       <c r="G170" s="4" t="inlineStr">
@@ -30037,7 +30045,7 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>siteCompanyCode</t>
+          <t>partsOrderDateTime</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
@@ -30058,7 +30066,7 @@
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.siteCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsOrderDateTime?</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
@@ -30077,7 +30085,7 @@
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>repairType</t>
+          <t>partsReceivedDateTime</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
@@ -30098,7 +30106,7 @@
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairType?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsReceivedDateTime?</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr">
@@ -30117,7 +30125,7 @@
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>partsOrderDateTime</t>
+          <t>repairCode</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
@@ -30138,7 +30146,7 @@
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsOrderDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCode?</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -30157,7 +30165,7 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>partsReceivedDateTime</t>
+          <t>repairCompany</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
@@ -30178,7 +30186,7 @@
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsReceivedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCompany?</t>
         </is>
       </c>
       <c r="G174" s="4" t="inlineStr">
@@ -30197,7 +30205,7 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>repairCode</t>
+          <t>raStatus</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
@@ -30218,7 +30226,7 @@
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.raStatus?</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
@@ -30237,7 +30245,7 @@
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>repairCompany</t>
+          <t>Warehouse</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
@@ -30258,7 +30266,7 @@
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCompany?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.Warehouse?</t>
         </is>
       </c>
       <c r="G176" s="4" t="inlineStr">
@@ -30277,7 +30285,7 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>raStatus</t>
+          <t>assignedPerson</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
@@ -30298,7 +30306,7 @@
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.raStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.assignedPerson?</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
@@ -30317,7 +30325,7 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
@@ -30338,7 +30346,7 @@
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.Warehouse?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.resolvedDateTime?</t>
         </is>
       </c>
       <c r="G178" s="4" t="inlineStr">
@@ -30357,7 +30365,7 @@
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>assignedPerson</t>
+          <t>serialNumber</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
@@ -30378,7 +30386,7 @@
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.assignedPerson?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.serialNumber?</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
@@ -30397,7 +30405,7 @@
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>quantityUsed</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
@@ -30418,7 +30426,7 @@
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.resolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.quantityUsed?</t>
         </is>
       </c>
       <c r="G180" s="4" t="inlineStr">
@@ -30437,7 +30445,7 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>serialNumber</t>
+          <t>deviceSerialNumber</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
@@ -30458,7 +30466,7 @@
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.serialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.deviceSerialNumber?</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
@@ -30477,7 +30485,7 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>quantityUsed</t>
+          <t>orderedPartId</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
@@ -30498,7 +30506,7 @@
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.quantityUsed?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderedPartId?</t>
         </is>
       </c>
       <c r="G182" s="4" t="inlineStr">
@@ -30517,7 +30525,7 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>deviceSerialNumber</t>
+          <t>actualPartId</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
@@ -30538,7 +30546,7 @@
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.deviceSerialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.actualPartId?</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
@@ -30557,12 +30565,12 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>orderedPartId</t>
+          <t>partCode</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
@@ -30578,7 +30586,7 @@
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderedPartId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr">
@@ -30597,12 +30605,12 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>actualPartId</t>
+          <t>modelCode</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
@@ -30618,7 +30626,7 @@
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.actualPartId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr">
@@ -30637,7 +30645,7 @@
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>modelDescription</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
@@ -30658,7 +30666,7 @@
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
         </is>
       </c>
       <c r="G186" s="4" t="inlineStr">
@@ -30677,12 +30685,12 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>modelCode</t>
+          <t>inventoryTransferImoId</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
@@ -30698,7 +30706,7 @@
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.inventoryTransferImoId?</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr">
@@ -30717,12 +30725,12 @@
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>modelDescription</t>
+          <t>createdDateTime</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
@@ -30738,7 +30746,7 @@
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.createdDateTime?</t>
         </is>
       </c>
       <c r="G188" s="4" t="inlineStr">
@@ -30757,7 +30765,7 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>inventoryTransferImoId</t>
+          <t>completedDateTime</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
@@ -30778,7 +30786,7 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.inventoryTransferImoId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.completedDateTime?</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr">
@@ -30797,7 +30805,7 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>createdDateTime</t>
+          <t>fromWarehouseId</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
@@ -30818,7 +30826,7 @@
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.createdDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.fromWarehouseId?</t>
         </is>
       </c>
       <c r="G190" s="4" t="inlineStr">
@@ -30837,7 +30845,7 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>completedDateTime</t>
+          <t>toWarehouseId</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
@@ -30858,7 +30866,7 @@
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.completedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.toWarehouseId?</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -30877,7 +30885,7 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>fromWarehouseId</t>
+          <t>demandStatus</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
@@ -30898,7 +30906,7 @@
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.fromWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.demandStatus?</t>
         </is>
       </c>
       <c r="G192" s="4" t="inlineStr">
@@ -30917,7 +30925,7 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>toWarehouseId</t>
+          <t>orderStatusIsClosed</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
@@ -30938,7 +30946,7 @@
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.toWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.orderStatusIsClosed?</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -30957,7 +30965,7 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>demandStatus</t>
+          <t>movementType</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
@@ -30978,7 +30986,7 @@
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.demandStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr">
@@ -30997,7 +31005,7 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>orderStatusIsClosed</t>
+          <t>addressId</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
@@ -31018,7 +31026,7 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.orderStatusIsClosed?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -31037,7 +31045,7 @@
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>movementType</t>
+          <t>Bpart</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
@@ -31058,7 +31066,7 @@
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.Bpart?</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr">
@@ -31077,7 +31085,7 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>addressId</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
@@ -31098,7 +31106,7 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.quantity?</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
@@ -31117,7 +31125,7 @@
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>Bpart</t>
+          <t>shipListCode</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
@@ -31138,7 +31146,7 @@
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.Bpart?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr">
@@ -31155,54 +31163,54 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="4" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="B199" s="4" t="inlineStr">
-        <is>
-          <t>InventoryTransfers</t>
-        </is>
-      </c>
-      <c r="C199" s="4" t="inlineStr">
+      <c r="A199" s="3" t="inlineStr">
+        <is>
+          <t>demandStatus</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>PurchaseOrders</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
         <is>
           <t>Planning V2 template</t>
         </is>
       </c>
-      <c r="D199" s="4" t="inlineStr"/>
-      <c r="E199" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F199" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.quantity?</t>
-        </is>
-      </c>
-      <c r="G199" s="4" t="inlineStr">
+      <c r="D199" s="3" t="inlineStr"/>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="F199" s="3" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
+        </is>
+      </c>
+      <c r="G199" s="3" t="inlineStr">
         <is>
           <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
         </is>
       </c>
-      <c r="H199" s="4" t="inlineStr"/>
-      <c r="I199" s="4" t="inlineStr"/>
-      <c r="J199" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="H199" s="3" t="inlineStr"/>
+      <c r="I199" s="3" t="inlineStr"/>
+      <c r="J199" s="3" t="inlineStr">
+        <is>
+          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.NumAtCard and part/SPL Master evidence also matches.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>shipListCode</t>
+          <t>partType</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
@@ -31218,7 +31226,7 @@
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.partType?</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr">
@@ -31235,49 +31243,49 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="3" t="inlineStr">
-        <is>
-          <t>demandStatus</t>
-        </is>
-      </c>
-      <c r="B201" s="3" t="inlineStr">
-        <is>
-          <t>PurchaseOrders</t>
-        </is>
-      </c>
-      <c r="C201" s="3" t="inlineStr">
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>partTypeDescription</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>PartTypes</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr">
         <is>
           <t>Planning V2 template</t>
         </is>
       </c>
-      <c r="D201" s="3" t="inlineStr"/>
-      <c r="E201" s="3" t="inlineStr">
-        <is>
-          <t>Review required</t>
-        </is>
-      </c>
-      <c r="F201" s="3" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
-        </is>
-      </c>
-      <c r="G201" s="3" t="inlineStr">
+      <c r="D201" s="4" t="inlineStr"/>
+      <c r="E201" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F201" s="4" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeDescription?</t>
+        </is>
+      </c>
+      <c r="G201" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
         </is>
       </c>
-      <c r="H201" s="3" t="inlineStr"/>
-      <c r="I201" s="3" t="inlineStr"/>
-      <c r="J201" s="3" t="inlineStr">
-        <is>
-          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.NumAtCard and part/SPL Master evidence also matches.</t>
+      <c r="H201" s="4" t="inlineStr"/>
+      <c r="I201" s="4" t="inlineStr"/>
+      <c r="J201" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>partType</t>
+          <t>isReworkable</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
@@ -31298,7 +31306,7 @@
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.partType?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.isReworkable?</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr">
@@ -31317,12 +31325,12 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>partTypeDescription</t>
+          <t>partNumber</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
@@ -31338,7 +31346,7 @@
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeDescription?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -31357,12 +31365,12 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>isReworkable</t>
+          <t>unitOfMeasure</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
@@ -31378,7 +31386,7 @@
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.isReworkable?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr">
@@ -31397,7 +31405,7 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>partNumber</t>
+          <t>yield</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
@@ -31418,7 +31426,7 @@
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
@@ -31437,12 +31445,12 @@
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>unitOfMeasure</t>
+          <t>Secondary TO</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
@@ -31458,7 +31466,7 @@
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary TO?</t>
         </is>
       </c>
       <c r="G206" s="4" t="inlineStr">
@@ -31477,12 +31485,12 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>yield</t>
+          <t>Secondary FROM</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Yields</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
@@ -31498,7 +31506,7 @@
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary FROM?</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -31517,7 +31525,7 @@
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>Secondary TO</t>
+          <t>Cross TO</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
@@ -31538,7 +31546,7 @@
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary TO?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross TO?</t>
         </is>
       </c>
       <c r="G208" s="4" t="inlineStr">
@@ -31557,7 +31565,7 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>Secondary FROM</t>
+          <t>Cross FROM</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
@@ -31578,7 +31586,7 @@
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary FROM?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross FROM?</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr">
@@ -31597,7 +31605,7 @@
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>Cross TO</t>
+          <t>Primary TO</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
@@ -31618,7 +31626,7 @@
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross TO?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Primary TO?</t>
         </is>
       </c>
       <c r="G210" s="4" t="inlineStr">
@@ -31634,88 +31642,8 @@
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="4" t="inlineStr">
-        <is>
-          <t>Cross FROM</t>
-        </is>
-      </c>
-      <c r="B211" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C211" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D211" s="4" t="inlineStr"/>
-      <c r="E211" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F211" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross FROM?</t>
-        </is>
-      </c>
-      <c r="G211" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H211" s="4" t="inlineStr"/>
-      <c r="I211" s="4" t="inlineStr"/>
-      <c r="J211" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="4" t="inlineStr">
-        <is>
-          <t>Primary TO</t>
-        </is>
-      </c>
-      <c r="B212" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C212" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D212" s="4" t="inlineStr"/>
-      <c r="E212" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F212" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Primary TO?</t>
-        </is>
-      </c>
-      <c r="G212" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H212" s="4" t="inlineStr"/>
-      <c r="I212" s="4" t="inlineStr"/>
-      <c r="J212" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J212"/>
+  <autoFilter ref="A1:J210"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -32343,7 +32271,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>OrderType; orderStartDatetime; orderStatus; resolvedDateTime; relCompanyId; assignedPersonCode</t>
+          <t>OrderType; resolvedDateTime; relCompanyId; assignedPersonCode</t>
         </is>
       </c>
     </row>

--- a/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
+++ b/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Target Fields'!$A$1:$S$151</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Template Fields'!$A$1:$H$177</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Evidence'!$A$1:$D$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$J$210</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$J$200</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Output Objects'!$A$1:$E$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Missing Important Fields'!$A$1:$E$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'SAP Investigation Log'!$A$1:$E$10</definedName>
@@ -244,8 +244,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:J210" headerRowCount="1">
-  <autoFilter ref="A1:J210"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:J200" headerRowCount="1">
+  <autoFilter ref="A1:J200"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Field"/>
     <tableColumn id="2" name="Object"/>
@@ -15359,36 +15359,40 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Vendors</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>vendorId</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Canonical header from Vendors.xlsx</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>SAP Service Layer SQLQueries:OPOR.CardCode</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -15427,40 +15431,44 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Vendors</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>isActive</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Canonical header from Vendors.xlsx</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>SAP Service Layer SQLQueries:OCRD.validFor joined from PO vendor</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -17189,40 +17197,36 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>WarehouseStockOnHand</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>partNumber</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr"/>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr"/>
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>Canonical header from Warehouse Stock on Hand.xlsx</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>SAP Service Layer SQLQueries:OITW.ItemCode</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
@@ -17991,36 +17995,40 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>PartsUsage</t>
         </is>
       </c>
-      <c r="B82" s="4" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>OrderType</t>
         </is>
       </c>
-      <c r="C82" s="4" t="inlineStr"/>
-      <c r="D82" s="4" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr"/>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Canonical header from PartsUsage.xlsx</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr"/>
-      <c r="G82" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Business rule: service_order for all CoCre8 usage</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -20117,268 +20125,296 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="4" t="inlineStr">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>InventoryTransfers</t>
         </is>
       </c>
-      <c r="B137" s="4" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>inventoryTransferImoId</t>
         </is>
       </c>
-      <c r="C137" s="4" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D137" s="4" t="inlineStr">
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Canonical header from Inventory Transfers.xlsx</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F137" s="4" t="inlineStr"/>
-      <c r="G137" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H137" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Stock Audit Report.txt:Document + Item No. + absolute Quantity + pair sequence for IM rows</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="4" t="inlineStr">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>InventoryTransfers</t>
         </is>
       </c>
-      <c r="B138" s="4" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>createdDateTime</t>
         </is>
       </c>
-      <c r="C138" s="4" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
         <is>
           <t>Datetime</t>
         </is>
       </c>
-      <c r="D138" s="4" t="inlineStr">
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Canonical header from Inventory Transfers.xlsx</t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F138" s="4" t="inlineStr"/>
-      <c r="G138" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H138" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Stock Audit Report.txt:Posting Date for paired IM rows</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="4" t="inlineStr">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>InventoryTransfers</t>
         </is>
       </c>
-      <c r="B139" s="4" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>completedDateTime</t>
         </is>
       </c>
-      <c r="C139" s="4" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
         <is>
           <t>Datetime</t>
         </is>
       </c>
-      <c r="D139" s="4" t="inlineStr">
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Canonical header from Inventory Transfers.xlsx</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr"/>
-      <c r="G139" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H139" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Stock Audit Report.txt:Posting Date for paired IM rows</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="4" t="inlineStr">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>InventoryTransfers</t>
         </is>
       </c>
-      <c r="B140" s="4" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>fromWarehouseId</t>
         </is>
       </c>
-      <c r="C140" s="4" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D140" s="4" t="inlineStr">
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Canonical header from Inventory Transfers.xlsx</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr"/>
-      <c r="G140" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H140" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Stock Audit Report.txt:Whse on negative IM quantity row</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="4" t="inlineStr">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>InventoryTransfers</t>
         </is>
       </c>
-      <c r="B141" s="4" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>toWarehouseId</t>
         </is>
       </c>
-      <c r="C141" s="4" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D141" s="4" t="inlineStr">
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Canonical header from Inventory Transfers.xlsx</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr"/>
-      <c r="G141" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H141" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Stock Audit Report.txt:Whse on positive IM quantity row</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="4" t="inlineStr">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>InventoryTransfers</t>
         </is>
       </c>
-      <c r="B142" s="4" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>demandStatus</t>
         </is>
       </c>
-      <c r="C142" s="4" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
         <is>
           <t>Enum&lt;String&gt;</t>
         </is>
       </c>
-      <c r="D142" s="4" t="inlineStr">
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Canonical header from Inventory Transfers.xlsx</t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr"/>
-      <c r="G142" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H142" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Business rule: Fulfilled for posted paired IM rows</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="4" t="inlineStr">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>InventoryTransfers</t>
         </is>
       </c>
-      <c r="B143" s="4" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>orderStatusIsClosed</t>
         </is>
       </c>
-      <c r="C143" s="4" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D143" s="4" t="inlineStr">
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Canonical header from Inventory Transfers.xlsx</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F143" s="4" t="inlineStr"/>
-      <c r="G143" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H143" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Business rule: Y for posted paired IM rows</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -20493,40 +20529,44 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="4" t="inlineStr">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>InventoryTransfers</t>
         </is>
       </c>
-      <c r="B147" s="4" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="C147" s="4" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="D147" s="4" t="inlineStr">
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Canonical header from Inventory Transfers.xlsx</t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F147" s="4" t="inlineStr"/>
-      <c r="G147" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H147" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Stock Audit Report.txt:absolute IM Quantity for paired rows</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -22027,7 +22067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J210"/>
+  <dimension ref="A1:J200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -27845,7 +27885,7 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>vendorId</t>
+          <t>vendorName</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
@@ -27866,7 +27906,7 @@
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Vendors.vendorId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Vendors.vendorName?</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
@@ -27885,12 +27925,12 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>vendorName</t>
+          <t>productClass</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Vendors</t>
+          <t>Parts</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -27901,12 +27941,12 @@
       <c r="D117" s="4" t="inlineStr"/>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Not available in checked source</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Vendors.vendorName?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.productClass?</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
@@ -27918,19 +27958,19 @@
       <c r="I117" s="4" t="inlineStr"/>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. Live SAP item master check found broad ItemGroups such as FUJITSU/ACER/CHOICE and generic ItemType/ItemClass/MaterialType values, not Planning V2 class/type semantics.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>isActive</t>
+          <t>productType</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>Vendors</t>
+          <t>Parts</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
@@ -27941,12 +27981,12 @@
       <c r="D118" s="4" t="inlineStr"/>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Not available in checked source</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Vendors.isActive?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.productType?</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
@@ -27958,14 +27998,14 @@
       <c r="I118" s="4" t="inlineStr"/>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. Live SAP item master check found broad ItemGroups such as FUJITSU/ACER/CHOICE and generic ItemType/ItemClass/MaterialType values, not Planning V2 class/type semantics.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>productClass</t>
+          <t>costCategory</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -27981,12 +28021,12 @@
       <c r="D119" s="4" t="inlineStr"/>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>Not available in checked source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.productClass?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.costCategory?</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
@@ -27998,14 +28038,14 @@
       <c r="I119" s="4" t="inlineStr"/>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>Left blank. Live SAP item master check found broad ItemGroups such as FUJITSU/ACER/CHOICE and generic ItemType/ItemClass/MaterialType values, not Planning V2 class/type semantics.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>productType</t>
+          <t>partType</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
@@ -28026,7 +28066,7 @@
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.productType?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.partType?</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr">
@@ -28045,7 +28085,7 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>costCategory</t>
+          <t>isKit</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -28066,7 +28106,7 @@
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.costCategory?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isKit?</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
@@ -28085,7 +28125,7 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>partType</t>
+          <t>isCritical</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
@@ -28101,12 +28141,12 @@
       <c r="D122" s="4" t="inlineStr"/>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>Not available in checked source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.partType?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isCritical?</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr">
@@ -28118,19 +28158,19 @@
       <c r="I122" s="4" t="inlineStr"/>
       <c r="J122" s="4" t="inlineStr">
         <is>
-          <t>Left blank. Live SAP item master check found broad ItemGroups such as FUJITSU/ACER/CHOICE and generic ItemType/ItemClass/MaterialType values, not Planning V2 class/type semantics.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>isKit</t>
+          <t>externalAddressId</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Parts</t>
+          <t>Addresses</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -28146,7 +28186,7 @@
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isKit?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.externalAddressId?</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
@@ -28158,19 +28198,19 @@
       <c r="I123" s="4" t="inlineStr"/>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>isCritical</t>
+          <t>customerExternalId</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>Parts</t>
+          <t>Addresses</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
@@ -28186,7 +28226,7 @@
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isCritical?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.customerExternalId?</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr">
@@ -28198,14 +28238,14 @@
       <c r="I124" s="4" t="inlineStr"/>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>externalAddressId</t>
+          <t>6,0</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
@@ -28226,7 +28266,7 @@
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.externalAddressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.6,0?</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
@@ -28245,7 +28285,7 @@
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>customerExternalId</t>
+          <t>addressLine2</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
@@ -28266,7 +28306,7 @@
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.customerExternalId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine2?</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr">
@@ -28285,7 +28325,7 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>6,0</t>
+          <t>addressLine3</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -28306,7 +28346,7 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.6,0?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine3?</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
@@ -28325,7 +28365,7 @@
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>addressLine2</t>
+          <t>city</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
@@ -28346,7 +28386,7 @@
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine2?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.city?</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr">
@@ -28365,7 +28405,7 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>addressLine3</t>
+          <t>stateProvince</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -28386,7 +28426,7 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine3?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.stateProvince?</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
@@ -28405,7 +28445,7 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>countryCode</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
@@ -28426,7 +28466,7 @@
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.city?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.countryCode?</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr">
@@ -28445,7 +28485,7 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>stateProvince</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
@@ -28466,7 +28506,7 @@
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.stateProvince?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.latitude?</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
@@ -28485,7 +28525,7 @@
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>countryCode</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
@@ -28506,7 +28546,7 @@
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.countryCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.longitude?</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr">
@@ -28525,7 +28565,7 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>timeZone</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -28546,7 +28586,7 @@
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.latitude?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.timeZone?</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
@@ -28565,7 +28605,7 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>nodeId</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
@@ -28586,7 +28626,7 @@
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.longitude?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.nodeId?</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr">
@@ -28605,12 +28645,12 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>timeZone</t>
+          <t>partNumber</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Addresses</t>
+          <t>WarehouseStockOnHand</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -28626,7 +28666,7 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.timeZone?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseStockOnHand.partNumber?</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
@@ -28645,12 +28685,12 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>nodeId</t>
+          <t>personId</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>Addresses</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -28666,7 +28706,7 @@
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.nodeId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.personId?</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr">
@@ -28685,7 +28725,7 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>personId</t>
+          <t>role</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -28706,7 +28746,7 @@
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.personId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.role?</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
@@ -28725,7 +28765,7 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>addressId</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
@@ -28746,7 +28786,7 @@
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.role?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.addressId?</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr">
@@ -28765,7 +28805,7 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>addressId</t>
+          <t>nodeId</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
@@ -28786,7 +28826,7 @@
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.addressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.nodeId?</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
@@ -28805,7 +28845,7 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>nodeId</t>
+          <t>firstName</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
@@ -28826,7 +28866,7 @@
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.nodeId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.firstName?</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr">
@@ -28845,7 +28885,7 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>firstName</t>
+          <t>middleName</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -28866,7 +28906,7 @@
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.firstName?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.middleName?</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
@@ -28885,7 +28925,7 @@
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>middleName</t>
+          <t>surname</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
@@ -28906,7 +28946,7 @@
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.middleName?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.surname?</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
@@ -28925,7 +28965,7 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>surname</t>
+          <t>isActive</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
@@ -28946,7 +28986,7 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.surname?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.isActive?</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
@@ -28965,7 +29005,7 @@
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>isActive</t>
+          <t>telephoneNumber</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
@@ -28986,7 +29026,7 @@
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.isActive?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.telephoneNumber?</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr">
@@ -29005,7 +29045,7 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>telephoneNumber</t>
+          <t>whs id</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
@@ -29026,7 +29066,7 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.telephoneNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.whs id?</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
@@ -29045,12 +29085,12 @@
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>whs id</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -29066,7 +29106,7 @@
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.whs id?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr">
@@ -29085,7 +29125,7 @@
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>OrderType</t>
+          <t>relCompanyId</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -29106,7 +29146,7 @@
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.OrderType?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
@@ -29125,7 +29165,7 @@
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>assignedPersonCode</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
@@ -29146,7 +29186,7 @@
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr">
@@ -29165,12 +29205,12 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>relCompanyId</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -29186,7 +29226,7 @@
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.orderNumber?</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
@@ -29205,12 +29245,12 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>assignedPersonCode</t>
+          <t>RequestID</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>ServiceOrder</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
@@ -29226,7 +29266,7 @@
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.RequestID?</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr">
@@ -29245,7 +29285,7 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
@@ -29266,7 +29306,7 @@
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.location?</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
@@ -29285,7 +29325,7 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>RequestID</t>
+          <t>eta</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
@@ -29306,7 +29346,7 @@
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.RequestID?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.eta?</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
@@ -29325,7 +29365,7 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>actualEta</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
@@ -29346,7 +29386,7 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.location?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualEta?</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
@@ -29365,7 +29405,7 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>eta</t>
+          <t>actualResolveDateTime</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
@@ -29386,7 +29426,7 @@
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.eta?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualResolveDateTime?</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr">
@@ -29405,7 +29445,7 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>actualEta</t>
+          <t>recallDateTime</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
@@ -29426,7 +29466,7 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualEta?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.recallDateTime?</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
@@ -29445,7 +29485,7 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>actualResolveDateTime</t>
+          <t>actualRecallDateTime</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
@@ -29466,7 +29506,7 @@
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualResolveDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualRecallDateTime?</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr">
@@ -29485,7 +29525,7 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>recallDateTime</t>
+          <t>slaEtaClock</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
@@ -29506,7 +29546,7 @@
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.recallDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaClock?</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
@@ -29525,7 +29565,7 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>actualRecallDateTime</t>
+          <t>slaResolveClock</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
@@ -29546,7 +29586,7 @@
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualRecallDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveClock?</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr">
@@ -29565,7 +29605,7 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>slaEtaClock</t>
+          <t>slaFailureCode</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
@@ -29586,7 +29626,7 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaClock?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaFailureCode?</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
@@ -29605,7 +29645,7 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>slaResolveClock</t>
+          <t>slaEtaHit</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
@@ -29626,7 +29666,7 @@
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveClock?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaHit?</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr">
@@ -29645,7 +29685,7 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>slaFailureCode</t>
+          <t>slaResolveDateTime</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
@@ -29666,7 +29706,7 @@
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaFailureCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveDateTime?</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
@@ -29685,12 +29725,12 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>slaEtaHit</t>
+          <t>orderNumber</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
@@ -29706,7 +29746,7 @@
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaHit?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderNumber?</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr">
@@ -29725,12 +29765,12 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>slaResolveDateTime</t>
+          <t>requestId</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>RepairOrder</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
@@ -29746,7 +29786,7 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.requestId?</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
@@ -29765,7 +29805,7 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>customerCompanyCode</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
@@ -29786,7 +29826,7 @@
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.customerCompanyCode?</t>
         </is>
       </c>
       <c r="G164" s="4" t="inlineStr">
@@ -29805,7 +29845,7 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>requestId</t>
+          <t>orderStatus</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
@@ -29826,7 +29866,7 @@
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.requestId?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStatus?</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
@@ -29845,7 +29885,7 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>customerCompanyCode</t>
+          <t>orderStartDatetime</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
@@ -29866,7 +29906,7 @@
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.customerCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStartDatetime?</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr">
@@ -29885,7 +29925,7 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>orderStatus</t>
+          <t>siteCompanyCode</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
@@ -29906,7 +29946,7 @@
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.siteCompanyCode?</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -29925,7 +29965,7 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>orderStartDatetime</t>
+          <t>repairType</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
@@ -29946,7 +29986,7 @@
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStartDatetime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairType?</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr">
@@ -29965,7 +30005,7 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>siteCompanyCode</t>
+          <t>partsOrderDateTime</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
@@ -29986,7 +30026,7 @@
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.siteCompanyCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsOrderDateTime?</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
@@ -30005,7 +30045,7 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>repairType</t>
+          <t>partsReceivedDateTime</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
@@ -30026,7 +30066,7 @@
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairType?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsReceivedDateTime?</t>
         </is>
       </c>
       <c r="G170" s="4" t="inlineStr">
@@ -30045,7 +30085,7 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>partsOrderDateTime</t>
+          <t>repairCode</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
@@ -30066,7 +30106,7 @@
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsOrderDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCode?</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
@@ -30085,7 +30125,7 @@
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>partsReceivedDateTime</t>
+          <t>repairCompany</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
@@ -30106,7 +30146,7 @@
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsReceivedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCompany?</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr">
@@ -30125,7 +30165,7 @@
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>repairCode</t>
+          <t>raStatus</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
@@ -30146,7 +30186,7 @@
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.raStatus?</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -30165,7 +30205,7 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>repairCompany</t>
+          <t>Warehouse</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
@@ -30186,7 +30226,7 @@
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCompany?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.Warehouse?</t>
         </is>
       </c>
       <c r="G174" s="4" t="inlineStr">
@@ -30205,7 +30245,7 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>raStatus</t>
+          <t>assignedPerson</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
@@ -30226,7 +30266,7 @@
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.raStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.assignedPerson?</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
@@ -30245,7 +30285,7 @@
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
@@ -30266,7 +30306,7 @@
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.Warehouse?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.resolvedDateTime?</t>
         </is>
       </c>
       <c r="G176" s="4" t="inlineStr">
@@ -30285,7 +30325,7 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>assignedPerson</t>
+          <t>serialNumber</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
@@ -30306,7 +30346,7 @@
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.assignedPerson?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.serialNumber?</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
@@ -30325,7 +30365,7 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>quantityUsed</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
@@ -30346,7 +30386,7 @@
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.resolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.quantityUsed?</t>
         </is>
       </c>
       <c r="G178" s="4" t="inlineStr">
@@ -30365,7 +30405,7 @@
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>serialNumber</t>
+          <t>deviceSerialNumber</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
@@ -30386,7 +30426,7 @@
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.serialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.deviceSerialNumber?</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
@@ -30405,7 +30445,7 @@
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>quantityUsed</t>
+          <t>orderedPartId</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
@@ -30426,7 +30466,7 @@
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.quantityUsed?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderedPartId?</t>
         </is>
       </c>
       <c r="G180" s="4" t="inlineStr">
@@ -30445,7 +30485,7 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>deviceSerialNumber</t>
+          <t>actualPartId</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
@@ -30466,7 +30506,7 @@
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.deviceSerialNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate RepairOrder.actualPartId?</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
@@ -30485,12 +30525,12 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>orderedPartId</t>
+          <t>partCode</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
@@ -30506,7 +30546,7 @@
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderedPartId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
         </is>
       </c>
       <c r="G182" s="4" t="inlineStr">
@@ -30525,12 +30565,12 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>actualPartId</t>
+          <t>modelCode</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>RepairOrder</t>
+          <t>Models</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
@@ -30546,7 +30586,7 @@
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.actualPartId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
@@ -30565,7 +30605,7 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>partCode</t>
+          <t>modelDescription</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
@@ -30586,7 +30626,7 @@
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr">
@@ -30605,12 +30645,12 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>modelCode</t>
+          <t>movementType</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
@@ -30626,7 +30666,7 @@
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr">
@@ -30645,12 +30685,12 @@
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>modelDescription</t>
+          <t>addressId</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>Models</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
@@ -30666,7 +30706,7 @@
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
         </is>
       </c>
       <c r="G186" s="4" t="inlineStr">
@@ -30685,7 +30725,7 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>inventoryTransferImoId</t>
+          <t>Bpart</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
@@ -30706,7 +30746,7 @@
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.inventoryTransferImoId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.Bpart?</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr">
@@ -30725,7 +30765,7 @@
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>createdDateTime</t>
+          <t>shipListCode</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
@@ -30746,7 +30786,7 @@
       </c>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.createdDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
         </is>
       </c>
       <c r="G188" s="4" t="inlineStr">
@@ -30763,54 +30803,54 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="4" t="inlineStr">
-        <is>
-          <t>completedDateTime</t>
-        </is>
-      </c>
-      <c r="B189" s="4" t="inlineStr">
-        <is>
-          <t>InventoryTransfers</t>
-        </is>
-      </c>
-      <c r="C189" s="4" t="inlineStr">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>demandStatus</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>PurchaseOrders</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
         <is>
           <t>Planning V2 template</t>
         </is>
       </c>
-      <c r="D189" s="4" t="inlineStr"/>
-      <c r="E189" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F189" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.completedDateTime?</t>
-        </is>
-      </c>
-      <c r="G189" s="4" t="inlineStr">
+      <c r="D189" s="3" t="inlineStr"/>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="F189" s="3" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
+        </is>
+      </c>
+      <c r="G189" s="3" t="inlineStr">
         <is>
           <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
         </is>
       </c>
-      <c r="H189" s="4" t="inlineStr"/>
-      <c r="I189" s="4" t="inlineStr"/>
-      <c r="J189" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="H189" s="3" t="inlineStr"/>
+      <c r="I189" s="3" t="inlineStr"/>
+      <c r="J189" s="3" t="inlineStr">
+        <is>
+          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.NumAtCard and part/SPL Master evidence also matches.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>fromWarehouseId</t>
+          <t>partType</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
@@ -30826,7 +30866,7 @@
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.fromWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.partType?</t>
         </is>
       </c>
       <c r="G190" s="4" t="inlineStr">
@@ -30845,12 +30885,12 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>toWarehouseId</t>
+          <t>partTypeDescription</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
@@ -30866,7 +30906,7 @@
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.toWarehouseId?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeDescription?</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -30885,12 +30925,12 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>demandStatus</t>
+          <t>isReworkable</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
@@ -30906,7 +30946,7 @@
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.demandStatus?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.isReworkable?</t>
         </is>
       </c>
       <c r="G192" s="4" t="inlineStr">
@@ -30925,12 +30965,12 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>orderStatusIsClosed</t>
+          <t>partNumber</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
@@ -30946,7 +30986,7 @@
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.orderStatusIsClosed?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -30965,12 +31005,12 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>movementType</t>
+          <t>unitOfMeasure</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
@@ -30986,7 +31026,7 @@
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr">
@@ -31005,12 +31045,12 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>addressId</t>
+          <t>yield</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>Yields</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -31026,7 +31066,7 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -31045,12 +31085,12 @@
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>Bpart</t>
+          <t>Secondary TO</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
@@ -31066,7 +31106,7 @@
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.Bpart?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary TO?</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr">
@@ -31085,12 +31125,12 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>Secondary FROM</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
@@ -31106,7 +31146,7 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.quantity?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary FROM?</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
@@ -31125,12 +31165,12 @@
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>shipListCode</t>
+          <t>Cross TO</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>InventoryTransfers</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
@@ -31146,7 +31186,7 @@
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross TO?</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr">
@@ -31163,54 +31203,54 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="3" t="inlineStr">
-        <is>
-          <t>demandStatus</t>
-        </is>
-      </c>
-      <c r="B199" s="3" t="inlineStr">
-        <is>
-          <t>PurchaseOrders</t>
-        </is>
-      </c>
-      <c r="C199" s="3" t="inlineStr">
+      <c r="A199" s="4" t="inlineStr">
+        <is>
+          <t>Cross FROM</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>WarehouseExclusions</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
         <is>
           <t>Planning V2 template</t>
         </is>
       </c>
-      <c r="D199" s="3" t="inlineStr"/>
-      <c r="E199" s="3" t="inlineStr">
-        <is>
-          <t>Review required</t>
-        </is>
-      </c>
-      <c r="F199" s="3" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
-        </is>
-      </c>
-      <c r="G199" s="3" t="inlineStr">
+      <c r="D199" s="4" t="inlineStr"/>
+      <c r="E199" s="4" t="inlineStr">
+        <is>
+          <t>Investigate SAP first</t>
+        </is>
+      </c>
+      <c r="F199" s="4" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross FROM?</t>
+        </is>
+      </c>
+      <c r="G199" s="4" t="inlineStr">
         <is>
           <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
         </is>
       </c>
-      <c r="H199" s="3" t="inlineStr"/>
-      <c r="I199" s="3" t="inlineStr"/>
-      <c r="J199" s="3" t="inlineStr">
-        <is>
-          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.NumAtCard and part/SPL Master evidence also matches.</t>
+      <c r="H199" s="4" t="inlineStr"/>
+      <c r="I199" s="4" t="inlineStr"/>
+      <c r="J199" s="4" t="inlineStr">
+        <is>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>partType</t>
+          <t>Primary TO</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>PartTypes</t>
+          <t>WarehouseExclusions</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
@@ -31226,7 +31266,7 @@
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.partType?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Primary TO?</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr">
@@ -31242,408 +31282,8 @@
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="4" t="inlineStr">
-        <is>
-          <t>partTypeDescription</t>
-        </is>
-      </c>
-      <c r="B201" s="4" t="inlineStr">
-        <is>
-          <t>PartTypes</t>
-        </is>
-      </c>
-      <c r="C201" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D201" s="4" t="inlineStr"/>
-      <c r="E201" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F201" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeDescription?</t>
-        </is>
-      </c>
-      <c r="G201" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H201" s="4" t="inlineStr"/>
-      <c r="I201" s="4" t="inlineStr"/>
-      <c r="J201" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="4" t="inlineStr">
-        <is>
-          <t>isReworkable</t>
-        </is>
-      </c>
-      <c r="B202" s="4" t="inlineStr">
-        <is>
-          <t>PartTypes</t>
-        </is>
-      </c>
-      <c r="C202" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D202" s="4" t="inlineStr"/>
-      <c r="E202" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F202" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.isReworkable?</t>
-        </is>
-      </c>
-      <c r="G202" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H202" s="4" t="inlineStr"/>
-      <c r="I202" s="4" t="inlineStr"/>
-      <c r="J202" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="4" t="inlineStr">
-        <is>
-          <t>partNumber</t>
-        </is>
-      </c>
-      <c r="B203" s="4" t="inlineStr">
-        <is>
-          <t>Yields</t>
-        </is>
-      </c>
-      <c r="C203" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D203" s="4" t="inlineStr"/>
-      <c r="E203" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F203" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
-        </is>
-      </c>
-      <c r="G203" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H203" s="4" t="inlineStr"/>
-      <c r="I203" s="4" t="inlineStr"/>
-      <c r="J203" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="4" t="inlineStr">
-        <is>
-          <t>unitOfMeasure</t>
-        </is>
-      </c>
-      <c r="B204" s="4" t="inlineStr">
-        <is>
-          <t>Yields</t>
-        </is>
-      </c>
-      <c r="C204" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D204" s="4" t="inlineStr"/>
-      <c r="E204" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F204" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
-        </is>
-      </c>
-      <c r="G204" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H204" s="4" t="inlineStr"/>
-      <c r="I204" s="4" t="inlineStr"/>
-      <c r="J204" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="4" t="inlineStr">
-        <is>
-          <t>yield</t>
-        </is>
-      </c>
-      <c r="B205" s="4" t="inlineStr">
-        <is>
-          <t>Yields</t>
-        </is>
-      </c>
-      <c r="C205" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D205" s="4" t="inlineStr"/>
-      <c r="E205" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F205" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
-        </is>
-      </c>
-      <c r="G205" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H205" s="4" t="inlineStr"/>
-      <c r="I205" s="4" t="inlineStr"/>
-      <c r="J205" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="4" t="inlineStr">
-        <is>
-          <t>Secondary TO</t>
-        </is>
-      </c>
-      <c r="B206" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C206" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D206" s="4" t="inlineStr"/>
-      <c r="E206" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F206" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary TO?</t>
-        </is>
-      </c>
-      <c r="G206" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H206" s="4" t="inlineStr"/>
-      <c r="I206" s="4" t="inlineStr"/>
-      <c r="J206" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="4" t="inlineStr">
-        <is>
-          <t>Secondary FROM</t>
-        </is>
-      </c>
-      <c r="B207" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C207" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D207" s="4" t="inlineStr"/>
-      <c r="E207" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F207" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary FROM?</t>
-        </is>
-      </c>
-      <c r="G207" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H207" s="4" t="inlineStr"/>
-      <c r="I207" s="4" t="inlineStr"/>
-      <c r="J207" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="4" t="inlineStr">
-        <is>
-          <t>Cross TO</t>
-        </is>
-      </c>
-      <c r="B208" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C208" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D208" s="4" t="inlineStr"/>
-      <c r="E208" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F208" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross TO?</t>
-        </is>
-      </c>
-      <c r="G208" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H208" s="4" t="inlineStr"/>
-      <c r="I208" s="4" t="inlineStr"/>
-      <c r="J208" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="4" t="inlineStr">
-        <is>
-          <t>Cross FROM</t>
-        </is>
-      </c>
-      <c r="B209" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C209" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D209" s="4" t="inlineStr"/>
-      <c r="E209" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F209" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross FROM?</t>
-        </is>
-      </c>
-      <c r="G209" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H209" s="4" t="inlineStr"/>
-      <c r="I209" s="4" t="inlineStr"/>
-      <c r="J209" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="4" t="inlineStr">
-        <is>
-          <t>Primary TO</t>
-        </is>
-      </c>
-      <c r="B210" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C210" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D210" s="4" t="inlineStr"/>
-      <c r="E210" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F210" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Primary TO?</t>
-        </is>
-      </c>
-      <c r="G210" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H210" s="4" t="inlineStr"/>
-      <c r="I210" s="4" t="inlineStr"/>
-      <c r="J210" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J210"/>
+  <autoFilter ref="A1:J200"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -32095,29 +31735,29 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Vendors</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Vendors.csv</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Pending/header only</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>vendorId, vendorName, isActive</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>vendorId; vendorName; isActive</t>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>vendorName</t>
         </is>
       </c>
     </row>
@@ -32199,27 +31839,31 @@
       <c r="E21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>WarehouseStockOnHand</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>WarehouseStockOnHand.csv</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>partNumber, warehouseCode, quantityAllocated, quantityOnHand, quantityInbound, uniqueId</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>partNumber</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -32271,7 +31915,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>OrderType; resolvedDateTime; relCompanyId; assignedPersonCode</t>
+          <t>resolvedDateTime; relCompanyId; assignedPersonCode</t>
         </is>
       </c>
     </row>
@@ -32380,29 +32024,29 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>InventoryTransfers</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>InventoryTransfers.csv</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Pending/header only</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>inventoryTransferImoId, createdDateTime, completedDateTime, fromWarehouseId, toWarehouseId, demandStatus, orderStatusIsClosed, movementType, addressId, Bpart, quantity, shipListCode</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>inventoryTransferImoId; createdDateTime; completedDateTime; fromWarehouseId; toWarehouseId; demandStatus; orderStatusIsClosed; movementType; addressId; Bpart; quantity; shipListCode</t>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>movementType; addressId; Bpart; shipListCode</t>
         </is>
       </c>
     </row>

--- a/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
+++ b/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
@@ -15,15 +15,7 @@
     <sheet name="Missing Important Fields" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="SAP Investigation Log" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Target Fields'!$A$1:$S$151</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Template Fields'!$A$1:$H$177</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Source Evidence'!$A$1:$D$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Unknowns'!$A$1:$J$200</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Output Objects'!$A$1:$E$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Missing Important Fields'!$A$1:$E$88</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'SAP Investigation Log'!$A$1:$E$10</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -183,125 +175,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TargetFields" displayName="TargetFields" ref="A1:S151" headerRowCount="1">
-  <autoFilter ref="A1:S151"/>
-  <tableColumns count="19">
-    <tableColumn id="1" name="Reference Row"/>
-    <tableColumn id="2" name="Field"/>
-    <tableColumn id="3" name="Object"/>
-    <tableColumn id="4" name="Context"/>
-    <tableColumn id="5" name="Used by SPL"/>
-    <tableColumn id="6" name="CC8 Relevant"/>
-    <tableColumn id="7" name="CC8 Supply Hint"/>
-    <tableColumn id="8" name="Priority"/>
-    <tableColumn id="9" name="CC8 Comment"/>
-    <tableColumn id="10" name="Data Type"/>
-    <tableColumn id="11" name="Source Status"/>
-    <tableColumn id="12" name="Source System"/>
-    <tableColumn id="13" name="Source Object"/>
-    <tableColumn id="14" name="Source Field"/>
-    <tableColumn id="15" name="Transform"/>
-    <tableColumn id="16" name="Confidence"/>
-    <tableColumn id="17" name="Explanation"/>
-    <tableColumn id="18" name="Codex"/>
-    <tableColumn id="19" name="Notes"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TemplateFields" displayName="TemplateFields" ref="A1:H177" headerRowCount="1">
-  <autoFilter ref="A1:H177"/>
-  <tableColumns count="8">
-    <tableColumn id="1" name="Template Object"/>
-    <tableColumn id="2" name="Field"/>
-    <tableColumn id="3" name="Field Type"/>
-    <tableColumn id="4" name="Template Notes"/>
-    <tableColumn id="5" name="Source Status"/>
-    <tableColumn id="6" name="Source"/>
-    <tableColumn id="7" name="Confidence"/>
-    <tableColumn id="8" name="Implementation Notes"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SourceEvidence" displayName="SourceEvidence" ref="A1:D15" headerRowCount="1">
-  <autoFilter ref="A1:D15"/>
-  <tableColumns count="4">
-    <tableColumn id="1" name="Source"/>
-    <tableColumn id="2" name="Path"/>
-    <tableColumn id="3" name="Exists"/>
-    <tableColumn id="4" name="Evidence"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Unknowns" displayName="Unknowns" ref="A1:J200" headerRowCount="1">
-  <autoFilter ref="A1:J200"/>
-  <tableColumns count="10">
-    <tableColumn id="1" name="Field"/>
-    <tableColumn id="2" name="Object"/>
-    <tableColumn id="3" name="Context"/>
-    <tableColumn id="4" name="Priority"/>
-    <tableColumn id="5" name="Status"/>
-    <tableColumn id="6" name="Question"/>
-    <tableColumn id="7" name="Next Action"/>
-    <tableColumn id="8" name="CC8 Comment"/>
-    <tableColumn id="9" name="Codex"/>
-    <tableColumn id="10" name="Notes"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="OutputObjects" displayName="OutputObjects" ref="A1:E34" headerRowCount="1">
-  <autoFilter ref="A1:E34"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Object"/>
-    <tableColumn id="2" name="CSV"/>
-    <tableColumn id="3" name="Readiness"/>
-    <tableColumn id="4" name="Fields"/>
-    <tableColumn id="5" name="Blockers"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="MissingImportantFields" displayName="MissingImportantFields" ref="A1:E88" headerRowCount="1">
-  <autoFilter ref="A1:E88"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Potential Gap"/>
-    <tableColumn id="2" name="Why It Matters"/>
-    <tableColumn id="3" name="Reference Evidence"/>
-    <tableColumn id="4" name="Dictionary Evidence"/>
-    <tableColumn id="5" name="Recommended Action"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="SAPInvestigationLog" displayName="SAPInvestigationLog" ref="A1:E10" headerRowCount="1">
-  <autoFilter ref="A1:E10"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Object"/>
-    <tableColumn id="2" name="SAP Candidate"/>
-    <tableColumn id="3" name="Purpose"/>
-    <tableColumn id="4" name="Status"/>
-    <tableColumn id="5" name="Decision"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14841,11 +14714,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S151"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -14911,116 +14780,116 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Nodes</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>nodeId</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Canonical header from Nodes.xlsx</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Deferred post-MVP</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: regional umbrella for warehouse/address hierarchy; not for MVP.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Nodes</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>parentNodeId</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Canonical header from Nodes.xlsx</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Deferred post-MVP</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: regional umbrella for warehouse/address hierarchy; not for MVP.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Nodes</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>nodeDescription</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Canonical header from Nodes.xlsx</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Deferred post-MVP</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: regional umbrella for warehouse/address hierarchy; not for MVP.</t>
         </is>
       </c>
     </row>
@@ -18563,1248 +18432,1248 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="A96" s="5" t="inlineStr">
         <is>
           <t>ServiceOrder</t>
         </is>
       </c>
-      <c r="B96" s="4" t="inlineStr">
+      <c r="B96" s="5" t="inlineStr">
         <is>
           <t>orderNumber</t>
         </is>
       </c>
-      <c r="C96" s="4" t="inlineStr">
+      <c r="C96" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D96" s="4" t="inlineStr">
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>Canonical header from ServiceOrder.xlsx</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr"/>
-      <c r="G96" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>Deferred post-MVP</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr"/>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: this would be the HelpDesk ticket list, but without ticket close times it is not usable for MVP.</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t>ServiceOrder</t>
         </is>
       </c>
-      <c r="B97" s="4" t="inlineStr">
+      <c r="B97" s="5" t="inlineStr">
         <is>
           <t>RequestID</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr"/>
-      <c r="D97" s="4" t="inlineStr">
+      <c r="C97" s="5" t="inlineStr"/>
+      <c r="D97" s="5" t="inlineStr">
         <is>
           <t>Canonical header from ServiceOrder.xlsx</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr"/>
-      <c r="G97" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H97" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>Deferred post-MVP</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr"/>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: this would be the HelpDesk ticket list, but without ticket close times it is not usable for MVP.</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="4" t="inlineStr">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t>ServiceOrder</t>
         </is>
       </c>
-      <c r="B98" s="4" t="inlineStr">
+      <c r="B98" s="5" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="C98" s="4" t="inlineStr">
+      <c r="C98" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D98" s="4" t="inlineStr">
+      <c r="D98" s="5" t="inlineStr">
         <is>
           <t>Canonical header from ServiceOrder.xlsx</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr"/>
-      <c r="G98" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H98" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>Deferred post-MVP</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr"/>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: this would be the HelpDesk ticket list, but without ticket close times it is not usable for MVP.</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="inlineStr">
+      <c r="A99" s="5" t="inlineStr">
         <is>
           <t>ServiceOrder</t>
         </is>
       </c>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>eta</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr">
+      <c r="C99" s="5" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
       </c>
-      <c r="D99" s="4" t="inlineStr">
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>Canonical header from ServiceOrder.xlsx</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr"/>
-      <c r="G99" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H99" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>Deferred post-MVP</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr"/>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: this would be the HelpDesk ticket list, but without ticket close times it is not usable for MVP.</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="inlineStr">
+      <c r="A100" s="5" t="inlineStr">
         <is>
           <t>ServiceOrder</t>
         </is>
       </c>
-      <c r="B100" s="4" t="inlineStr">
+      <c r="B100" s="5" t="inlineStr">
         <is>
           <t>actualEta</t>
         </is>
       </c>
-      <c r="C100" s="4" t="inlineStr">
+      <c r="C100" s="5" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
       </c>
-      <c r="D100" s="4" t="inlineStr">
+      <c r="D100" s="5" t="inlineStr">
         <is>
           <t>Canonical header from ServiceOrder.xlsx</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr"/>
-      <c r="G100" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H100" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>Deferred post-MVP</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr"/>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: this would be the HelpDesk ticket list, but without ticket close times it is not usable for MVP.</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="inlineStr">
+      <c r="A101" s="5" t="inlineStr">
         <is>
           <t>ServiceOrder</t>
         </is>
       </c>
-      <c r="B101" s="4" t="inlineStr">
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>actualResolveDateTime</t>
         </is>
       </c>
-      <c r="C101" s="4" t="inlineStr">
+      <c r="C101" s="5" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
       </c>
-      <c r="D101" s="4" t="inlineStr">
+      <c r="D101" s="5" t="inlineStr">
         <is>
           <t>Canonical header from ServiceOrder.xlsx</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr"/>
-      <c r="G101" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H101" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>Deferred post-MVP</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr"/>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: this would be the HelpDesk ticket list, but without ticket close times it is not usable for MVP.</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="inlineStr">
+      <c r="A102" s="5" t="inlineStr">
         <is>
           <t>ServiceOrder</t>
         </is>
       </c>
-      <c r="B102" s="4" t="inlineStr">
+      <c r="B102" s="5" t="inlineStr">
         <is>
           <t>recallDateTime</t>
         </is>
       </c>
-      <c r="C102" s="4" t="inlineStr">
+      <c r="C102" s="5" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
       </c>
-      <c r="D102" s="4" t="inlineStr">
+      <c r="D102" s="5" t="inlineStr">
         <is>
           <t>Canonical header from ServiceOrder.xlsx</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr"/>
-      <c r="G102" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H102" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>Deferred post-MVP</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr"/>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: this would be the HelpDesk ticket list, but without ticket close times it is not usable for MVP.</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="inlineStr">
+      <c r="A103" s="5" t="inlineStr">
         <is>
           <t>ServiceOrder</t>
         </is>
       </c>
-      <c r="B103" s="4" t="inlineStr">
+      <c r="B103" s="5" t="inlineStr">
         <is>
           <t>actualRecallDateTime</t>
         </is>
       </c>
-      <c r="C103" s="4" t="inlineStr">
+      <c r="C103" s="5" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
       </c>
-      <c r="D103" s="4" t="inlineStr">
+      <c r="D103" s="5" t="inlineStr">
         <is>
           <t>Canonical header from ServiceOrder.xlsx</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr"/>
-      <c r="G103" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H103" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>Deferred post-MVP</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr"/>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: this would be the HelpDesk ticket list, but without ticket close times it is not usable for MVP.</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="4" t="inlineStr">
+      <c r="A104" s="5" t="inlineStr">
         <is>
           <t>ServiceOrder</t>
         </is>
       </c>
-      <c r="B104" s="4" t="inlineStr">
+      <c r="B104" s="5" t="inlineStr">
         <is>
           <t>slaEtaClock</t>
         </is>
       </c>
-      <c r="C104" s="4" t="inlineStr">
+      <c r="C104" s="5" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="D104" s="4" t="inlineStr">
+      <c r="D104" s="5" t="inlineStr">
         <is>
           <t>Canonical header from ServiceOrder.xlsx</t>
         </is>
       </c>
-      <c r="E104" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F104" s="4" t="inlineStr"/>
-      <c r="G104" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H104" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>Deferred post-MVP</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr"/>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: this would be the HelpDesk ticket list, but without ticket close times it is not usable for MVP.</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="4" t="inlineStr">
+      <c r="A105" s="5" t="inlineStr">
         <is>
           <t>ServiceOrder</t>
         </is>
       </c>
-      <c r="B105" s="4" t="inlineStr">
+      <c r="B105" s="5" t="inlineStr">
         <is>
           <t>slaResolveClock</t>
         </is>
       </c>
-      <c r="C105" s="4" t="inlineStr">
+      <c r="C105" s="5" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="D105" s="4" t="inlineStr">
+      <c r="D105" s="5" t="inlineStr">
         <is>
           <t>Canonical header from ServiceOrder.xlsx</t>
         </is>
       </c>
-      <c r="E105" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F105" s="4" t="inlineStr"/>
-      <c r="G105" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H105" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>Deferred post-MVP</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr"/>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: this would be the HelpDesk ticket list, but without ticket close times it is not usable for MVP.</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="4" t="inlineStr">
+      <c r="A106" s="5" t="inlineStr">
         <is>
           <t>ServiceOrder</t>
         </is>
       </c>
-      <c r="B106" s="4" t="inlineStr">
+      <c r="B106" s="5" t="inlineStr">
         <is>
           <t>slaFailureCode</t>
         </is>
       </c>
-      <c r="C106" s="4" t="inlineStr">
+      <c r="C106" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D106" s="4" t="inlineStr">
+      <c r="D106" s="5" t="inlineStr">
         <is>
           <t>Canonical header from ServiceOrder.xlsx</t>
         </is>
       </c>
-      <c r="E106" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F106" s="4" t="inlineStr"/>
-      <c r="G106" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H106" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>Deferred post-MVP</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr"/>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: this would be the HelpDesk ticket list, but without ticket close times it is not usable for MVP.</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="inlineStr">
+      <c r="A107" s="5" t="inlineStr">
         <is>
           <t>ServiceOrder</t>
         </is>
       </c>
-      <c r="B107" s="4" t="inlineStr">
+      <c r="B107" s="5" t="inlineStr">
         <is>
           <t>slaEtaHit</t>
         </is>
       </c>
-      <c r="C107" s="4" t="inlineStr">
+      <c r="C107" s="5" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
       </c>
-      <c r="D107" s="4" t="inlineStr">
+      <c r="D107" s="5" t="inlineStr">
         <is>
           <t>Canonical header from ServiceOrder.xlsx</t>
         </is>
       </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F107" s="4" t="inlineStr"/>
-      <c r="G107" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H107" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>Deferred post-MVP</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr"/>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: this would be the HelpDesk ticket list, but without ticket close times it is not usable for MVP.</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="4" t="inlineStr">
+      <c r="A108" s="5" t="inlineStr">
         <is>
           <t>ServiceOrder</t>
         </is>
       </c>
-      <c r="B108" s="4" t="inlineStr">
+      <c r="B108" s="5" t="inlineStr">
         <is>
           <t>slaResolveDateTime</t>
         </is>
       </c>
-      <c r="C108" s="4" t="inlineStr"/>
-      <c r="D108" s="4" t="inlineStr">
+      <c r="C108" s="5" t="inlineStr"/>
+      <c r="D108" s="5" t="inlineStr">
         <is>
           <t>Canonical header from ServiceOrder.xlsx</t>
         </is>
       </c>
-      <c r="E108" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F108" s="4" t="inlineStr"/>
-      <c r="G108" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H108" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>Deferred post-MVP</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr"/>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: this would be the HelpDesk ticket list, but without ticket close times it is not usable for MVP.</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="inlineStr">
+      <c r="A109" s="5" t="inlineStr">
         <is>
           <t>RepairOrder</t>
         </is>
       </c>
-      <c r="B109" s="4" t="inlineStr">
+      <c r="B109" s="5" t="inlineStr">
         <is>
           <t>orderNumber</t>
         </is>
       </c>
-      <c r="C109" s="4" t="inlineStr">
+      <c r="C109" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D109" s="4" t="inlineStr">
+      <c r="D109" s="5" t="inlineStr">
         <is>
           <t>Canonical header from RepairOrders.xlsx</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr"/>
-      <c r="G109" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H109" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr"/>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: RepairOrder is not used by CoCre8.</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="4" t="inlineStr">
+      <c r="A110" s="5" t="inlineStr">
         <is>
           <t>RepairOrder</t>
         </is>
       </c>
-      <c r="B110" s="4" t="inlineStr">
+      <c r="B110" s="5" t="inlineStr">
         <is>
           <t>requestId</t>
         </is>
       </c>
-      <c r="C110" s="4" t="inlineStr">
+      <c r="C110" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D110" s="4" t="inlineStr">
+      <c r="D110" s="5" t="inlineStr">
         <is>
           <t>Canonical header from RepairOrders.xlsx</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr"/>
-      <c r="G110" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H110" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr"/>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: RepairOrder is not used by CoCre8.</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="inlineStr">
+      <c r="A111" s="5" t="inlineStr">
         <is>
           <t>RepairOrder</t>
         </is>
       </c>
-      <c r="B111" s="4" t="inlineStr">
+      <c r="B111" s="5" t="inlineStr">
         <is>
           <t>customerCompanyCode</t>
         </is>
       </c>
-      <c r="C111" s="4" t="inlineStr">
+      <c r="C111" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D111" s="4" t="inlineStr">
+      <c r="D111" s="5" t="inlineStr">
         <is>
           <t>Canonical header from RepairOrders.xlsx</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F111" s="4" t="inlineStr"/>
-      <c r="G111" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H111" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr"/>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: RepairOrder is not used by CoCre8.</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="4" t="inlineStr">
+      <c r="A112" s="5" t="inlineStr">
         <is>
           <t>RepairOrder</t>
         </is>
       </c>
-      <c r="B112" s="4" t="inlineStr">
+      <c r="B112" s="5" t="inlineStr">
         <is>
           <t>orderStatus</t>
         </is>
       </c>
-      <c r="C112" s="4" t="inlineStr">
+      <c r="C112" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D112" s="4" t="inlineStr">
+      <c r="D112" s="5" t="inlineStr">
         <is>
           <t>Canonical header from RepairOrders.xlsx</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr"/>
-      <c r="G112" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H112" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr"/>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: RepairOrder is not used by CoCre8.</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="inlineStr">
+      <c r="A113" s="5" t="inlineStr">
         <is>
           <t>RepairOrder</t>
         </is>
       </c>
-      <c r="B113" s="4" t="inlineStr">
+      <c r="B113" s="5" t="inlineStr">
         <is>
           <t>orderStartDatetime</t>
         </is>
       </c>
-      <c r="C113" s="4" t="inlineStr">
+      <c r="C113" s="5" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
       </c>
-      <c r="D113" s="4" t="inlineStr">
+      <c r="D113" s="5" t="inlineStr">
         <is>
           <t>Canonical header from RepairOrders.xlsx</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr"/>
-      <c r="G113" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H113" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr"/>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: RepairOrder is not used by CoCre8.</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="4" t="inlineStr">
+      <c r="A114" s="5" t="inlineStr">
         <is>
           <t>RepairOrder</t>
         </is>
       </c>
-      <c r="B114" s="4" t="inlineStr">
+      <c r="B114" s="5" t="inlineStr">
         <is>
           <t>siteCompanyCode</t>
         </is>
       </c>
-      <c r="C114" s="4" t="inlineStr">
+      <c r="C114" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D114" s="4" t="inlineStr">
+      <c r="D114" s="5" t="inlineStr">
         <is>
           <t>Canonical header from RepairOrders.xlsx</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr"/>
-      <c r="G114" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H114" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr"/>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: RepairOrder is not used by CoCre8.</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="4" t="inlineStr">
+      <c r="A115" s="5" t="inlineStr">
         <is>
           <t>RepairOrder</t>
         </is>
       </c>
-      <c r="B115" s="4" t="inlineStr">
+      <c r="B115" s="5" t="inlineStr">
         <is>
           <t>repairType</t>
         </is>
       </c>
-      <c r="C115" s="4" t="inlineStr">
+      <c r="C115" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D115" s="4" t="inlineStr">
+      <c r="D115" s="5" t="inlineStr">
         <is>
           <t>Canonical header from RepairOrders.xlsx</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F115" s="4" t="inlineStr"/>
-      <c r="G115" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H115" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr"/>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: RepairOrder is not used by CoCre8.</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="4" t="inlineStr">
+      <c r="A116" s="5" t="inlineStr">
         <is>
           <t>RepairOrder</t>
         </is>
       </c>
-      <c r="B116" s="4" t="inlineStr">
+      <c r="B116" s="5" t="inlineStr">
         <is>
           <t>partsOrderDateTime</t>
         </is>
       </c>
-      <c r="C116" s="4" t="inlineStr">
+      <c r="C116" s="5" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
       </c>
-      <c r="D116" s="4" t="inlineStr">
+      <c r="D116" s="5" t="inlineStr">
         <is>
           <t>Canonical header from RepairOrders.xlsx</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr"/>
-      <c r="G116" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H116" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr"/>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: RepairOrder is not used by CoCre8.</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="inlineStr">
+      <c r="A117" s="5" t="inlineStr">
         <is>
           <t>RepairOrder</t>
         </is>
       </c>
-      <c r="B117" s="4" t="inlineStr">
+      <c r="B117" s="5" t="inlineStr">
         <is>
           <t>partsReceivedDateTime</t>
         </is>
       </c>
-      <c r="C117" s="4" t="inlineStr">
+      <c r="C117" s="5" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
       </c>
-      <c r="D117" s="4" t="inlineStr">
+      <c r="D117" s="5" t="inlineStr">
         <is>
           <t>Canonical header from RepairOrders.xlsx</t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F117" s="4" t="inlineStr"/>
-      <c r="G117" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H117" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr"/>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: RepairOrder is not used by CoCre8.</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="4" t="inlineStr">
+      <c r="A118" s="5" t="inlineStr">
         <is>
           <t>RepairOrder</t>
         </is>
       </c>
-      <c r="B118" s="4" t="inlineStr">
+      <c r="B118" s="5" t="inlineStr">
         <is>
           <t>repairCode</t>
         </is>
       </c>
-      <c r="C118" s="4" t="inlineStr">
+      <c r="C118" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D118" s="4" t="inlineStr">
+      <c r="D118" s="5" t="inlineStr">
         <is>
           <t>Canonical header from RepairOrders.xlsx</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr"/>
-      <c r="G118" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H118" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr"/>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: RepairOrder is not used by CoCre8.</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="4" t="inlineStr">
+      <c r="A119" s="5" t="inlineStr">
         <is>
           <t>RepairOrder</t>
         </is>
       </c>
-      <c r="B119" s="4" t="inlineStr">
+      <c r="B119" s="5" t="inlineStr">
         <is>
           <t>repairCompany</t>
         </is>
       </c>
-      <c r="C119" s="4" t="inlineStr">
+      <c r="C119" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D119" s="4" t="inlineStr">
+      <c r="D119" s="5" t="inlineStr">
         <is>
           <t>Canonical header from RepairOrders.xlsx</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F119" s="4" t="inlineStr"/>
-      <c r="G119" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H119" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr"/>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: RepairOrder is not used by CoCre8.</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="4" t="inlineStr">
+      <c r="A120" s="5" t="inlineStr">
         <is>
           <t>RepairOrder</t>
         </is>
       </c>
-      <c r="B120" s="4" t="inlineStr">
+      <c r="B120" s="5" t="inlineStr">
         <is>
           <t>raStatus</t>
         </is>
       </c>
-      <c r="C120" s="4" t="inlineStr">
+      <c r="C120" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D120" s="4" t="inlineStr">
+      <c r="D120" s="5" t="inlineStr">
         <is>
           <t>Canonical header from RepairOrders.xlsx</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F120" s="4" t="inlineStr"/>
-      <c r="G120" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H120" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr"/>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: RepairOrder is not used by CoCre8.</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="4" t="inlineStr">
+      <c r="A121" s="5" t="inlineStr">
         <is>
           <t>RepairOrder</t>
         </is>
       </c>
-      <c r="B121" s="4" t="inlineStr">
+      <c r="B121" s="5" t="inlineStr">
         <is>
           <t>Warehouse</t>
         </is>
       </c>
-      <c r="C121" s="4" t="inlineStr">
+      <c r="C121" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D121" s="4" t="inlineStr">
+      <c r="D121" s="5" t="inlineStr">
         <is>
           <t>Canonical header from RepairOrders.xlsx</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr"/>
-      <c r="G121" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H121" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr"/>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: RepairOrder is not used by CoCre8.</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="4" t="inlineStr">
+      <c r="A122" s="5" t="inlineStr">
         <is>
           <t>RepairOrder</t>
         </is>
       </c>
-      <c r="B122" s="4" t="inlineStr">
+      <c r="B122" s="5" t="inlineStr">
         <is>
           <t>assignedPerson</t>
         </is>
       </c>
-      <c r="C122" s="4" t="inlineStr">
+      <c r="C122" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D122" s="4" t="inlineStr">
+      <c r="D122" s="5" t="inlineStr">
         <is>
           <t>Canonical header from RepairOrders.xlsx</t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr"/>
-      <c r="G122" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H122" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr"/>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: RepairOrder is not used by CoCre8.</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="4" t="inlineStr">
+      <c r="A123" s="5" t="inlineStr">
         <is>
           <t>RepairOrder</t>
         </is>
       </c>
-      <c r="B123" s="4" t="inlineStr">
+      <c r="B123" s="5" t="inlineStr">
         <is>
           <t>resolvedDateTime</t>
         </is>
       </c>
-      <c r="C123" s="4" t="inlineStr">
+      <c r="C123" s="5" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
       </c>
-      <c r="D123" s="4" t="inlineStr">
+      <c r="D123" s="5" t="inlineStr">
         <is>
           <t>Canonical header from RepairOrders.xlsx</t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F123" s="4" t="inlineStr"/>
-      <c r="G123" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H123" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr"/>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: RepairOrder is not used by CoCre8.</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="4" t="inlineStr">
+      <c r="A124" s="5" t="inlineStr">
         <is>
           <t>RepairOrder</t>
         </is>
       </c>
-      <c r="B124" s="4" t="inlineStr">
+      <c r="B124" s="5" t="inlineStr">
         <is>
           <t>serialNumber</t>
         </is>
       </c>
-      <c r="C124" s="4" t="inlineStr">
+      <c r="C124" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D124" s="4" t="inlineStr">
+      <c r="D124" s="5" t="inlineStr">
         <is>
           <t>Canonical header from RepairOrders.xlsx</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr"/>
-      <c r="G124" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H124" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr"/>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: RepairOrder is not used by CoCre8.</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="4" t="inlineStr">
+      <c r="A125" s="5" t="inlineStr">
         <is>
           <t>RepairOrder</t>
         </is>
       </c>
-      <c r="B125" s="4" t="inlineStr">
+      <c r="B125" s="5" t="inlineStr">
         <is>
           <t>quantityUsed</t>
         </is>
       </c>
-      <c r="C125" s="4" t="inlineStr">
+      <c r="C125" s="5" t="inlineStr">
         <is>
           <t>Float</t>
         </is>
       </c>
-      <c r="D125" s="4" t="inlineStr">
+      <c r="D125" s="5" t="inlineStr">
         <is>
           <t>Canonical header from RepairOrders.xlsx</t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr"/>
-      <c r="G125" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H125" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr"/>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: RepairOrder is not used by CoCre8.</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="4" t="inlineStr">
+      <c r="A126" s="5" t="inlineStr">
         <is>
           <t>RepairOrder</t>
         </is>
       </c>
-      <c r="B126" s="4" t="inlineStr">
+      <c r="B126" s="5" t="inlineStr">
         <is>
           <t>deviceSerialNumber</t>
         </is>
       </c>
-      <c r="C126" s="4" t="inlineStr">
+      <c r="C126" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D126" s="4" t="inlineStr">
+      <c r="D126" s="5" t="inlineStr">
         <is>
           <t>Canonical header from RepairOrders.xlsx</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="inlineStr"/>
-      <c r="G126" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H126" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="inlineStr"/>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: RepairOrder is not used by CoCre8.</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="4" t="inlineStr">
+      <c r="A127" s="5" t="inlineStr">
         <is>
           <t>RepairOrder</t>
         </is>
       </c>
-      <c r="B127" s="4" t="inlineStr">
+      <c r="B127" s="5" t="inlineStr">
         <is>
           <t>orderedPartId</t>
         </is>
       </c>
-      <c r="C127" s="4" t="inlineStr">
+      <c r="C127" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D127" s="4" t="inlineStr">
+      <c r="D127" s="5" t="inlineStr">
         <is>
           <t>Canonical header from RepairOrders.xlsx</t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr"/>
-      <c r="G127" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H127" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr"/>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: RepairOrder is not used by CoCre8.</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="4" t="inlineStr">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>RepairOrder</t>
         </is>
       </c>
-      <c r="B128" s="4" t="inlineStr">
+      <c r="B128" s="5" t="inlineStr">
         <is>
           <t>actualPartId</t>
         </is>
       </c>
-      <c r="C128" s="4" t="inlineStr">
+      <c r="C128" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D128" s="4" t="inlineStr">
+      <c r="D128" s="5" t="inlineStr">
         <is>
           <t>Canonical header from RepairOrders.xlsx</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr"/>
-      <c r="G128" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H128" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>Out of v1 scope</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr"/>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H128" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: RepairOrder is not used by CoCre8.</t>
         </is>
       </c>
     </row>
@@ -20011,116 +19880,116 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="4" t="inlineStr">
+      <c r="A134" s="5" t="inlineStr">
         <is>
           <t>Models</t>
         </is>
       </c>
-      <c r="B134" s="4" t="inlineStr">
+      <c r="B134" s="5" t="inlineStr">
         <is>
           <t>partCode</t>
         </is>
       </c>
-      <c r="C134" s="4" t="inlineStr">
+      <c r="C134" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D134" s="4" t="inlineStr">
+      <c r="D134" s="5" t="inlineStr">
         <is>
           <t>Canonical header from Models.xlsx</t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr"/>
-      <c r="G134" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H134" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>Deferred post-MVP</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr"/>
+      <c r="G134" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H134" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: important, but not for MVP.</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="4" t="inlineStr">
+      <c r="A135" s="5" t="inlineStr">
         <is>
           <t>Models</t>
         </is>
       </c>
-      <c r="B135" s="4" t="inlineStr">
+      <c r="B135" s="5" t="inlineStr">
         <is>
           <t>modelCode</t>
         </is>
       </c>
-      <c r="C135" s="4" t="inlineStr">
+      <c r="C135" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D135" s="4" t="inlineStr">
+      <c r="D135" s="5" t="inlineStr">
         <is>
           <t>Canonical header from Models.xlsx</t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F135" s="4" t="inlineStr"/>
-      <c r="G135" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H135" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>Deferred post-MVP</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr"/>
+      <c r="G135" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: important, but not for MVP.</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="4" t="inlineStr">
+      <c r="A136" s="5" t="inlineStr">
         <is>
           <t>Models</t>
         </is>
       </c>
-      <c r="B136" s="4" t="inlineStr">
+      <c r="B136" s="5" t="inlineStr">
         <is>
           <t>modelDescription</t>
         </is>
       </c>
-      <c r="C136" s="4" t="inlineStr">
+      <c r="C136" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D136" s="4" t="inlineStr">
+      <c r="D136" s="5" t="inlineStr">
         <is>
           <t>Canonical header from Models.xlsx</t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr"/>
-      <c r="G136" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H136" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>Deferred post-MVP</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr"/>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: important, but not for MVP.</t>
         </is>
       </c>
     </row>
@@ -21211,116 +21080,116 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="4" t="inlineStr">
+      <c r="A164" s="5" t="inlineStr">
         <is>
           <t>Yields</t>
         </is>
       </c>
-      <c r="B164" s="4" t="inlineStr">
+      <c r="B164" s="5" t="inlineStr">
         <is>
           <t>partNumber</t>
         </is>
       </c>
-      <c r="C164" s="4" t="inlineStr">
+      <c r="C164" s="5" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D164" s="4" t="inlineStr">
+      <c r="D164" s="5" t="inlineStr">
         <is>
           <t>Canonical header from Yields.xlsx</t>
         </is>
       </c>
-      <c r="E164" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F164" s="4" t="inlineStr"/>
-      <c r="G164" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H164" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E164" s="5" t="inlineStr">
+        <is>
+          <t>Deferred post-MVP</t>
+        </is>
+      </c>
+      <c r="F164" s="5" t="inlineStr"/>
+      <c r="G164" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H164" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: yield means expected uses or average years before breakdown; not for MVP.</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="4" t="inlineStr">
+      <c r="A165" s="5" t="inlineStr">
         <is>
           <t>Yields</t>
         </is>
       </c>
-      <c r="B165" s="4" t="inlineStr">
+      <c r="B165" s="5" t="inlineStr">
         <is>
           <t>unitOfMeasure</t>
         </is>
       </c>
-      <c r="C165" s="4" t="inlineStr">
+      <c r="C165" s="5" t="inlineStr">
         <is>
           <t>Enum&lt;String&gt;</t>
         </is>
       </c>
-      <c r="D165" s="4" t="inlineStr">
+      <c r="D165" s="5" t="inlineStr">
         <is>
           <t>Canonical header from Yields.xlsx</t>
         </is>
       </c>
-      <c r="E165" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F165" s="4" t="inlineStr"/>
-      <c r="G165" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H165" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E165" s="5" t="inlineStr">
+        <is>
+          <t>Deferred post-MVP</t>
+        </is>
+      </c>
+      <c r="F165" s="5" t="inlineStr"/>
+      <c r="G165" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H165" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: yield means expected uses or average years before breakdown; not for MVP.</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="4" t="inlineStr">
+      <c r="A166" s="5" t="inlineStr">
         <is>
           <t>Yields</t>
         </is>
       </c>
-      <c r="B166" s="4" t="inlineStr">
+      <c r="B166" s="5" t="inlineStr">
         <is>
           <t>yield</t>
         </is>
       </c>
-      <c r="C166" s="4" t="inlineStr">
+      <c r="C166" s="5" t="inlineStr">
         <is>
           <t>Double</t>
         </is>
       </c>
-      <c r="D166" s="4" t="inlineStr">
+      <c r="D166" s="5" t="inlineStr">
         <is>
           <t>Canonical header from Yields.xlsx</t>
         </is>
       </c>
-      <c r="E166" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F166" s="4" t="inlineStr"/>
-      <c r="G166" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H166" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E166" s="5" t="inlineStr">
+        <is>
+          <t>Deferred post-MVP</t>
+        </is>
+      </c>
+      <c r="F166" s="5" t="inlineStr"/>
+      <c r="G166" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H166" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: yield means expected uses or average years before breakdown; not for MVP.</t>
         </is>
       </c>
     </row>
@@ -21529,181 +21398,197 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="4" t="inlineStr">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>WarehouseExclusions</t>
         </is>
       </c>
-      <c r="B173" s="4" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>Secondary TO</t>
         </is>
       </c>
-      <c r="C173" s="4" t="inlineStr"/>
-      <c r="D173" s="4" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr"/>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Canonical header from Warehouse Distribution Exclusions.xlsx</t>
         </is>
       </c>
-      <c r="E173" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F173" s="4" t="inlineStr"/>
-      <c r="G173" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H173" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Business decision</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>Chris feedback: no warehouse exclusions to start with; empty upload is intentional.</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="4" t="inlineStr">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>WarehouseExclusions</t>
         </is>
       </c>
-      <c r="B174" s="4" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>Secondary FROM</t>
         </is>
       </c>
-      <c r="C174" s="4" t="inlineStr"/>
-      <c r="D174" s="4" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr"/>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Canonical header from Warehouse Distribution Exclusions.xlsx</t>
         </is>
       </c>
-      <c r="E174" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F174" s="4" t="inlineStr"/>
-      <c r="G174" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H174" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Business decision</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>Chris feedback: no warehouse exclusions to start with; empty upload is intentional.</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="4" t="inlineStr">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>WarehouseExclusions</t>
         </is>
       </c>
-      <c r="B175" s="4" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>Cross TO</t>
         </is>
       </c>
-      <c r="C175" s="4" t="inlineStr"/>
-      <c r="D175" s="4" t="inlineStr">
+      <c r="C175" s="2" t="inlineStr"/>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Canonical header from Warehouse Distribution Exclusions.xlsx</t>
         </is>
       </c>
-      <c r="E175" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F175" s="4" t="inlineStr"/>
-      <c r="G175" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H175" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>Business decision</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>Chris feedback: no warehouse exclusions to start with; empty upload is intentional.</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="4" t="inlineStr">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>WarehouseExclusions</t>
         </is>
       </c>
-      <c r="B176" s="4" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>Cross FROM</t>
         </is>
       </c>
-      <c r="C176" s="4" t="inlineStr"/>
-      <c r="D176" s="4" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr"/>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Canonical header from Warehouse Distribution Exclusions.xlsx</t>
         </is>
       </c>
-      <c r="E176" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F176" s="4" t="inlineStr"/>
-      <c r="G176" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H176" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>Business decision</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>Chris feedback: no warehouse exclusions to start with; empty upload is intentional.</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="4" t="inlineStr">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>WarehouseExclusions</t>
         </is>
       </c>
-      <c r="B177" s="4" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>Primary TO</t>
         </is>
       </c>
-      <c r="C177" s="4" t="inlineStr"/>
-      <c r="D177" s="4" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr"/>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Canonical header from Warehouse Distribution Exclusions.xlsx</t>
         </is>
       </c>
-      <c r="E177" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F177" s="4" t="inlineStr"/>
-      <c r="G177" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H177" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>Business decision</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>Chris feedback: no warehouse exclusions to start with; empty upload is intentional.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H177"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -22053,11 +21938,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -22067,7 +21948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J200"/>
+  <dimension ref="A1:J153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -27405,12 +27286,12 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>nodeId</t>
+          <t>customerId</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Nodes</t>
+          <t>Customers</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -27421,12 +27302,12 @@
       <c r="D104" s="4" t="inlineStr"/>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Nodes.nodeId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.customerId?</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
@@ -27438,19 +27319,19 @@
       <c r="I104" s="4" t="inlineStr"/>
       <c r="J104" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. SAP BusinessPartners can supply customer codes, but the correct Planning V2 customer scope is not confirmed.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>parentNodeId</t>
+          <t>customerName</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Nodes</t>
+          <t>Customers</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -27466,7 +27347,7 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Nodes.parentNodeId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.customerName?</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
@@ -27485,12 +27366,12 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>nodeDescription</t>
+          <t>customerGroupId</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Nodes</t>
+          <t>Customers</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -27501,12 +27382,12 @@
       <c r="D106" s="4" t="inlineStr"/>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Nodes.nodeDescription?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.customerGroupId?</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
@@ -27518,14 +27399,14 @@
       <c r="I106" s="4" t="inlineStr"/>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User has no confirmed source yet for customer grouping.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>customerId</t>
+          <t>assignAnySkill</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -27546,7 +27427,7 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Customers.customerId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.assignAnySkill?</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
@@ -27558,14 +27439,14 @@
       <c r="I107" s="4" t="inlineStr"/>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>Left blank. SAP BusinessPartners can supply customer codes, but the correct Planning V2 customer scope is not confirmed.</t>
+          <t>Left blank. User has no confirmed source yet for customer skill assignment rules.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>customerName</t>
+          <t>isActive</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
@@ -27581,12 +27462,12 @@
       <c r="D108" s="4" t="inlineStr"/>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>Investigate SAP first</t>
+          <t>Investigate source</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Customers.customerName?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.isActive?</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
@@ -27598,14 +27479,14 @@
       <c r="I108" s="4" t="inlineStr"/>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User has no confirmed source yet for customer active/inactive status.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>customerGroupId</t>
+          <t>dseSlaCost</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -27626,7 +27507,7 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Customers.customerGroupId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.dseSlaCost?</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
@@ -27638,14 +27519,14 @@
       <c r="I109" s="4" t="inlineStr"/>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User has no confirmed source yet for customer grouping.</t>
+          <t>Left blank. User has no confirmed source yet for SLA cost.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>assignAnySkill</t>
+          <t>dseSlaRevenue</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
@@ -27666,7 +27547,7 @@
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Customers.assignAnySkill?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.dseSlaRevenue?</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
@@ -27678,14 +27559,14 @@
       <c r="I110" s="4" t="inlineStr"/>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User has no confirmed source yet for customer skill assignment rules.</t>
+          <t>Left blank. User has no confirmed source yet for SLA revenue.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>isActive</t>
+          <t>stdResponseTime</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -27706,7 +27587,7 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Customers.isActive?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.stdResponseTime?</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
@@ -27718,14 +27599,14 @@
       <c r="I111" s="4" t="inlineStr"/>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User has no confirmed source yet for customer active/inactive status.</t>
+          <t>Left blank. User has no confirmed source yet for standard response time.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>dseSlaCost</t>
+          <t>stdRepairTime</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
@@ -27746,7 +27627,7 @@
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Customers.dseSlaCost?</t>
+          <t>What confirmed CoCre8/SAP source should populate Customers.stdRepairTime?</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
@@ -27758,19 +27639,19 @@
       <c r="I112" s="4" t="inlineStr"/>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User has no confirmed source yet for SLA cost.</t>
+          <t>Left blank. User has no confirmed source yet for standard repair time.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>dseSlaRevenue</t>
+          <t>vendorName</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Vendors</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -27781,12 +27662,12 @@
       <c r="D113" s="4" t="inlineStr"/>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>Investigate source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Customers.dseSlaRevenue?</t>
+          <t>What confirmed CoCre8/SAP source should populate Vendors.vendorName?</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
@@ -27798,19 +27679,19 @@
       <c r="I113" s="4" t="inlineStr"/>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User has no confirmed source yet for SLA revenue.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>stdResponseTime</t>
+          <t>productClass</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Parts</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -27821,12 +27702,12 @@
       <c r="D114" s="4" t="inlineStr"/>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>Investigate source</t>
+          <t>Not available in checked source</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Customers.stdResponseTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.productClass?</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
@@ -27838,19 +27719,19 @@
       <c r="I114" s="4" t="inlineStr"/>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User has no confirmed source yet for standard response time.</t>
+          <t>Left blank. Live SAP item master check found broad ItemGroups such as FUJITSU/ACER/CHOICE and generic ItemType/ItemClass/MaterialType values, not Planning V2 class/type semantics.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>stdRepairTime</t>
+          <t>productType</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Parts</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -27861,12 +27742,12 @@
       <c r="D115" s="4" t="inlineStr"/>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>Investigate source</t>
+          <t>Not available in checked source</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Customers.stdRepairTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.productType?</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
@@ -27878,19 +27759,19 @@
       <c r="I115" s="4" t="inlineStr"/>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User has no confirmed source yet for standard repair time.</t>
+          <t>Left blank. Live SAP item master check found broad ItemGroups such as FUJITSU/ACER/CHOICE and generic ItemType/ItemClass/MaterialType values, not Planning V2 class/type semantics.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>vendorName</t>
+          <t>costCategory</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>Vendors</t>
+          <t>Parts</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -27906,7 +27787,7 @@
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Vendors.vendorName?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.costCategory?</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
@@ -27918,14 +27799,14 @@
       <c r="I116" s="4" t="inlineStr"/>
       <c r="J116" s="4" t="inlineStr">
         <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>productClass</t>
+          <t>partType</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -27946,7 +27827,7 @@
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.productClass?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.partType?</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
@@ -27965,7 +27846,7 @@
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>productType</t>
+          <t>isKit</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
@@ -27981,12 +27862,12 @@
       <c r="D118" s="4" t="inlineStr"/>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>Not available in checked source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.productType?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isKit?</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
@@ -27998,14 +27879,14 @@
       <c r="I118" s="4" t="inlineStr"/>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>Left blank. Live SAP item master check found broad ItemGroups such as FUJITSU/ACER/CHOICE and generic ItemType/ItemClass/MaterialType values, not Planning V2 class/type semantics.</t>
+          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>costCategory</t>
+          <t>isCritical</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -28026,7 +27907,7 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.costCategory?</t>
+          <t>What confirmed CoCre8/SAP source should populate Parts.isCritical?</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
@@ -28045,12 +27926,12 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>partType</t>
+          <t>externalAddressId</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>Parts</t>
+          <t>Addresses</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
@@ -28061,12 +27942,12 @@
       <c r="D120" s="4" t="inlineStr"/>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>Not available in checked source</t>
+          <t>Investigate SAP first</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.partType?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.externalAddressId?</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr">
@@ -28078,19 +27959,19 @@
       <c r="I120" s="4" t="inlineStr"/>
       <c r="J120" s="4" t="inlineStr">
         <is>
-          <t>Left blank. Live SAP item master check found broad ItemGroups such as FUJITSU/ACER/CHOICE and generic ItemType/ItemClass/MaterialType values, not Planning V2 class/type semantics.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>isKit</t>
+          <t>customerExternalId</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Parts</t>
+          <t>Addresses</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -28106,7 +27987,7 @@
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isKit?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.customerExternalId?</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
@@ -28118,19 +27999,19 @@
       <c r="I121" s="4" t="inlineStr"/>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>isCritical</t>
+          <t>6,0</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>Parts</t>
+          <t>Addresses</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -28146,7 +28027,7 @@
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Parts.isCritical?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.6,0?</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr">
@@ -28158,14 +28039,14 @@
       <c r="I122" s="4" t="inlineStr"/>
       <c r="J122" s="4" t="inlineStr">
         <is>
-          <t>Left blank. User indicated this field is unlikely to be available from current CoCre8 sources.</t>
+          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>externalAddressId</t>
+          <t>addressLine2</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
@@ -28186,7 +28067,7 @@
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.externalAddressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine2?</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
@@ -28205,7 +28086,7 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>customerExternalId</t>
+          <t>addressLine3</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
@@ -28226,7 +28107,7 @@
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.customerExternalId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine3?</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr">
@@ -28245,7 +28126,7 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>6,0</t>
+          <t>city</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
@@ -28266,7 +28147,7 @@
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.6,0?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.city?</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
@@ -28285,7 +28166,7 @@
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>addressLine2</t>
+          <t>stateProvince</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
@@ -28306,7 +28187,7 @@
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine2?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.stateProvince?</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr">
@@ -28325,7 +28206,7 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>addressLine3</t>
+          <t>countryCode</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -28346,7 +28227,7 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.addressLine3?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.countryCode?</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
@@ -28365,7 +28246,7 @@
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
@@ -28386,7 +28267,7 @@
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.city?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.latitude?</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr">
@@ -28405,7 +28286,7 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>stateProvince</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -28426,7 +28307,7 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.stateProvince?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.longitude?</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
@@ -28445,7 +28326,7 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>countryCode</t>
+          <t>timeZone</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
@@ -28466,7 +28347,7 @@
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.countryCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.timeZone?</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr">
@@ -28485,7 +28366,7 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>nodeId</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
@@ -28506,7 +28387,7 @@
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.latitude?</t>
+          <t>What confirmed CoCre8/SAP source should populate Addresses.nodeId?</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
@@ -28525,12 +28406,12 @@
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>partNumber</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>Addresses</t>
+          <t>WarehouseStockOnHand</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -28546,7 +28427,7 @@
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.longitude?</t>
+          <t>What confirmed CoCre8/SAP source should populate WarehouseStockOnHand.partNumber?</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr">
@@ -28565,12 +28446,12 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>timeZone</t>
+          <t>personId</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Addresses</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -28586,7 +28467,7 @@
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.timeZone?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.personId?</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
@@ -28605,12 +28486,12 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>nodeId</t>
+          <t>role</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>Addresses</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -28626,7 +28507,7 @@
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Addresses.nodeId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.role?</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr">
@@ -28645,12 +28526,12 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>partNumber</t>
+          <t>addressId</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>WarehouseStockOnHand</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -28666,7 +28547,7 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseStockOnHand.partNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.addressId?</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
@@ -28685,7 +28566,7 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>personId</t>
+          <t>nodeId</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
@@ -28706,7 +28587,7 @@
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.personId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.nodeId?</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr">
@@ -28725,7 +28606,7 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>firstName</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -28746,7 +28627,7 @@
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.role?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.firstName?</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
@@ -28765,7 +28646,7 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>addressId</t>
+          <t>middleName</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
@@ -28786,7 +28667,7 @@
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.addressId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.middleName?</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr">
@@ -28805,7 +28686,7 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>nodeId</t>
+          <t>surname</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
@@ -28826,7 +28707,7 @@
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.nodeId?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.surname?</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
@@ -28845,7 +28726,7 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>firstName</t>
+          <t>isActive</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
@@ -28866,7 +28747,7 @@
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.firstName?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.isActive?</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr">
@@ -28885,7 +28766,7 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>middleName</t>
+          <t>telephoneNumber</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -28906,7 +28787,7 @@
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.middleName?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.telephoneNumber?</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
@@ -28925,7 +28806,7 @@
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>surname</t>
+          <t>whs id</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
@@ -28946,7 +28827,7 @@
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.surname?</t>
+          <t>What confirmed CoCre8/SAP source should populate Employees.whs id?</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
@@ -28965,12 +28846,12 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>isActive</t>
+          <t>resolvedDateTime</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -28986,7 +28867,7 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.isActive?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
@@ -29005,12 +28886,12 @@
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>telephoneNumber</t>
+          <t>relCompanyId</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -29026,7 +28907,7 @@
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.telephoneNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr">
@@ -29045,12 +28926,12 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>whs id</t>
+          <t>assignedPersonCode</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Employees</t>
+          <t>PartsUsage</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -29066,7 +28947,7 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate Employees.whs id?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
@@ -29085,12 +28966,12 @@
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>resolvedDateTime</t>
+          <t>movementType</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -29106,7 +28987,7 @@
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.resolvedDateTime?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr">
@@ -29125,12 +29006,12 @@
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>relCompanyId</t>
+          <t>addressId</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -29146,7 +29027,7 @@
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.relCompanyId?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
@@ -29165,12 +29046,12 @@
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>assignedPersonCode</t>
+          <t>Bpart</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>PartsUsage</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
@@ -29186,7 +29067,7 @@
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartsUsage.assignedPersonCode?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.Bpart?</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr">
@@ -29205,12 +29086,12 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>orderNumber</t>
+          <t>shipListCode</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>InventoryTransfers</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -29226,7 +29107,7 @@
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.orderNumber?</t>
+          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
@@ -29243,54 +29124,54 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="4" t="inlineStr">
-        <is>
-          <t>RequestID</t>
-        </is>
-      </c>
-      <c r="B150" s="4" t="inlineStr">
-        <is>
-          <t>ServiceOrder</t>
-        </is>
-      </c>
-      <c r="C150" s="4" t="inlineStr">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>demandStatus</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>PurchaseOrders</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
         <is>
           <t>Planning V2 template</t>
         </is>
       </c>
-      <c r="D150" s="4" t="inlineStr"/>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.RequestID?</t>
-        </is>
-      </c>
-      <c r="G150" s="4" t="inlineStr">
+      <c r="D150" s="3" t="inlineStr"/>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>Review required</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
         <is>
           <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
         </is>
       </c>
-      <c r="H150" s="4" t="inlineStr"/>
-      <c r="I150" s="4" t="inlineStr"/>
-      <c r="J150" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="H150" s="3" t="inlineStr"/>
+      <c r="I150" s="3" t="inlineStr"/>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.NumAtCard and part/SPL Master evidence also matches.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>partType</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -29306,7 +29187,7 @@
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.location?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.partType?</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
@@ -29325,12 +29206,12 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>eta</t>
+          <t>partTypeDescription</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
@@ -29346,7 +29227,7 @@
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.eta?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeDescription?</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
@@ -29365,12 +29246,12 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>actualEta</t>
+          <t>isReworkable</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>ServiceOrder</t>
+          <t>PartTypes</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -29386,7 +29267,7 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualEta?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.isReworkable?</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
@@ -29402,1892 +29283,8 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="4" t="inlineStr">
-        <is>
-          <t>actualResolveDateTime</t>
-        </is>
-      </c>
-      <c r="B154" s="4" t="inlineStr">
-        <is>
-          <t>ServiceOrder</t>
-        </is>
-      </c>
-      <c r="C154" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D154" s="4" t="inlineStr"/>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F154" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualResolveDateTime?</t>
-        </is>
-      </c>
-      <c r="G154" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H154" s="4" t="inlineStr"/>
-      <c r="I154" s="4" t="inlineStr"/>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="4" t="inlineStr">
-        <is>
-          <t>recallDateTime</t>
-        </is>
-      </c>
-      <c r="B155" s="4" t="inlineStr">
-        <is>
-          <t>ServiceOrder</t>
-        </is>
-      </c>
-      <c r="C155" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="inlineStr"/>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.recallDateTime?</t>
-        </is>
-      </c>
-      <c r="G155" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H155" s="4" t="inlineStr"/>
-      <c r="I155" s="4" t="inlineStr"/>
-      <c r="J155" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="4" t="inlineStr">
-        <is>
-          <t>actualRecallDateTime</t>
-        </is>
-      </c>
-      <c r="B156" s="4" t="inlineStr">
-        <is>
-          <t>ServiceOrder</t>
-        </is>
-      </c>
-      <c r="C156" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D156" s="4" t="inlineStr"/>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.actualRecallDateTime?</t>
-        </is>
-      </c>
-      <c r="G156" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H156" s="4" t="inlineStr"/>
-      <c r="I156" s="4" t="inlineStr"/>
-      <c r="J156" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="4" t="inlineStr">
-        <is>
-          <t>slaEtaClock</t>
-        </is>
-      </c>
-      <c r="B157" s="4" t="inlineStr">
-        <is>
-          <t>ServiceOrder</t>
-        </is>
-      </c>
-      <c r="C157" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D157" s="4" t="inlineStr"/>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaClock?</t>
-        </is>
-      </c>
-      <c r="G157" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H157" s="4" t="inlineStr"/>
-      <c r="I157" s="4" t="inlineStr"/>
-      <c r="J157" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="4" t="inlineStr">
-        <is>
-          <t>slaResolveClock</t>
-        </is>
-      </c>
-      <c r="B158" s="4" t="inlineStr">
-        <is>
-          <t>ServiceOrder</t>
-        </is>
-      </c>
-      <c r="C158" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D158" s="4" t="inlineStr"/>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveClock?</t>
-        </is>
-      </c>
-      <c r="G158" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H158" s="4" t="inlineStr"/>
-      <c r="I158" s="4" t="inlineStr"/>
-      <c r="J158" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="4" t="inlineStr">
-        <is>
-          <t>slaFailureCode</t>
-        </is>
-      </c>
-      <c r="B159" s="4" t="inlineStr">
-        <is>
-          <t>ServiceOrder</t>
-        </is>
-      </c>
-      <c r="C159" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D159" s="4" t="inlineStr"/>
-      <c r="E159" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F159" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaFailureCode?</t>
-        </is>
-      </c>
-      <c r="G159" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H159" s="4" t="inlineStr"/>
-      <c r="I159" s="4" t="inlineStr"/>
-      <c r="J159" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="4" t="inlineStr">
-        <is>
-          <t>slaEtaHit</t>
-        </is>
-      </c>
-      <c r="B160" s="4" t="inlineStr">
-        <is>
-          <t>ServiceOrder</t>
-        </is>
-      </c>
-      <c r="C160" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D160" s="4" t="inlineStr"/>
-      <c r="E160" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F160" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaEtaHit?</t>
-        </is>
-      </c>
-      <c r="G160" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H160" s="4" t="inlineStr"/>
-      <c r="I160" s="4" t="inlineStr"/>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="4" t="inlineStr">
-        <is>
-          <t>slaResolveDateTime</t>
-        </is>
-      </c>
-      <c r="B161" s="4" t="inlineStr">
-        <is>
-          <t>ServiceOrder</t>
-        </is>
-      </c>
-      <c r="C161" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D161" s="4" t="inlineStr"/>
-      <c r="E161" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F161" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate ServiceOrder.slaResolveDateTime?</t>
-        </is>
-      </c>
-      <c r="G161" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H161" s="4" t="inlineStr"/>
-      <c r="I161" s="4" t="inlineStr"/>
-      <c r="J161" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="4" t="inlineStr">
-        <is>
-          <t>orderNumber</t>
-        </is>
-      </c>
-      <c r="B162" s="4" t="inlineStr">
-        <is>
-          <t>RepairOrder</t>
-        </is>
-      </c>
-      <c r="C162" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D162" s="4" t="inlineStr"/>
-      <c r="E162" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F162" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderNumber?</t>
-        </is>
-      </c>
-      <c r="G162" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H162" s="4" t="inlineStr"/>
-      <c r="I162" s="4" t="inlineStr"/>
-      <c r="J162" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="4" t="inlineStr">
-        <is>
-          <t>requestId</t>
-        </is>
-      </c>
-      <c r="B163" s="4" t="inlineStr">
-        <is>
-          <t>RepairOrder</t>
-        </is>
-      </c>
-      <c r="C163" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D163" s="4" t="inlineStr"/>
-      <c r="E163" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F163" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.requestId?</t>
-        </is>
-      </c>
-      <c r="G163" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H163" s="4" t="inlineStr"/>
-      <c r="I163" s="4" t="inlineStr"/>
-      <c r="J163" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="4" t="inlineStr">
-        <is>
-          <t>customerCompanyCode</t>
-        </is>
-      </c>
-      <c r="B164" s="4" t="inlineStr">
-        <is>
-          <t>RepairOrder</t>
-        </is>
-      </c>
-      <c r="C164" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D164" s="4" t="inlineStr"/>
-      <c r="E164" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F164" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.customerCompanyCode?</t>
-        </is>
-      </c>
-      <c r="G164" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H164" s="4" t="inlineStr"/>
-      <c r="I164" s="4" t="inlineStr"/>
-      <c r="J164" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="4" t="inlineStr">
-        <is>
-          <t>orderStatus</t>
-        </is>
-      </c>
-      <c r="B165" s="4" t="inlineStr">
-        <is>
-          <t>RepairOrder</t>
-        </is>
-      </c>
-      <c r="C165" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D165" s="4" t="inlineStr"/>
-      <c r="E165" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F165" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStatus?</t>
-        </is>
-      </c>
-      <c r="G165" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H165" s="4" t="inlineStr"/>
-      <c r="I165" s="4" t="inlineStr"/>
-      <c r="J165" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="4" t="inlineStr">
-        <is>
-          <t>orderStartDatetime</t>
-        </is>
-      </c>
-      <c r="B166" s="4" t="inlineStr">
-        <is>
-          <t>RepairOrder</t>
-        </is>
-      </c>
-      <c r="C166" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D166" s="4" t="inlineStr"/>
-      <c r="E166" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F166" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderStartDatetime?</t>
-        </is>
-      </c>
-      <c r="G166" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H166" s="4" t="inlineStr"/>
-      <c r="I166" s="4" t="inlineStr"/>
-      <c r="J166" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="4" t="inlineStr">
-        <is>
-          <t>siteCompanyCode</t>
-        </is>
-      </c>
-      <c r="B167" s="4" t="inlineStr">
-        <is>
-          <t>RepairOrder</t>
-        </is>
-      </c>
-      <c r="C167" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D167" s="4" t="inlineStr"/>
-      <c r="E167" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F167" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.siteCompanyCode?</t>
-        </is>
-      </c>
-      <c r="G167" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H167" s="4" t="inlineStr"/>
-      <c r="I167" s="4" t="inlineStr"/>
-      <c r="J167" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="4" t="inlineStr">
-        <is>
-          <t>repairType</t>
-        </is>
-      </c>
-      <c r="B168" s="4" t="inlineStr">
-        <is>
-          <t>RepairOrder</t>
-        </is>
-      </c>
-      <c r="C168" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D168" s="4" t="inlineStr"/>
-      <c r="E168" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F168" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairType?</t>
-        </is>
-      </c>
-      <c r="G168" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H168" s="4" t="inlineStr"/>
-      <c r="I168" s="4" t="inlineStr"/>
-      <c r="J168" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="4" t="inlineStr">
-        <is>
-          <t>partsOrderDateTime</t>
-        </is>
-      </c>
-      <c r="B169" s="4" t="inlineStr">
-        <is>
-          <t>RepairOrder</t>
-        </is>
-      </c>
-      <c r="C169" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D169" s="4" t="inlineStr"/>
-      <c r="E169" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F169" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsOrderDateTime?</t>
-        </is>
-      </c>
-      <c r="G169" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H169" s="4" t="inlineStr"/>
-      <c r="I169" s="4" t="inlineStr"/>
-      <c r="J169" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="4" t="inlineStr">
-        <is>
-          <t>partsReceivedDateTime</t>
-        </is>
-      </c>
-      <c r="B170" s="4" t="inlineStr">
-        <is>
-          <t>RepairOrder</t>
-        </is>
-      </c>
-      <c r="C170" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D170" s="4" t="inlineStr"/>
-      <c r="E170" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F170" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.partsReceivedDateTime?</t>
-        </is>
-      </c>
-      <c r="G170" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H170" s="4" t="inlineStr"/>
-      <c r="I170" s="4" t="inlineStr"/>
-      <c r="J170" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="4" t="inlineStr">
-        <is>
-          <t>repairCode</t>
-        </is>
-      </c>
-      <c r="B171" s="4" t="inlineStr">
-        <is>
-          <t>RepairOrder</t>
-        </is>
-      </c>
-      <c r="C171" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D171" s="4" t="inlineStr"/>
-      <c r="E171" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F171" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCode?</t>
-        </is>
-      </c>
-      <c r="G171" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H171" s="4" t="inlineStr"/>
-      <c r="I171" s="4" t="inlineStr"/>
-      <c r="J171" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="4" t="inlineStr">
-        <is>
-          <t>repairCompany</t>
-        </is>
-      </c>
-      <c r="B172" s="4" t="inlineStr">
-        <is>
-          <t>RepairOrder</t>
-        </is>
-      </c>
-      <c r="C172" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D172" s="4" t="inlineStr"/>
-      <c r="E172" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F172" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.repairCompany?</t>
-        </is>
-      </c>
-      <c r="G172" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H172" s="4" t="inlineStr"/>
-      <c r="I172" s="4" t="inlineStr"/>
-      <c r="J172" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="4" t="inlineStr">
-        <is>
-          <t>raStatus</t>
-        </is>
-      </c>
-      <c r="B173" s="4" t="inlineStr">
-        <is>
-          <t>RepairOrder</t>
-        </is>
-      </c>
-      <c r="C173" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D173" s="4" t="inlineStr"/>
-      <c r="E173" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F173" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.raStatus?</t>
-        </is>
-      </c>
-      <c r="G173" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H173" s="4" t="inlineStr"/>
-      <c r="I173" s="4" t="inlineStr"/>
-      <c r="J173" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="4" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
-      <c r="B174" s="4" t="inlineStr">
-        <is>
-          <t>RepairOrder</t>
-        </is>
-      </c>
-      <c r="C174" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D174" s="4" t="inlineStr"/>
-      <c r="E174" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F174" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.Warehouse?</t>
-        </is>
-      </c>
-      <c r="G174" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H174" s="4" t="inlineStr"/>
-      <c r="I174" s="4" t="inlineStr"/>
-      <c r="J174" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="4" t="inlineStr">
-        <is>
-          <t>assignedPerson</t>
-        </is>
-      </c>
-      <c r="B175" s="4" t="inlineStr">
-        <is>
-          <t>RepairOrder</t>
-        </is>
-      </c>
-      <c r="C175" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D175" s="4" t="inlineStr"/>
-      <c r="E175" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F175" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.assignedPerson?</t>
-        </is>
-      </c>
-      <c r="G175" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H175" s="4" t="inlineStr"/>
-      <c r="I175" s="4" t="inlineStr"/>
-      <c r="J175" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="4" t="inlineStr">
-        <is>
-          <t>resolvedDateTime</t>
-        </is>
-      </c>
-      <c r="B176" s="4" t="inlineStr">
-        <is>
-          <t>RepairOrder</t>
-        </is>
-      </c>
-      <c r="C176" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D176" s="4" t="inlineStr"/>
-      <c r="E176" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F176" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.resolvedDateTime?</t>
-        </is>
-      </c>
-      <c r="G176" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H176" s="4" t="inlineStr"/>
-      <c r="I176" s="4" t="inlineStr"/>
-      <c r="J176" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="4" t="inlineStr">
-        <is>
-          <t>serialNumber</t>
-        </is>
-      </c>
-      <c r="B177" s="4" t="inlineStr">
-        <is>
-          <t>RepairOrder</t>
-        </is>
-      </c>
-      <c r="C177" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D177" s="4" t="inlineStr"/>
-      <c r="E177" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F177" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.serialNumber?</t>
-        </is>
-      </c>
-      <c r="G177" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H177" s="4" t="inlineStr"/>
-      <c r="I177" s="4" t="inlineStr"/>
-      <c r="J177" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="4" t="inlineStr">
-        <is>
-          <t>quantityUsed</t>
-        </is>
-      </c>
-      <c r="B178" s="4" t="inlineStr">
-        <is>
-          <t>RepairOrder</t>
-        </is>
-      </c>
-      <c r="C178" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D178" s="4" t="inlineStr"/>
-      <c r="E178" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F178" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.quantityUsed?</t>
-        </is>
-      </c>
-      <c r="G178" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H178" s="4" t="inlineStr"/>
-      <c r="I178" s="4" t="inlineStr"/>
-      <c r="J178" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="4" t="inlineStr">
-        <is>
-          <t>deviceSerialNumber</t>
-        </is>
-      </c>
-      <c r="B179" s="4" t="inlineStr">
-        <is>
-          <t>RepairOrder</t>
-        </is>
-      </c>
-      <c r="C179" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D179" s="4" t="inlineStr"/>
-      <c r="E179" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F179" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.deviceSerialNumber?</t>
-        </is>
-      </c>
-      <c r="G179" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H179" s="4" t="inlineStr"/>
-      <c r="I179" s="4" t="inlineStr"/>
-      <c r="J179" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="4" t="inlineStr">
-        <is>
-          <t>orderedPartId</t>
-        </is>
-      </c>
-      <c r="B180" s="4" t="inlineStr">
-        <is>
-          <t>RepairOrder</t>
-        </is>
-      </c>
-      <c r="C180" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D180" s="4" t="inlineStr"/>
-      <c r="E180" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F180" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.orderedPartId?</t>
-        </is>
-      </c>
-      <c r="G180" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H180" s="4" t="inlineStr"/>
-      <c r="I180" s="4" t="inlineStr"/>
-      <c r="J180" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="4" t="inlineStr">
-        <is>
-          <t>actualPartId</t>
-        </is>
-      </c>
-      <c r="B181" s="4" t="inlineStr">
-        <is>
-          <t>RepairOrder</t>
-        </is>
-      </c>
-      <c r="C181" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D181" s="4" t="inlineStr"/>
-      <c r="E181" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F181" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate RepairOrder.actualPartId?</t>
-        </is>
-      </c>
-      <c r="G181" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H181" s="4" t="inlineStr"/>
-      <c r="I181" s="4" t="inlineStr"/>
-      <c r="J181" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="4" t="inlineStr">
-        <is>
-          <t>partCode</t>
-        </is>
-      </c>
-      <c r="B182" s="4" t="inlineStr">
-        <is>
-          <t>Models</t>
-        </is>
-      </c>
-      <c r="C182" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D182" s="4" t="inlineStr"/>
-      <c r="E182" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F182" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.partCode?</t>
-        </is>
-      </c>
-      <c r="G182" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H182" s="4" t="inlineStr"/>
-      <c r="I182" s="4" t="inlineStr"/>
-      <c r="J182" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="4" t="inlineStr">
-        <is>
-          <t>modelCode</t>
-        </is>
-      </c>
-      <c r="B183" s="4" t="inlineStr">
-        <is>
-          <t>Models</t>
-        </is>
-      </c>
-      <c r="C183" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D183" s="4" t="inlineStr"/>
-      <c r="E183" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F183" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelCode?</t>
-        </is>
-      </c>
-      <c r="G183" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H183" s="4" t="inlineStr"/>
-      <c r="I183" s="4" t="inlineStr"/>
-      <c r="J183" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="4" t="inlineStr">
-        <is>
-          <t>modelDescription</t>
-        </is>
-      </c>
-      <c r="B184" s="4" t="inlineStr">
-        <is>
-          <t>Models</t>
-        </is>
-      </c>
-      <c r="C184" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D184" s="4" t="inlineStr"/>
-      <c r="E184" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F184" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate Models.modelDescription?</t>
-        </is>
-      </c>
-      <c r="G184" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H184" s="4" t="inlineStr"/>
-      <c r="I184" s="4" t="inlineStr"/>
-      <c r="J184" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="4" t="inlineStr">
-        <is>
-          <t>movementType</t>
-        </is>
-      </c>
-      <c r="B185" s="4" t="inlineStr">
-        <is>
-          <t>InventoryTransfers</t>
-        </is>
-      </c>
-      <c r="C185" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D185" s="4" t="inlineStr"/>
-      <c r="E185" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F185" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.movementType?</t>
-        </is>
-      </c>
-      <c r="G185" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H185" s="4" t="inlineStr"/>
-      <c r="I185" s="4" t="inlineStr"/>
-      <c r="J185" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="4" t="inlineStr">
-        <is>
-          <t>addressId</t>
-        </is>
-      </c>
-      <c r="B186" s="4" t="inlineStr">
-        <is>
-          <t>InventoryTransfers</t>
-        </is>
-      </c>
-      <c r="C186" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D186" s="4" t="inlineStr"/>
-      <c r="E186" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F186" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.addressId?</t>
-        </is>
-      </c>
-      <c r="G186" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H186" s="4" t="inlineStr"/>
-      <c r="I186" s="4" t="inlineStr"/>
-      <c r="J186" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="4" t="inlineStr">
-        <is>
-          <t>Bpart</t>
-        </is>
-      </c>
-      <c r="B187" s="4" t="inlineStr">
-        <is>
-          <t>InventoryTransfers</t>
-        </is>
-      </c>
-      <c r="C187" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D187" s="4" t="inlineStr"/>
-      <c r="E187" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F187" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.Bpart?</t>
-        </is>
-      </c>
-      <c r="G187" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H187" s="4" t="inlineStr"/>
-      <c r="I187" s="4" t="inlineStr"/>
-      <c r="J187" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="4" t="inlineStr">
-        <is>
-          <t>shipListCode</t>
-        </is>
-      </c>
-      <c r="B188" s="4" t="inlineStr">
-        <is>
-          <t>InventoryTransfers</t>
-        </is>
-      </c>
-      <c r="C188" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D188" s="4" t="inlineStr"/>
-      <c r="E188" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F188" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate InventoryTransfers.shipListCode?</t>
-        </is>
-      </c>
-      <c r="G188" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H188" s="4" t="inlineStr"/>
-      <c r="I188" s="4" t="inlineStr"/>
-      <c r="J188" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="3" t="inlineStr">
-        <is>
-          <t>demandStatus</t>
-        </is>
-      </c>
-      <c r="B189" s="3" t="inlineStr">
-        <is>
-          <t>PurchaseOrders</t>
-        </is>
-      </c>
-      <c r="C189" s="3" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D189" s="3" t="inlineStr"/>
-      <c r="E189" s="3" t="inlineStr">
-        <is>
-          <t>Review required</t>
-        </is>
-      </c>
-      <c r="F189" s="3" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PurchaseOrders.demandStatus?</t>
-        </is>
-      </c>
-      <c r="G189" s="3" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H189" s="3" t="inlineStr"/>
-      <c r="I189" s="3" t="inlineStr"/>
-      <c r="J189" s="3" t="inlineStr">
-        <is>
-          <t>Conditional HelpDesk enrichment. Use ReplenishStatus only when PurchaseOrder filename stem matches SAP OPOR.NumAtCard and part/SPL Master evidence also matches.</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="4" t="inlineStr">
-        <is>
-          <t>partType</t>
-        </is>
-      </c>
-      <c r="B190" s="4" t="inlineStr">
-        <is>
-          <t>PartTypes</t>
-        </is>
-      </c>
-      <c r="C190" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D190" s="4" t="inlineStr"/>
-      <c r="E190" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F190" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.partType?</t>
-        </is>
-      </c>
-      <c r="G190" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H190" s="4" t="inlineStr"/>
-      <c r="I190" s="4" t="inlineStr"/>
-      <c r="J190" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="4" t="inlineStr">
-        <is>
-          <t>partTypeDescription</t>
-        </is>
-      </c>
-      <c r="B191" s="4" t="inlineStr">
-        <is>
-          <t>PartTypes</t>
-        </is>
-      </c>
-      <c r="C191" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D191" s="4" t="inlineStr"/>
-      <c r="E191" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F191" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeDescription?</t>
-        </is>
-      </c>
-      <c r="G191" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H191" s="4" t="inlineStr"/>
-      <c r="I191" s="4" t="inlineStr"/>
-      <c r="J191" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="4" t="inlineStr">
-        <is>
-          <t>isReworkable</t>
-        </is>
-      </c>
-      <c r="B192" s="4" t="inlineStr">
-        <is>
-          <t>PartTypes</t>
-        </is>
-      </c>
-      <c r="C192" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D192" s="4" t="inlineStr"/>
-      <c r="E192" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F192" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.isReworkable?</t>
-        </is>
-      </c>
-      <c r="G192" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H192" s="4" t="inlineStr"/>
-      <c r="I192" s="4" t="inlineStr"/>
-      <c r="J192" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="4" t="inlineStr">
-        <is>
-          <t>partNumber</t>
-        </is>
-      </c>
-      <c r="B193" s="4" t="inlineStr">
-        <is>
-          <t>Yields</t>
-        </is>
-      </c>
-      <c r="C193" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D193" s="4" t="inlineStr"/>
-      <c r="E193" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F193" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.partNumber?</t>
-        </is>
-      </c>
-      <c r="G193" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H193" s="4" t="inlineStr"/>
-      <c r="I193" s="4" t="inlineStr"/>
-      <c r="J193" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="4" t="inlineStr">
-        <is>
-          <t>unitOfMeasure</t>
-        </is>
-      </c>
-      <c r="B194" s="4" t="inlineStr">
-        <is>
-          <t>Yields</t>
-        </is>
-      </c>
-      <c r="C194" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D194" s="4" t="inlineStr"/>
-      <c r="E194" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F194" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.unitOfMeasure?</t>
-        </is>
-      </c>
-      <c r="G194" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H194" s="4" t="inlineStr"/>
-      <c r="I194" s="4" t="inlineStr"/>
-      <c r="J194" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="4" t="inlineStr">
-        <is>
-          <t>yield</t>
-        </is>
-      </c>
-      <c r="B195" s="4" t="inlineStr">
-        <is>
-          <t>Yields</t>
-        </is>
-      </c>
-      <c r="C195" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D195" s="4" t="inlineStr"/>
-      <c r="E195" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F195" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate Yields.yield?</t>
-        </is>
-      </c>
-      <c r="G195" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H195" s="4" t="inlineStr"/>
-      <c r="I195" s="4" t="inlineStr"/>
-      <c r="J195" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="4" t="inlineStr">
-        <is>
-          <t>Secondary TO</t>
-        </is>
-      </c>
-      <c r="B196" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C196" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D196" s="4" t="inlineStr"/>
-      <c r="E196" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F196" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary TO?</t>
-        </is>
-      </c>
-      <c r="G196" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H196" s="4" t="inlineStr"/>
-      <c r="I196" s="4" t="inlineStr"/>
-      <c r="J196" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="4" t="inlineStr">
-        <is>
-          <t>Secondary FROM</t>
-        </is>
-      </c>
-      <c r="B197" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C197" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D197" s="4" t="inlineStr"/>
-      <c r="E197" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F197" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Secondary FROM?</t>
-        </is>
-      </c>
-      <c r="G197" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H197" s="4" t="inlineStr"/>
-      <c r="I197" s="4" t="inlineStr"/>
-      <c r="J197" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="4" t="inlineStr">
-        <is>
-          <t>Cross TO</t>
-        </is>
-      </c>
-      <c r="B198" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C198" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D198" s="4" t="inlineStr"/>
-      <c r="E198" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F198" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross TO?</t>
-        </is>
-      </c>
-      <c r="G198" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H198" s="4" t="inlineStr"/>
-      <c r="I198" s="4" t="inlineStr"/>
-      <c r="J198" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="4" t="inlineStr">
-        <is>
-          <t>Cross FROM</t>
-        </is>
-      </c>
-      <c r="B199" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C199" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D199" s="4" t="inlineStr"/>
-      <c r="E199" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F199" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Cross FROM?</t>
-        </is>
-      </c>
-      <c r="G199" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H199" s="4" t="inlineStr"/>
-      <c r="I199" s="4" t="inlineStr"/>
-      <c r="J199" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="4" t="inlineStr">
-        <is>
-          <t>Primary TO</t>
-        </is>
-      </c>
-      <c r="B200" s="4" t="inlineStr">
-        <is>
-          <t>WarehouseExclusions</t>
-        </is>
-      </c>
-      <c r="C200" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D200" s="4" t="inlineStr"/>
-      <c r="E200" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F200" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate WarehouseExclusions.Primary TO?</t>
-        </is>
-      </c>
-      <c r="G200" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H200" s="4" t="inlineStr"/>
-      <c r="I200" s="4" t="inlineStr"/>
-      <c r="J200" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J200"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -31681,29 +29678,29 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Nodes</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Nodes.csv</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Pending/header only</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Deferred post-MVP</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>nodeId, parentNodeId, nodeDescription</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>nodeId; parentNodeId; nodeDescription</t>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: regional umbrella for warehouse/address hierarchy; not for MVP.</t>
         </is>
       </c>
     </row>
@@ -31920,56 +29917,56 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>ServiceOrder</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>ServiceOrder.csv</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Pending/header only</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Deferred post-MVP</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>orderNumber, RequestID, location, eta, actualEta, actualResolveDateTime, recallDateTime, actualRecallDateTime, slaEtaClock, slaResolveClock, slaFailureCode, slaEtaHit, slaResolveDateTime</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>orderNumber; RequestID; location; eta; actualEta; actualResolveDateTime; recallDateTime; actualRecallDateTime; slaEtaClock; slaResolveClock; slaFailureCode; slaEtaHit; slaResolveDateTime</t>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: this would be the HelpDesk ticket list, but without ticket close times it is not usable for MVP.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>RepairOrder</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>RepairOrder.csv</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Pending/header only</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Out of CoCre8 scope</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>orderNumber, requestId, customerCompanyCode, orderStatus, orderStartDatetime, siteCompanyCode, repairType, partsOrderDateTime, partsReceivedDateTime, repairCode, repairCompany, raStatus, Warehouse, assignedPerson, resolvedDateTime, serialNumber, quantityUsed, deviceSerialNumber, orderedPartId, actualPartId</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>orderNumber; requestId; customerCompanyCode; orderStatus; orderStartDatetime; siteCompanyCode; repairType; partsOrderDateTime; partsReceivedDateTime; repairCode; repairCompany; raStatus; Warehouse; assignedPerson; resolvedDateTime; serialNumber; quantityUsed; deviceSerialNumber; orderedPartId; actualPartId</t>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Chris feedback: RepairOrder is not used by CoCre8.</t>
         </is>
       </c>
     </row>
@@ -31997,29 +29994,29 @@
       <c r="E27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Models</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Models.csv</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Pending/header only</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Deferred post-MVP</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>partCode, modelCode, modelDescription</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>partCode; modelCode; modelDescription</t>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: important, but not for MVP.</t>
         </is>
       </c>
     </row>
@@ -32105,29 +30102,29 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>Yields</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Yields.csv</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Pending/header only</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Deferred post-MVP</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>partNumber, unitOfMeasure, yield</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>partNumber; unitOfMeasure; yield</t>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: yield means expected uses or average years before breakdown; not for MVP.</t>
         </is>
       </c>
     </row>
@@ -32144,45 +30141,49 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Out of v1 scope</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr"/>
-      <c r="E33" s="5" t="inlineStr"/>
+          <t>Deferred post-MVP</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>actionGroupId, nodeId, actionGroupDescription, assignAnySkill, isUsed, isObsolete</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Chris feedback: technician/action group by region; not for MVP.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>WarehouseExclusions</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>WarehouseExclusions.csv</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Pending/header only</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Ready</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>Secondary TO, Secondary FROM, Cross TO, Cross FROM, Primary TO</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>Secondary TO; Secondary FROM; Cross TO; Cross FROM; Primary TO</t>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Chris feedback: no warehouse exclusions to start with; empty upload is intentional.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -34579,11 +32580,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -34874,10 +32871,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
--- a/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
+++ b/docs/field-map/CoCre8_PlanningV2_Field_Map.xlsx
@@ -20978,70 +20978,78 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="4" t="inlineStr">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>PartTypes</t>
         </is>
       </c>
-      <c r="B161" s="4" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>partType</t>
         </is>
       </c>
-      <c r="C161" s="4" t="inlineStr"/>
-      <c r="D161" s="4" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr"/>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Canonical header from partTypes.xlsx</t>
         </is>
       </c>
-      <c r="E161" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F161" s="4" t="inlineStr"/>
-      <c r="G161" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H161" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Hosted Altsgen batch API:commodity_type for CoCre8 parts</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="4" t="inlineStr">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>PartTypes</t>
         </is>
       </c>
-      <c r="B162" s="4" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>partTypeDescription</t>
         </is>
       </c>
-      <c r="C162" s="4" t="inlineStr"/>
-      <c r="D162" s="4" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr"/>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Canonical header from partTypes.xlsx</t>
         </is>
       </c>
-      <c r="E162" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F162" s="4" t="inlineStr"/>
-      <c r="G162" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H162" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>Hosted Altsgen batch API:spec_summary.description or humanized commodity_type</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>Populated in template CSV from confirmed live SAP Service Layer or allowed SPI source.</t>
         </is>
       </c>
     </row>
@@ -21948,7 +21956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J153"/>
+  <dimension ref="A1:J151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -29166,7 +29174,7 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>partType</t>
+          <t>isReworkable</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
@@ -29187,7 +29195,7 @@
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.partType?</t>
+          <t>What confirmed CoCre8/SAP source should populate PartTypes.isReworkable?</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
@@ -29198,86 +29206,6 @@
       <c r="H151" s="4" t="inlineStr"/>
       <c r="I151" s="4" t="inlineStr"/>
       <c r="J151" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="4" t="inlineStr">
-        <is>
-          <t>partTypeDescription</t>
-        </is>
-      </c>
-      <c r="B152" s="4" t="inlineStr">
-        <is>
-          <t>PartTypes</t>
-        </is>
-      </c>
-      <c r="C152" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D152" s="4" t="inlineStr"/>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F152" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.partTypeDescription?</t>
-        </is>
-      </c>
-      <c r="G152" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H152" s="4" t="inlineStr"/>
-      <c r="I152" s="4" t="inlineStr"/>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="4" t="inlineStr">
-        <is>
-          <t>isReworkable</t>
-        </is>
-      </c>
-      <c r="B153" s="4" t="inlineStr">
-        <is>
-          <t>PartTypes</t>
-        </is>
-      </c>
-      <c r="C153" s="4" t="inlineStr">
-        <is>
-          <t>Planning V2 template</t>
-        </is>
-      </c>
-      <c r="D153" s="4" t="inlineStr"/>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP first</t>
-        </is>
-      </c>
-      <c r="F153" s="4" t="inlineStr">
-        <is>
-          <t>What confirmed CoCre8/SAP source should populate PartTypes.isReworkable?</t>
-        </is>
-      </c>
-      <c r="G153" s="4" t="inlineStr">
-        <is>
-          <t>Investigate SAP Service Layer first; only use external/manual source if SAP cannot supply it.</t>
-        </is>
-      </c>
-      <c r="H153" s="4" t="inlineStr"/>
-      <c r="I153" s="4" t="inlineStr"/>
-      <c r="J153" s="4" t="inlineStr">
         <is>
           <t>Left blank in generated template CSV until source and semantics are confirmed.</t>
         </is>
@@ -30075,29 +30003,29 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>PartTypes</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>PartTypes.csv</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Pending/header only</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>partType, partTypeDescription, isReworkable</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>partType; partTypeDescription; isReworkable</t>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>isReworkable</t>
         </is>
       </c>
     </row>
